--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30318"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="282" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E12C3ED9-BCF8-44EA-9114-C7489D24A71A}"/>
+  <xr:revisionPtr revIDLastSave="332" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D8165A2-D382-4E56-AC07-AD791523EB0C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="523">
   <si>
     <t>material</t>
   </si>
@@ -388,6 +388,15 @@
     <t>CX FERRAMENTA RANDON</t>
   </si>
   <si>
+    <t>CJ ENGATE HIDRAULICO 16. 1POL NPT</t>
+  </si>
+  <si>
+    <t>CJ ENGATE HIDRAULICO 16. 3/4 NPT</t>
+  </si>
+  <si>
+    <t>CJ ENGATE HIDRAULICO 12. 3/4 NPT</t>
+  </si>
+  <si>
     <t>DESLIZANTE RANDON</t>
   </si>
   <si>
@@ -874,6 +883,9 @@
     <t>PORCA CASTELADA LIBRELATO (PORCA DO EIXO DO CUBO)</t>
   </si>
   <si>
+    <t>PRATO PNEUMATICO RANDON SUPERIOR 33MM</t>
+  </si>
+  <si>
     <t>PRATO PNEUMATICO RANDON INFERIOR 33MM</t>
   </si>
   <si>
@@ -1033,6 +1045,9 @@
     <t>SUPORTE LANTERNA PARALAMA VOLVO</t>
   </si>
   <si>
+    <t>SUPORTE LANTERNA LATERAL PARALAMA SCANIA</t>
+  </si>
+  <si>
     <t>SUPORTE FIXO BARRA CICLISTA LIBRELATO</t>
   </si>
   <si>
@@ -1216,6 +1231,9 @@
     <t>VALVULA LIBERAÇÃO CARRETA</t>
   </si>
   <si>
+    <t>SIRENE DE RÉ</t>
+  </si>
+  <si>
     <t>VALVULA TRANSFERÊNCIA</t>
   </si>
   <si>
@@ -1456,6 +1474,9 @@
     <t>Borracharia</t>
   </si>
   <si>
+    <t>BICO DE RODA CAVALO</t>
+  </si>
+  <si>
     <t>BICO PNEU (RODA FERRO CARRETA)</t>
   </si>
   <si>
@@ -1598,13 +1619,16 @@
   </si>
   <si>
     <t>TINTA SPRAY AZU 250GR</t>
+  </si>
+  <si>
+    <t>REBITE DE FERRRO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1656,6 +1680,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1677,7 +1709,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1802,11 +1834,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1889,6 +1934,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2170,7 +2225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1210"/>
+  <dimension ref="A1:F1217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2400,7 +2455,7 @@
     </row>
     <row r="21" spans="1:3" ht="15.75">
       <c r="A21" s="14">
-        <v>68686</v>
+        <v>1010003615</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>23</v>
@@ -2433,7 +2488,7 @@
     </row>
     <row r="24" spans="1:3" ht="15.75">
       <c r="A24" s="15">
-        <v>1040097671</v>
+        <v>1010012011</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>26</v>
@@ -3368,7 +3423,7 @@
     </row>
     <row r="109" spans="1:3" ht="15.75">
       <c r="A109" s="15">
-        <v>1040098597</v>
+        <v>1010087644</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>111</v>
@@ -3379,7 +3434,7 @@
     </row>
     <row r="110" spans="1:3" ht="15.75">
       <c r="A110" s="15">
-        <v>1040084464</v>
+        <v>1010087544</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>112</v>
@@ -3390,7 +3445,7 @@
     </row>
     <row r="111" spans="1:3" ht="15.75">
       <c r="A111" s="15">
-        <v>1040017773</v>
+        <v>1010087773</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>113</v>
@@ -3401,7 +3456,7 @@
     </row>
     <row r="112" spans="1:3" ht="15.75">
       <c r="A112" s="15">
-        <v>1010007405</v>
+        <v>1040098597</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>114</v>
@@ -3411,8 +3466,8 @@
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75">
-      <c r="A113" s="17">
-        <v>1040077365</v>
+      <c r="A113" s="15">
+        <v>1040084464</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>115</v>
@@ -3423,7 +3478,7 @@
     </row>
     <row r="114" spans="1:3" ht="15.75">
       <c r="A114" s="15">
-        <v>1010027794</v>
+        <v>1040017773</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>116</v>
@@ -3434,7 +3489,7 @@
     </row>
     <row r="115" spans="1:3" ht="15.75">
       <c r="A115" s="15">
-        <v>1040077366</v>
+        <v>1010007405</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>117</v>
@@ -3444,8 +3499,8 @@
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75">
-      <c r="A116" s="15">
-        <v>1040077367</v>
+      <c r="A116" s="17">
+        <v>1040077365</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>118</v>
@@ -3456,7 +3511,7 @@
     </row>
     <row r="117" spans="1:3" ht="15.75">
       <c r="A117" s="15">
-        <v>1010021561</v>
+        <v>1010027794</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>119</v>
@@ -3467,7 +3522,7 @@
     </row>
     <row r="118" spans="1:3" ht="15.75">
       <c r="A118" s="15">
-        <v>1010021562</v>
+        <v>1040077366</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>120</v>
@@ -3478,7 +3533,7 @@
     </row>
     <row r="119" spans="1:3" ht="15.75">
       <c r="A119" s="15">
-        <v>1010027792</v>
+        <v>1040077367</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>121</v>
@@ -3489,7 +3544,7 @@
     </row>
     <row r="120" spans="1:3" ht="15.75">
       <c r="A120" s="15">
-        <v>1010084930</v>
+        <v>1010021561</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>122</v>
@@ -3500,7 +3555,7 @@
     </row>
     <row r="121" spans="1:3" ht="15.75">
       <c r="A121" s="15">
-        <v>341430</v>
+        <v>1010021562</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>123</v>
@@ -3511,7 +3566,7 @@
     </row>
     <row r="122" spans="1:3" ht="15.75">
       <c r="A122" s="15">
-        <v>1010029366</v>
+        <v>1010027792</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>124</v>
@@ -3521,8 +3576,8 @@
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75">
-      <c r="A123" s="18">
-        <v>1010031723</v>
+      <c r="A123" s="15">
+        <v>1010084930</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>125</v>
@@ -3532,8 +3587,8 @@
       </c>
     </row>
     <row r="124" spans="1:3" ht="15.75">
-      <c r="A124" s="18">
-        <v>1010049216</v>
+      <c r="A124" s="15">
+        <v>341430</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>126</v>
@@ -3544,7 +3599,7 @@
     </row>
     <row r="125" spans="1:3" ht="15.75">
       <c r="A125" s="15">
-        <v>405558</v>
+        <v>1010029366</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>127</v>
@@ -3554,8 +3609,8 @@
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75">
-      <c r="A126" s="15">
-        <v>1010023038</v>
+      <c r="A126" s="18">
+        <v>1010031723</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>128</v>
@@ -3565,8 +3620,8 @@
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75">
-      <c r="A127" s="15">
-        <v>1010084109</v>
+      <c r="A127" s="18">
+        <v>1010049216</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>129</v>
@@ -3577,7 +3632,7 @@
     </row>
     <row r="128" spans="1:3" ht="15.75">
       <c r="A128" s="15">
-        <v>1010021582</v>
+        <v>405558</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>130</v>
@@ -3588,7 +3643,7 @@
     </row>
     <row r="129" spans="1:3" ht="15.75">
       <c r="A129" s="15">
-        <v>1010021544</v>
+        <v>1010023038</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>131</v>
@@ -3599,7 +3654,7 @@
     </row>
     <row r="130" spans="1:3" ht="15.75">
       <c r="A130" s="15">
-        <v>1010021564</v>
+        <v>1010084109</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>132</v>
@@ -3610,7 +3665,7 @@
     </row>
     <row r="131" spans="1:3" ht="15.75">
       <c r="A131" s="15">
-        <v>1010023019</v>
+        <v>1010021582</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>133</v>
@@ -3621,7 +3676,7 @@
     </row>
     <row r="132" spans="1:3" ht="15.75">
       <c r="A132" s="15">
-        <v>1010048541</v>
+        <v>1010021544</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>134</v>
@@ -3632,7 +3687,7 @@
     </row>
     <row r="133" spans="1:3" ht="15.75">
       <c r="A133" s="15">
-        <v>1010059334</v>
+        <v>1010021564</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>135</v>
@@ -3643,7 +3698,7 @@
     </row>
     <row r="134" spans="1:3" ht="15.75">
       <c r="A134" s="15">
-        <v>1010000277</v>
+        <v>1010023019</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>136</v>
@@ -3653,10 +3708,10 @@
       </c>
     </row>
     <row r="135" spans="1:3" ht="15.75">
-      <c r="A135" s="19">
-        <v>1010085344</v>
-      </c>
-      <c r="B135" s="8" t="s">
+      <c r="A135" s="15">
+        <v>1010048541</v>
+      </c>
+      <c r="B135" s="5" t="s">
         <v>137</v>
       </c>
       <c r="C135" s="4" t="s">
@@ -3664,10 +3719,10 @@
       </c>
     </row>
     <row r="136" spans="1:3" ht="15.75">
-      <c r="A136" s="19">
-        <v>1010085383</v>
-      </c>
-      <c r="B136" s="8" t="s">
+      <c r="A136" s="15">
+        <v>1010059334</v>
+      </c>
+      <c r="B136" s="5" t="s">
         <v>138</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -3676,7 +3731,7 @@
     </row>
     <row r="137" spans="1:3" ht="15.75">
       <c r="A137" s="15">
-        <v>1010001389</v>
+        <v>1010000277</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>139</v>
@@ -3686,10 +3741,10 @@
       </c>
     </row>
     <row r="138" spans="1:3" ht="15.75">
-      <c r="A138" s="15">
-        <v>1010017703</v>
-      </c>
-      <c r="B138" s="5" t="s">
+      <c r="A138" s="19">
+        <v>1010085344</v>
+      </c>
+      <c r="B138" s="8" t="s">
         <v>140</v>
       </c>
       <c r="C138" s="4" t="s">
@@ -3697,10 +3752,10 @@
       </c>
     </row>
     <row r="139" spans="1:3" ht="15.75">
-      <c r="A139" s="15">
-        <v>1010052036</v>
-      </c>
-      <c r="B139" s="5" t="s">
+      <c r="A139" s="19">
+        <v>1010085383</v>
+      </c>
+      <c r="B139" s="8" t="s">
         <v>141</v>
       </c>
       <c r="C139" s="4" t="s">
@@ -3709,7 +3764,7 @@
     </row>
     <row r="140" spans="1:3" ht="15.75">
       <c r="A140" s="15">
-        <v>1040097133</v>
+        <v>1010001389</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>142</v>
@@ -3720,9 +3775,9 @@
     </row>
     <row r="141" spans="1:3" ht="15.75">
       <c r="A141" s="15">
-        <v>1040019325</v>
-      </c>
-      <c r="B141" s="9" t="s">
+        <v>1010017703</v>
+      </c>
+      <c r="B141" s="5" t="s">
         <v>143</v>
       </c>
       <c r="C141" s="4" t="s">
@@ -3731,9 +3786,9 @@
     </row>
     <row r="142" spans="1:3" ht="15.75">
       <c r="A142" s="15">
-        <v>64262</v>
-      </c>
-      <c r="B142" s="9" t="s">
+        <v>1010052036</v>
+      </c>
+      <c r="B142" s="5" t="s">
         <v>144</v>
       </c>
       <c r="C142" s="4" t="s">
@@ -3741,10 +3796,10 @@
       </c>
     </row>
     <row r="143" spans="1:3" ht="15.75">
-      <c r="A143" s="14">
-        <v>1010047089</v>
-      </c>
-      <c r="B143" s="9" t="s">
+      <c r="A143" s="15">
+        <v>1040097133</v>
+      </c>
+      <c r="B143" s="5" t="s">
         <v>145</v>
       </c>
       <c r="C143" s="4" t="s">
@@ -3752,8 +3807,8 @@
       </c>
     </row>
     <row r="144" spans="1:3" ht="15.75">
-      <c r="A144" s="14">
-        <v>1040050168</v>
+      <c r="A144" s="15">
+        <v>1040019325</v>
       </c>
       <c r="B144" s="9" t="s">
         <v>146</v>
@@ -3763,8 +3818,8 @@
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75">
-      <c r="A145" s="14">
-        <v>1040077370</v>
+      <c r="A145" s="15">
+        <v>64262</v>
       </c>
       <c r="B145" s="9" t="s">
         <v>147</v>
@@ -3775,7 +3830,7 @@
     </row>
     <row r="146" spans="1:3" ht="15.75">
       <c r="A146" s="14">
-        <v>1040099247</v>
+        <v>1010047089</v>
       </c>
       <c r="B146" s="9" t="s">
         <v>148</v>
@@ -3785,10 +3840,10 @@
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75">
-      <c r="A147" s="15">
-        <v>1040100560</v>
-      </c>
-      <c r="B147" s="5" t="s">
+      <c r="A147" s="14">
+        <v>1040050168</v>
+      </c>
+      <c r="B147" s="9" t="s">
         <v>149</v>
       </c>
       <c r="C147" s="4" t="s">
@@ -3796,10 +3851,10 @@
       </c>
     </row>
     <row r="148" spans="1:3" ht="15.75">
-      <c r="A148" s="15">
-        <v>1040077399</v>
-      </c>
-      <c r="B148" s="5" t="s">
+      <c r="A148" s="14">
+        <v>1040077370</v>
+      </c>
+      <c r="B148" s="9" t="s">
         <v>150</v>
       </c>
       <c r="C148" s="4" t="s">
@@ -3807,10 +3862,10 @@
       </c>
     </row>
     <row r="149" spans="1:3" ht="15.75">
-      <c r="A149" s="15">
-        <v>1040077374</v>
-      </c>
-      <c r="B149" s="5" t="s">
+      <c r="A149" s="14">
+        <v>1040099247</v>
+      </c>
+      <c r="B149" s="9" t="s">
         <v>151</v>
       </c>
       <c r="C149" s="4" t="s">
@@ -3819,7 +3874,7 @@
     </row>
     <row r="150" spans="1:3" ht="15.75">
       <c r="A150" s="15">
-        <v>1040077399</v>
+        <v>1040100560</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>152</v>
@@ -3830,7 +3885,7 @@
     </row>
     <row r="151" spans="1:3" ht="15.75">
       <c r="A151" s="15">
-        <v>1010050632</v>
+        <v>1040077399</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>153</v>
@@ -3841,7 +3896,7 @@
     </row>
     <row r="152" spans="1:3" ht="15.75">
       <c r="A152" s="15">
-        <v>1010020504</v>
+        <v>1040077374</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>154</v>
@@ -3852,7 +3907,7 @@
     </row>
     <row r="153" spans="1:3" ht="15.75">
       <c r="A153" s="15">
-        <v>409250</v>
+        <v>1040077399</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>155</v>
@@ -3863,7 +3918,7 @@
     </row>
     <row r="154" spans="1:3" ht="15.75">
       <c r="A154" s="15">
-        <v>1010020541</v>
+        <v>1010050632</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>156</v>
@@ -3874,7 +3929,7 @@
     </row>
     <row r="155" spans="1:3" ht="15.75">
       <c r="A155" s="15">
-        <v>1010020879</v>
+        <v>1010020504</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>157</v>
@@ -3885,7 +3940,7 @@
     </row>
     <row r="156" spans="1:3" ht="15.75">
       <c r="A156" s="15">
-        <v>1040077380</v>
+        <v>409250</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>158</v>
@@ -3896,7 +3951,7 @@
     </row>
     <row r="157" spans="1:3" ht="15.75">
       <c r="A157" s="15">
-        <v>1010021520</v>
+        <v>1010020541</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>159</v>
@@ -3907,7 +3962,7 @@
     </row>
     <row r="158" spans="1:3" ht="15.75">
       <c r="A158" s="15">
-        <v>1040098861</v>
+        <v>1010020879</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>160</v>
@@ -3918,7 +3973,7 @@
     </row>
     <row r="159" spans="1:3" ht="15.75">
       <c r="A159" s="15">
-        <v>1010077261</v>
+        <v>1040077380</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>161</v>
@@ -3929,7 +3984,7 @@
     </row>
     <row r="160" spans="1:3" ht="15.75">
       <c r="A160" s="15">
-        <v>1010027664</v>
+        <v>1010021520</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>162</v>
@@ -3940,7 +3995,7 @@
     </row>
     <row r="161" spans="1:3" ht="15.75">
       <c r="A161" s="15">
-        <v>1010083731</v>
+        <v>1040098861</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>163</v>
@@ -3951,7 +4006,7 @@
     </row>
     <row r="162" spans="1:3" ht="15.75">
       <c r="A162" s="15">
-        <v>1010083885</v>
+        <v>1010077261</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>164</v>
@@ -3962,7 +4017,7 @@
     </row>
     <row r="163" spans="1:3" ht="15.75">
       <c r="A163" s="15">
-        <v>1010014834</v>
+        <v>1010027664</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>165</v>
@@ -3973,7 +4028,7 @@
     </row>
     <row r="164" spans="1:3" ht="15.75">
       <c r="A164" s="15">
-        <v>1010083908</v>
+        <v>1010083731</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>166</v>
@@ -3984,7 +4039,7 @@
     </row>
     <row r="165" spans="1:3" ht="15.75">
       <c r="A165" s="15">
-        <v>1010024047</v>
+        <v>1010083885</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>167</v>
@@ -3995,7 +4050,7 @@
     </row>
     <row r="166" spans="1:3" ht="15.75">
       <c r="A166" s="15">
-        <v>1040077377</v>
+        <v>1010014834</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>168</v>
@@ -4006,7 +4061,7 @@
     </row>
     <row r="167" spans="1:3" ht="15.75">
       <c r="A167" s="15">
-        <v>1010061942</v>
+        <v>1010083908</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>169</v>
@@ -4017,7 +4072,7 @@
     </row>
     <row r="168" spans="1:3" ht="15.75">
       <c r="A168" s="15">
-        <v>1040097070</v>
+        <v>1010024047</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>170</v>
@@ -4028,7 +4083,7 @@
     </row>
     <row r="169" spans="1:3" ht="15.75">
       <c r="A169" s="15">
-        <v>1040097068</v>
+        <v>1040077377</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>171</v>
@@ -4039,7 +4094,7 @@
     </row>
     <row r="170" spans="1:3" ht="15.75">
       <c r="A170" s="15">
-        <v>22004</v>
+        <v>1010061942</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>172</v>
@@ -4050,7 +4105,7 @@
     </row>
     <row r="171" spans="1:3" ht="15.75">
       <c r="A171" s="15">
-        <v>1010058554</v>
+        <v>1040097070</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>173</v>
@@ -4061,7 +4116,7 @@
     </row>
     <row r="172" spans="1:3" ht="15.75">
       <c r="A172" s="15">
-        <v>1010027308</v>
+        <v>1040097068</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>174</v>
@@ -4071,65 +4126,65 @@
       </c>
     </row>
     <row r="173" spans="1:3" ht="15.75">
-      <c r="A173" s="19">
+      <c r="A173" s="15">
+        <v>1010001010</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="15.75">
+      <c r="A174" s="15">
+        <v>1010058554</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="15.75">
+      <c r="A175" s="15">
+        <v>1010027308</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="15.75">
+      <c r="A176" s="19">
         <v>1040077383</v>
       </c>
-      <c r="B173" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="15.75">
-      <c r="A174" s="19">
+      <c r="B176" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="15.75">
+      <c r="A177" s="19">
         <v>1010025482</v>
       </c>
-      <c r="B174" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" ht="15.75">
-      <c r="A175" s="19">
+      <c r="B177" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="15.75">
+      <c r="A178" s="19">
         <v>1010025509</v>
       </c>
-      <c r="B175" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="15.75">
-      <c r="A176" s="15">
-        <v>1010027789</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="15.75">
-      <c r="A177" s="15">
-        <v>1010027790</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="15.75">
-      <c r="A178" s="15">
-        <v>1010018301</v>
-      </c>
-      <c r="B178" s="5" t="s">
+      <c r="B178" s="8" t="s">
         <v>180</v>
       </c>
       <c r="C178" s="4" t="s">
@@ -4138,7 +4193,7 @@
     </row>
     <row r="179" spans="1:3" ht="15.75">
       <c r="A179" s="15">
-        <v>1010031616</v>
+        <v>1010027789</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>181</v>
@@ -4149,7 +4204,7 @@
     </row>
     <row r="180" spans="1:3" ht="15.75">
       <c r="A180" s="15">
-        <v>1010053728</v>
+        <v>1010027790</v>
       </c>
       <c r="B180" s="5" t="s">
         <v>182</v>
@@ -4160,7 +4215,7 @@
     </row>
     <row r="181" spans="1:3" ht="15.75">
       <c r="A181" s="15">
-        <v>1010020758</v>
+        <v>1010018301</v>
       </c>
       <c r="B181" s="5" t="s">
         <v>183</v>
@@ -4171,7 +4226,7 @@
     </row>
     <row r="182" spans="1:3" ht="15.75">
       <c r="A182" s="15">
-        <v>1010020781</v>
+        <v>1010031616</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>184</v>
@@ -4181,54 +4236,54 @@
       </c>
     </row>
     <row r="183" spans="1:3" ht="15.75">
-      <c r="A183" s="14">
+      <c r="A183" s="15">
+        <v>1010053728</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="15.75">
+      <c r="A184" s="15">
+        <v>1010020758</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="15.75">
+      <c r="A185" s="15">
+        <v>1010020781</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="15.75">
+      <c r="A186" s="14">
         <v>1010058426</v>
       </c>
-      <c r="B183" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" ht="15.75">
-      <c r="A184" s="14">
+      <c r="B186" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="15.75">
+      <c r="A187" s="14">
         <v>1010059332</v>
       </c>
-      <c r="B184" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" ht="15.75">
-      <c r="A185" s="14">
-        <v>1040077389</v>
-      </c>
-      <c r="B185" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="15.75">
-      <c r="A186" s="15">
-        <v>1010021364</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="15.75">
-      <c r="A187" s="20">
-        <v>1010021541</v>
-      </c>
-      <c r="B187" s="5" t="s">
+      <c r="B187" s="9" t="s">
         <v>189</v>
       </c>
       <c r="C187" s="4" t="s">
@@ -4237,7 +4292,7 @@
     </row>
     <row r="188" spans="1:3" ht="15.75">
       <c r="A188" s="14">
-        <v>1010021955</v>
+        <v>1040077389</v>
       </c>
       <c r="B188" s="9" t="s">
         <v>190</v>
@@ -4248,7 +4303,7 @@
     </row>
     <row r="189" spans="1:3" ht="15.75">
       <c r="A189" s="15">
-        <v>1040077388</v>
+        <v>1010021364</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>191</v>
@@ -4258,8 +4313,8 @@
       </c>
     </row>
     <row r="190" spans="1:3" ht="15.75">
-      <c r="A190" s="15">
-        <v>1010058100</v>
+      <c r="A190" s="20">
+        <v>1010021541</v>
       </c>
       <c r="B190" s="5" t="s">
         <v>192</v>
@@ -4269,10 +4324,10 @@
       </c>
     </row>
     <row r="191" spans="1:3" ht="15.75">
-      <c r="A191" s="15">
-        <v>1010020524</v>
-      </c>
-      <c r="B191" s="5" t="s">
+      <c r="A191" s="14">
+        <v>1010021955</v>
+      </c>
+      <c r="B191" s="9" t="s">
         <v>193</v>
       </c>
       <c r="C191" s="4" t="s">
@@ -4281,7 +4336,7 @@
     </row>
     <row r="192" spans="1:3" ht="15.75">
       <c r="A192" s="15">
-        <v>1010021958</v>
+        <v>1040077388</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>194</v>
@@ -4292,7 +4347,7 @@
     </row>
     <row r="193" spans="1:3" ht="15.75">
       <c r="A193" s="15">
-        <v>1010019756</v>
+        <v>1010058100</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>195</v>
@@ -4303,7 +4358,7 @@
     </row>
     <row r="194" spans="1:3" ht="15.75">
       <c r="A194" s="15">
-        <v>1010019752</v>
+        <v>1010020524</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>196</v>
@@ -4314,7 +4369,7 @@
     </row>
     <row r="195" spans="1:3" ht="15.75">
       <c r="A195" s="15">
-        <v>409639</v>
+        <v>1010021958</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>197</v>
@@ -4325,7 +4380,7 @@
     </row>
     <row r="196" spans="1:3" ht="15.75">
       <c r="A196" s="15">
-        <v>1010047089</v>
+        <v>1010019756</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>198</v>
@@ -4336,7 +4391,7 @@
     </row>
     <row r="197" spans="1:3" ht="15.75">
       <c r="A197" s="15">
-        <v>1040084107</v>
+        <v>1010019752</v>
       </c>
       <c r="B197" s="5" t="s">
         <v>199</v>
@@ -4347,7 +4402,7 @@
     </row>
     <row r="198" spans="1:3" ht="15.75">
       <c r="A198" s="15">
-        <v>1010085203</v>
+        <v>409639</v>
       </c>
       <c r="B198" s="5" t="s">
         <v>200</v>
@@ -4358,7 +4413,7 @@
     </row>
     <row r="199" spans="1:3" ht="15.75">
       <c r="A199" s="15">
-        <v>424298</v>
+        <v>1010047089</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>201</v>
@@ -4369,7 +4424,7 @@
     </row>
     <row r="200" spans="1:3" ht="15.75">
       <c r="A200" s="15">
-        <v>421847</v>
+        <v>1040084107</v>
       </c>
       <c r="B200" s="5" t="s">
         <v>202</v>
@@ -4380,7 +4435,7 @@
     </row>
     <row r="201" spans="1:3" ht="15.75">
       <c r="A201" s="15">
-        <v>431573</v>
+        <v>1010085203</v>
       </c>
       <c r="B201" s="5" t="s">
         <v>203</v>
@@ -4391,7 +4446,7 @@
     </row>
     <row r="202" spans="1:3" ht="15.75">
       <c r="A202" s="15">
-        <v>1010021581</v>
+        <v>424298</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>204</v>
@@ -4401,10 +4456,10 @@
       </c>
     </row>
     <row r="203" spans="1:3" ht="15.75">
-      <c r="A203" s="21">
-        <v>412413</v>
-      </c>
-      <c r="B203" s="7" t="s">
+      <c r="A203" s="15">
+        <v>421847</v>
+      </c>
+      <c r="B203" s="5" t="s">
         <v>205</v>
       </c>
       <c r="C203" s="4" t="s">
@@ -4412,8 +4467,8 @@
       </c>
     </row>
     <row r="204" spans="1:3" ht="15.75">
-      <c r="A204" s="22">
-        <v>1010022606</v>
+      <c r="A204" s="15">
+        <v>431573</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>206</v>
@@ -4423,10 +4478,10 @@
       </c>
     </row>
     <row r="205" spans="1:3" ht="15.75">
-      <c r="A205" s="23">
-        <v>1010003527</v>
-      </c>
-      <c r="B205" s="7" t="s">
+      <c r="A205" s="15">
+        <v>1010021581</v>
+      </c>
+      <c r="B205" s="5" t="s">
         <v>207</v>
       </c>
       <c r="C205" s="4" t="s">
@@ -4434,8 +4489,8 @@
       </c>
     </row>
     <row r="206" spans="1:3" ht="15.75">
-      <c r="A206" s="23">
-        <v>1010055707</v>
+      <c r="A206" s="21">
+        <v>1010003541</v>
       </c>
       <c r="B206" s="7" t="s">
         <v>208</v>
@@ -4445,52 +4500,52 @@
       </c>
     </row>
     <row r="207" spans="1:3" ht="15.75">
-      <c r="A207" s="18">
+      <c r="A207" s="22">
+        <v>1010022606</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="15.75">
+      <c r="A208" s="23">
+        <v>1010003527</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="15.75">
+      <c r="A209" s="23">
+        <v>1010055707</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="15.75">
+      <c r="A210" s="18">
         <v>422027</v>
       </c>
-      <c r="B207" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" ht="15.75">
-      <c r="A208" s="14">
+      <c r="B210" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="15.75">
+      <c r="A211" s="14">
         <v>1010011313</v>
-      </c>
-      <c r="B208" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" ht="15.75">
-      <c r="A209" s="15">
-        <v>27051</v>
-      </c>
-      <c r="B209" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" ht="15.75">
-      <c r="A210" s="15">
-        <v>1010011304</v>
-      </c>
-      <c r="B210" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" ht="15.75">
-      <c r="A211" s="15">
-        <v>35659</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>213</v>
@@ -4501,7 +4556,7 @@
     </row>
     <row r="212" spans="1:3" ht="15.75">
       <c r="A212" s="15">
-        <v>1040077390</v>
+        <v>27051</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>214</v>
@@ -4512,7 +4567,7 @@
     </row>
     <row r="213" spans="1:3" ht="15.75">
       <c r="A213" s="15">
-        <v>1010021542</v>
+        <v>1010011304</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>215</v>
@@ -4523,7 +4578,7 @@
     </row>
     <row r="214" spans="1:3" ht="15.75">
       <c r="A214" s="15">
-        <v>1010021733</v>
+        <v>35659</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>216</v>
@@ -4534,7 +4589,7 @@
     </row>
     <row r="215" spans="1:3" ht="15.75">
       <c r="A215" s="15">
-        <v>1010011379</v>
+        <v>1040077390</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>217</v>
@@ -4545,7 +4600,7 @@
     </row>
     <row r="216" spans="1:3" ht="15.75">
       <c r="A216" s="15">
-        <v>1010003279</v>
+        <v>1010021542</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>218</v>
@@ -4556,7 +4611,7 @@
     </row>
     <row r="217" spans="1:3" ht="15.75">
       <c r="A217" s="15">
-        <v>1010011380</v>
+        <v>1010021733</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>219</v>
@@ -4567,7 +4622,7 @@
     </row>
     <row r="218" spans="1:3" ht="15.75">
       <c r="A218" s="15">
-        <v>351197</v>
+        <v>1010011379</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>220</v>
@@ -4578,7 +4633,7 @@
     </row>
     <row r="219" spans="1:3" ht="15.75">
       <c r="A219" s="15">
-        <v>1010011286</v>
+        <v>1010003279</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>221</v>
@@ -4589,7 +4644,7 @@
     </row>
     <row r="220" spans="1:3" ht="15.75">
       <c r="A220" s="15">
-        <v>2479</v>
+        <v>1010011380</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>222</v>
@@ -4600,7 +4655,7 @@
     </row>
     <row r="221" spans="1:3" ht="15.75">
       <c r="A221" s="15">
-        <v>1010011382</v>
+        <v>351197</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>223</v>
@@ -4610,10 +4665,10 @@
       </c>
     </row>
     <row r="222" spans="1:3" ht="15.75">
-      <c r="A222" s="16">
-        <v>1010055703</v>
-      </c>
-      <c r="B222" s="8" t="s">
+      <c r="A222" s="15">
+        <v>1010011286</v>
+      </c>
+      <c r="B222" s="5" t="s">
         <v>224</v>
       </c>
       <c r="C222" s="4" t="s">
@@ -4621,8 +4676,8 @@
       </c>
     </row>
     <row r="223" spans="1:3" ht="15.75">
-      <c r="A223" s="16">
-        <v>4165</v>
+      <c r="A223" s="15">
+        <v>2479</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>225</v>
@@ -4633,9 +4688,9 @@
     </row>
     <row r="224" spans="1:3" ht="15.75">
       <c r="A224" s="15">
-        <v>301626</v>
-      </c>
-      <c r="B224" s="9" t="s">
+        <v>1010011382</v>
+      </c>
+      <c r="B224" s="5" t="s">
         <v>226</v>
       </c>
       <c r="C224" s="4" t="s">
@@ -4643,10 +4698,10 @@
       </c>
     </row>
     <row r="225" spans="1:6" ht="15.75">
-      <c r="A225" s="15">
-        <v>429495</v>
-      </c>
-      <c r="B225" s="5" t="s">
+      <c r="A225" s="16">
+        <v>1010055703</v>
+      </c>
+      <c r="B225" s="8" t="s">
         <v>227</v>
       </c>
       <c r="C225" s="4" t="s">
@@ -4654,8 +4709,8 @@
       </c>
     </row>
     <row r="226" spans="1:6" ht="15.75">
-      <c r="A226" s="15">
-        <v>162998</v>
+      <c r="A226" s="16">
+        <v>4165</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>228</v>
@@ -4666,9 +4721,9 @@
     </row>
     <row r="227" spans="1:6" ht="15.75">
       <c r="A227" s="15">
-        <v>432657</v>
-      </c>
-      <c r="B227" s="5" t="s">
+        <v>301626</v>
+      </c>
+      <c r="B227" s="9" t="s">
         <v>229</v>
       </c>
       <c r="C227" s="4" t="s">
@@ -4677,7 +4732,7 @@
     </row>
     <row r="228" spans="1:6" ht="15.75">
       <c r="A228" s="15">
-        <v>1010021929</v>
+        <v>429495</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>230</v>
@@ -4688,7 +4743,7 @@
     </row>
     <row r="229" spans="1:6" ht="15.75">
       <c r="A229" s="15">
-        <v>428065</v>
+        <v>162998</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>231</v>
@@ -4699,7 +4754,7 @@
     </row>
     <row r="230" spans="1:6" ht="15.75">
       <c r="A230" s="15">
-        <v>1010003404</v>
+        <v>432657</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>232</v>
@@ -4710,9 +4765,9 @@
     </row>
     <row r="231" spans="1:6" ht="15.75">
       <c r="A231" s="15">
-        <v>1010003322</v>
-      </c>
-      <c r="B231" s="7" t="s">
+        <v>1010021929</v>
+      </c>
+      <c r="B231" s="5" t="s">
         <v>233</v>
       </c>
       <c r="C231" s="4" t="s">
@@ -4721,21 +4776,20 @@
     </row>
     <row r="232" spans="1:6" ht="15.75">
       <c r="A232" s="15">
-        <v>17738</v>
-      </c>
-      <c r="B232" s="7" t="s">
+        <v>428065</v>
+      </c>
+      <c r="B232" s="5" t="s">
         <v>234</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F232" s="29"/>
     </row>
     <row r="233" spans="1:6" ht="15.75">
       <c r="A233" s="15">
-        <v>1010085360</v>
-      </c>
-      <c r="B233" s="7" t="s">
+        <v>1010003404</v>
+      </c>
+      <c r="B233" s="5" t="s">
         <v>235</v>
       </c>
       <c r="C233" s="4" t="s">
@@ -4744,9 +4798,9 @@
     </row>
     <row r="234" spans="1:6" ht="15.75">
       <c r="A234" s="15">
-        <v>1040077391</v>
-      </c>
-      <c r="B234" s="5" t="s">
+        <v>1010003322</v>
+      </c>
+      <c r="B234" s="7" t="s">
         <v>236</v>
       </c>
       <c r="C234" s="4" t="s">
@@ -4755,20 +4809,21 @@
     </row>
     <row r="235" spans="1:6" ht="15.75">
       <c r="A235" s="15">
-        <v>1010058624</v>
-      </c>
-      <c r="B235" s="5" t="s">
+        <v>17738</v>
+      </c>
+      <c r="B235" s="7" t="s">
         <v>237</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="F235" s="29"/>
     </row>
     <row r="236" spans="1:6" ht="15.75">
       <c r="A236" s="15">
-        <v>1010024661</v>
-      </c>
-      <c r="B236" s="5" t="s">
+        <v>1010085360</v>
+      </c>
+      <c r="B236" s="7" t="s">
         <v>238</v>
       </c>
       <c r="C236" s="4" t="s">
@@ -4777,7 +4832,7 @@
     </row>
     <row r="237" spans="1:6" ht="15.75">
       <c r="A237" s="15">
-        <v>1040019315</v>
+        <v>1040077391</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>239</v>
@@ -4788,7 +4843,7 @@
     </row>
     <row r="238" spans="1:6" ht="15.75">
       <c r="A238" s="15">
-        <v>1010021089</v>
+        <v>1010058624</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>240</v>
@@ -4799,7 +4854,7 @@
     </row>
     <row r="239" spans="1:6" ht="15.75">
       <c r="A239" s="15">
-        <v>1040017264</v>
+        <v>1010024661</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>241</v>
@@ -4810,7 +4865,7 @@
     </row>
     <row r="240" spans="1:6" ht="15.75">
       <c r="A240" s="15">
-        <v>1010051765</v>
+        <v>1040019315</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>242</v>
@@ -4821,7 +4876,7 @@
     </row>
     <row r="241" spans="1:3" ht="15.75">
       <c r="A241" s="15">
-        <v>1010035272</v>
+        <v>1010021089</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>243</v>
@@ -4832,7 +4887,7 @@
     </row>
     <row r="242" spans="1:3" ht="15.75">
       <c r="A242" s="15">
-        <v>1040077392</v>
+        <v>1040017264</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>244</v>
@@ -4843,7 +4898,7 @@
     </row>
     <row r="243" spans="1:3" ht="15.75">
       <c r="A243" s="15">
-        <v>1040077393</v>
+        <v>1010051765</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>245</v>
@@ -4854,7 +4909,7 @@
     </row>
     <row r="244" spans="1:3" ht="15.75">
       <c r="A244" s="15">
-        <v>1040077395</v>
+        <v>1010035272</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>246</v>
@@ -4865,7 +4920,7 @@
     </row>
     <row r="245" spans="1:3" ht="15.75">
       <c r="A245" s="15">
-        <v>1040077401</v>
+        <v>1040077392</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>247</v>
@@ -4876,7 +4931,7 @@
     </row>
     <row r="246" spans="1:3" ht="15.75">
       <c r="A246" s="15">
-        <v>27572</v>
+        <v>1040077393</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>248</v>
@@ -4887,7 +4942,7 @@
     </row>
     <row r="247" spans="1:3" ht="15.75">
       <c r="A247" s="15">
-        <v>18745</v>
+        <v>1040077395</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>249</v>
@@ -4898,7 +4953,7 @@
     </row>
     <row r="248" spans="1:3" ht="15.75">
       <c r="A248" s="15">
-        <v>1040077396</v>
+        <v>1040077401</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>250</v>
@@ -4909,7 +4964,7 @@
     </row>
     <row r="249" spans="1:3" ht="15.75">
       <c r="A249" s="15">
-        <v>1010036546</v>
+        <v>27572</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>251</v>
@@ -4920,7 +4975,7 @@
     </row>
     <row r="250" spans="1:3" ht="15.75">
       <c r="A250" s="15">
-        <v>1010014049</v>
+        <v>18745</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>252</v>
@@ -4931,7 +4986,7 @@
     </row>
     <row r="251" spans="1:3" ht="15.75">
       <c r="A251" s="15">
-        <v>1010025148</v>
+        <v>1040077396</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>253</v>
@@ -4942,7 +4997,7 @@
     </row>
     <row r="252" spans="1:3" ht="15.75">
       <c r="A252" s="15">
-        <v>1040077394</v>
+        <v>1010036546</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>254</v>
@@ -4953,7 +5008,7 @@
     </row>
     <row r="253" spans="1:3" ht="15.75">
       <c r="A253" s="15">
-        <v>1040077400</v>
+        <v>1010014049</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>255</v>
@@ -4964,7 +5019,7 @@
     </row>
     <row r="254" spans="1:3" ht="15.75">
       <c r="A254" s="15">
-        <v>1040079329</v>
+        <v>1010025148</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>256</v>
@@ -4975,7 +5030,7 @@
     </row>
     <row r="255" spans="1:3" ht="15.75">
       <c r="A255" s="15">
-        <v>1040040957</v>
+        <v>1040077394</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>257</v>
@@ -4986,7 +5041,7 @@
     </row>
     <row r="256" spans="1:3" ht="15.75">
       <c r="A256" s="15">
-        <v>1040077398</v>
+        <v>1040077400</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>258</v>
@@ -4997,7 +5052,7 @@
     </row>
     <row r="257" spans="1:3" ht="15.75">
       <c r="A257" s="15">
-        <v>1010053128</v>
+        <v>1040079329</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>259</v>
@@ -5008,7 +5063,7 @@
     </row>
     <row r="258" spans="1:3" ht="15.75">
       <c r="A258" s="15">
-        <v>1010010599</v>
+        <v>1040040957</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>260</v>
@@ -5019,7 +5074,7 @@
     </row>
     <row r="259" spans="1:3" ht="15.75">
       <c r="A259" s="15">
-        <v>1010056064</v>
+        <v>1040077398</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>261</v>
@@ -5030,7 +5085,7 @@
     </row>
     <row r="260" spans="1:3" ht="15.75">
       <c r="A260" s="15">
-        <v>5389</v>
+        <v>1010053128</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>262</v>
@@ -5041,7 +5096,7 @@
     </row>
     <row r="261" spans="1:3" ht="15.75">
       <c r="A261" s="15">
-        <v>1010055969</v>
+        <v>1010010599</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>263</v>
@@ -5052,7 +5107,7 @@
     </row>
     <row r="262" spans="1:3" ht="15.75">
       <c r="A262" s="15">
-        <v>1010055970</v>
+        <v>1010056064</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>264</v>
@@ -5063,7 +5118,7 @@
     </row>
     <row r="263" spans="1:3" ht="15.75">
       <c r="A263" s="15">
-        <v>181395</v>
+        <v>5389</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>265</v>
@@ -5073,8 +5128,8 @@
       </c>
     </row>
     <row r="264" spans="1:3" ht="15.75">
-      <c r="A264" s="17">
-        <v>1010055962</v>
+      <c r="A264" s="15">
+        <v>1010055969</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>266</v>
@@ -5085,7 +5140,7 @@
     </row>
     <row r="265" spans="1:3" ht="15.75">
       <c r="A265" s="15">
-        <v>1010003578</v>
+        <v>1010055970</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>267</v>
@@ -5096,7 +5151,7 @@
     </row>
     <row r="266" spans="1:3" ht="15.75">
       <c r="A266" s="15">
-        <v>332891</v>
+        <v>181395</v>
       </c>
       <c r="B266" s="5" t="s">
         <v>268</v>
@@ -5106,8 +5161,8 @@
       </c>
     </row>
     <row r="267" spans="1:3" ht="15.75">
-      <c r="A267" s="15">
-        <v>17727</v>
+      <c r="A267" s="17">
+        <v>1010055962</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>269</v>
@@ -5118,7 +5173,7 @@
     </row>
     <row r="268" spans="1:3" ht="15.75">
       <c r="A268" s="15">
-        <v>17918</v>
+        <v>1010003578</v>
       </c>
       <c r="B268" s="5" t="s">
         <v>270</v>
@@ -5129,7 +5184,7 @@
     </row>
     <row r="269" spans="1:3" ht="15.75">
       <c r="A269" s="15">
-        <v>1010020554</v>
+        <v>332891</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>271</v>
@@ -5140,7 +5195,7 @@
     </row>
     <row r="270" spans="1:3" ht="15.75">
       <c r="A270" s="15">
-        <v>1040085949</v>
+        <v>17727</v>
       </c>
       <c r="B270" s="5" t="s">
         <v>272</v>
@@ -5151,7 +5206,7 @@
     </row>
     <row r="271" spans="1:3" ht="15.75">
       <c r="A271" s="15">
-        <v>1010062938</v>
+        <v>17918</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>273</v>
@@ -5162,7 +5217,7 @@
     </row>
     <row r="272" spans="1:3" ht="15.75">
       <c r="A272" s="15">
-        <v>1010062086</v>
+        <v>1010020554</v>
       </c>
       <c r="B272" s="5" t="s">
         <v>274</v>
@@ -5173,7 +5228,7 @@
     </row>
     <row r="273" spans="1:3" ht="15.75">
       <c r="A273" s="15">
-        <v>1010062087</v>
+        <v>1040085949</v>
       </c>
       <c r="B273" s="5" t="s">
         <v>275</v>
@@ -5184,7 +5239,7 @@
     </row>
     <row r="274" spans="1:3" ht="15.75">
       <c r="A274" s="15">
-        <v>1040077373</v>
+        <v>1010091004</v>
       </c>
       <c r="B274" s="5" t="s">
         <v>276</v>
@@ -5194,10 +5249,10 @@
       </c>
     </row>
     <row r="275" spans="1:3" ht="15.75">
-      <c r="A275" s="24">
-        <v>1040077372</v>
-      </c>
-      <c r="B275" s="6" t="s">
+      <c r="A275" s="15">
+        <v>1010062938</v>
+      </c>
+      <c r="B275" s="5" t="s">
         <v>277</v>
       </c>
       <c r="C275" s="4" t="s">
@@ -5205,10 +5260,10 @@
       </c>
     </row>
     <row r="276" spans="1:3" ht="15.75">
-      <c r="A276" s="24">
-        <v>1040097154</v>
-      </c>
-      <c r="B276" s="6" t="s">
+      <c r="A276" s="15">
+        <v>1010062086</v>
+      </c>
+      <c r="B276" s="5" t="s">
         <v>278</v>
       </c>
       <c r="C276" s="4" t="s">
@@ -5216,10 +5271,10 @@
       </c>
     </row>
     <row r="277" spans="1:3" ht="15.75">
-      <c r="A277" s="24">
-        <v>1010042579</v>
-      </c>
-      <c r="B277" s="6" t="s">
+      <c r="A277" s="15">
+        <v>1010062087</v>
+      </c>
+      <c r="B277" s="5" t="s">
         <v>279</v>
       </c>
       <c r="C277" s="4" t="s">
@@ -5228,7 +5283,7 @@
     </row>
     <row r="278" spans="1:3" ht="15.75">
       <c r="A278" s="15">
-        <v>1010081353</v>
+        <v>1040077373</v>
       </c>
       <c r="B278" s="5" t="s">
         <v>280</v>
@@ -5238,10 +5293,10 @@
       </c>
     </row>
     <row r="279" spans="1:3" ht="15.75">
-      <c r="A279" s="15">
-        <v>133108</v>
-      </c>
-      <c r="B279" s="5" t="s">
+      <c r="A279" s="24">
+        <v>1040077372</v>
+      </c>
+      <c r="B279" s="6" t="s">
         <v>281</v>
       </c>
       <c r="C279" s="4" t="s">
@@ -5249,10 +5304,10 @@
       </c>
     </row>
     <row r="280" spans="1:3" ht="15.75">
-      <c r="A280" s="15">
-        <v>269427</v>
-      </c>
-      <c r="B280" s="5" t="s">
+      <c r="A280" s="24">
+        <v>1040097154</v>
+      </c>
+      <c r="B280" s="6" t="s">
         <v>282</v>
       </c>
       <c r="C280" s="4" t="s">
@@ -5260,10 +5315,10 @@
       </c>
     </row>
     <row r="281" spans="1:3" ht="15.75">
-      <c r="A281" s="15">
-        <v>298227</v>
-      </c>
-      <c r="B281" s="5" t="s">
+      <c r="A281" s="24">
+        <v>1010042579</v>
+      </c>
+      <c r="B281" s="6" t="s">
         <v>283</v>
       </c>
       <c r="C281" s="4" t="s">
@@ -5272,7 +5327,7 @@
     </row>
     <row r="282" spans="1:3" ht="15.75">
       <c r="A282" s="15">
-        <v>1010062285</v>
+        <v>1010081353</v>
       </c>
       <c r="B282" s="5" t="s">
         <v>284</v>
@@ -5283,7 +5338,7 @@
     </row>
     <row r="283" spans="1:3" ht="15.75">
       <c r="A283" s="15">
-        <v>1010058052</v>
+        <v>133108</v>
       </c>
       <c r="B283" s="5" t="s">
         <v>285</v>
@@ -5294,7 +5349,7 @@
     </row>
     <row r="284" spans="1:3" ht="15.75">
       <c r="A284" s="15">
-        <v>1010050033</v>
+        <v>269427</v>
       </c>
       <c r="B284" s="5" t="s">
         <v>286</v>
@@ -5304,8 +5359,8 @@
       </c>
     </row>
     <row r="285" spans="1:3" ht="15.75">
-      <c r="A285" s="20">
-        <v>1040098869</v>
+      <c r="A285" s="15">
+        <v>298227</v>
       </c>
       <c r="B285" s="5" t="s">
         <v>287</v>
@@ -5315,8 +5370,8 @@
       </c>
     </row>
     <row r="286" spans="1:3" ht="15.75">
-      <c r="A286" s="20">
-        <v>1010056523</v>
+      <c r="A286" s="15">
+        <v>1010062285</v>
       </c>
       <c r="B286" s="5" t="s">
         <v>288</v>
@@ -5326,8 +5381,8 @@
       </c>
     </row>
     <row r="287" spans="1:3" ht="15.75">
-      <c r="A287" s="20">
-        <v>1010062045</v>
+      <c r="A287" s="15">
+        <v>1010058052</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>289</v>
@@ -5338,7 +5393,7 @@
     </row>
     <row r="288" spans="1:3" ht="15.75">
       <c r="A288" s="15">
-        <v>1040097575</v>
+        <v>1010050033</v>
       </c>
       <c r="B288" s="5" t="s">
         <v>290</v>
@@ -5348,8 +5403,8 @@
       </c>
     </row>
     <row r="289" spans="1:3" ht="15.75">
-      <c r="A289" s="5">
-        <v>1040100107</v>
+      <c r="A289" s="20">
+        <v>1040098869</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>291</v>
@@ -5359,8 +5414,8 @@
       </c>
     </row>
     <row r="290" spans="1:3" ht="15.75">
-      <c r="A290" s="15">
-        <v>1010040346</v>
+      <c r="A290" s="20">
+        <v>1010056523</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>292</v>
@@ -5370,8 +5425,8 @@
       </c>
     </row>
     <row r="291" spans="1:3" ht="15.75">
-      <c r="A291" s="15">
-        <v>1010021543</v>
+      <c r="A291" s="20">
+        <v>1010062045</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>293</v>
@@ -5382,7 +5437,7 @@
     </row>
     <row r="292" spans="1:3" ht="15.75">
       <c r="A292" s="15">
-        <v>1040077397</v>
+        <v>1040097575</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>294</v>
@@ -5392,8 +5447,8 @@
       </c>
     </row>
     <row r="293" spans="1:3" ht="15.75">
-      <c r="A293" s="15">
-        <v>1040094213</v>
+      <c r="A293" s="5">
+        <v>1040100107</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>295</v>
@@ -5404,7 +5459,7 @@
     </row>
     <row r="294" spans="1:3" ht="15.75">
       <c r="A294" s="15">
-        <v>1010085326</v>
+        <v>1010040346</v>
       </c>
       <c r="B294" s="5" t="s">
         <v>296</v>
@@ -5415,7 +5470,7 @@
     </row>
     <row r="295" spans="1:3" ht="15.75">
       <c r="A295" s="15">
-        <v>1010042564</v>
+        <v>1010021543</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>297</v>
@@ -5426,7 +5481,7 @@
     </row>
     <row r="296" spans="1:3" ht="15.75">
       <c r="A296" s="15">
-        <v>1010042688</v>
+        <v>1040077397</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>298</v>
@@ -5437,7 +5492,7 @@
     </row>
     <row r="297" spans="1:3" ht="15.75">
       <c r="A297" s="15">
-        <v>1010040133</v>
+        <v>1040094213</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>299</v>
@@ -5448,7 +5503,7 @@
     </row>
     <row r="298" spans="1:3" ht="15.75">
       <c r="A298" s="15">
-        <v>1010039879</v>
+        <v>1010085326</v>
       </c>
       <c r="B298" s="5" t="s">
         <v>300</v>
@@ -5459,7 +5514,7 @@
     </row>
     <row r="299" spans="1:3" ht="15.75">
       <c r="A299" s="15">
-        <v>62608</v>
+        <v>1010042564</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>301</v>
@@ -5470,7 +5525,7 @@
     </row>
     <row r="300" spans="1:3" ht="15.75">
       <c r="A300" s="15">
-        <v>1040098603</v>
+        <v>1010042688</v>
       </c>
       <c r="B300" s="5" t="s">
         <v>302</v>
@@ -5481,7 +5536,7 @@
     </row>
     <row r="301" spans="1:3" ht="15.75">
       <c r="A301" s="15">
-        <v>1040017266</v>
+        <v>1010040133</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>303</v>
@@ -5492,7 +5547,7 @@
     </row>
     <row r="302" spans="1:3" ht="15.75">
       <c r="A302" s="15">
-        <v>1010063326</v>
+        <v>1010039879</v>
       </c>
       <c r="B302" s="5" t="s">
         <v>304</v>
@@ -5503,7 +5558,7 @@
     </row>
     <row r="303" spans="1:3" ht="15.75">
       <c r="A303" s="15">
-        <v>1010050574</v>
+        <v>62608</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>305</v>
@@ -5513,8 +5568,8 @@
       </c>
     </row>
     <row r="304" spans="1:3" ht="15.75">
-      <c r="A304" s="20">
-        <v>1010086126</v>
+      <c r="A304" s="15">
+        <v>1040098603</v>
       </c>
       <c r="B304" s="5" t="s">
         <v>306</v>
@@ -5525,7 +5580,7 @@
     </row>
     <row r="305" spans="1:3" ht="15.75">
       <c r="A305" s="15">
-        <v>1040019838</v>
+        <v>1040017266</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>307</v>
@@ -5536,7 +5591,7 @@
     </row>
     <row r="306" spans="1:3" ht="15.75">
       <c r="A306" s="15">
-        <v>1010042882</v>
+        <v>1010063326</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>308</v>
@@ -5547,7 +5602,7 @@
     </row>
     <row r="307" spans="1:3" ht="15.75">
       <c r="A307" s="15">
-        <v>1010042873</v>
+        <v>1010050574</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>309</v>
@@ -5557,8 +5612,8 @@
       </c>
     </row>
     <row r="308" spans="1:3" ht="15.75">
-      <c r="A308" s="15">
-        <v>1010026842</v>
+      <c r="A308" s="20">
+        <v>1010086126</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>310</v>
@@ -5569,7 +5624,7 @@
     </row>
     <row r="309" spans="1:3" ht="15.75">
       <c r="A309" s="15">
-        <v>1010026841</v>
+        <v>1040019838</v>
       </c>
       <c r="B309" s="5" t="s">
         <v>311</v>
@@ -5580,7 +5635,7 @@
     </row>
     <row r="310" spans="1:3" ht="15.75">
       <c r="A310" s="15">
-        <v>1010059549</v>
+        <v>1010042882</v>
       </c>
       <c r="B310" s="5" t="s">
         <v>312</v>
@@ -5591,7 +5646,7 @@
     </row>
     <row r="311" spans="1:3" ht="15.75">
       <c r="A311" s="15">
-        <v>1010020552</v>
+        <v>1010042873</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>313</v>
@@ -5602,7 +5657,7 @@
     </row>
     <row r="312" spans="1:3" ht="15.75">
       <c r="A312" s="15">
-        <v>1040078895</v>
+        <v>1010026842</v>
       </c>
       <c r="B312" s="5" t="s">
         <v>314</v>
@@ -5613,7 +5668,7 @@
     </row>
     <row r="313" spans="1:3" ht="15.75">
       <c r="A313" s="15">
-        <v>1040024309</v>
+        <v>1010026841</v>
       </c>
       <c r="B313" s="5" t="s">
         <v>315</v>
@@ -5624,7 +5679,7 @@
     </row>
     <row r="314" spans="1:3" ht="15.75">
       <c r="A314" s="15">
-        <v>1040024323</v>
+        <v>1010059549</v>
       </c>
       <c r="B314" s="5" t="s">
         <v>316</v>
@@ -5635,7 +5690,7 @@
     </row>
     <row r="315" spans="1:3" ht="15.75">
       <c r="A315" s="15">
-        <v>1040024322</v>
+        <v>1010020552</v>
       </c>
       <c r="B315" s="5" t="s">
         <v>317</v>
@@ -5646,7 +5701,7 @@
     </row>
     <row r="316" spans="1:3" ht="15.75">
       <c r="A316" s="15">
-        <v>1010087245</v>
+        <v>1040078895</v>
       </c>
       <c r="B316" s="5" t="s">
         <v>318</v>
@@ -5657,7 +5712,7 @@
     </row>
     <row r="317" spans="1:3" ht="15.75">
       <c r="A317" s="15">
-        <v>1010059685</v>
+        <v>1040024309</v>
       </c>
       <c r="B317" s="5" t="s">
         <v>319</v>
@@ -5668,7 +5723,7 @@
     </row>
     <row r="318" spans="1:3" ht="15.75">
       <c r="A318" s="15">
-        <v>1010059687</v>
+        <v>1040024323</v>
       </c>
       <c r="B318" s="5" t="s">
         <v>320</v>
@@ -5679,7 +5734,7 @@
     </row>
     <row r="319" spans="1:3" ht="15.75">
       <c r="A319" s="15">
-        <v>1010077469</v>
+        <v>1040024322</v>
       </c>
       <c r="B319" s="5" t="s">
         <v>321</v>
@@ -5689,8 +5744,8 @@
       </c>
     </row>
     <row r="320" spans="1:3" ht="15.75">
-      <c r="A320" s="19">
-        <v>1010077470</v>
+      <c r="A320" s="15">
+        <v>1010087245</v>
       </c>
       <c r="B320" s="5" t="s">
         <v>322</v>
@@ -5701,9 +5756,9 @@
     </row>
     <row r="321" spans="1:3" ht="15.75">
       <c r="A321" s="15">
-        <v>1010084519</v>
-      </c>
-      <c r="B321" s="7" t="s">
+        <v>1010059685</v>
+      </c>
+      <c r="B321" s="5" t="s">
         <v>323</v>
       </c>
       <c r="C321" s="4" t="s">
@@ -5711,8 +5766,8 @@
       </c>
     </row>
     <row r="322" spans="1:3" ht="15.75">
-      <c r="A322" s="14">
-        <v>1010084108</v>
+      <c r="A322" s="15">
+        <v>1010059687</v>
       </c>
       <c r="B322" s="5" t="s">
         <v>324</v>
@@ -5722,8 +5777,8 @@
       </c>
     </row>
     <row r="323" spans="1:3" ht="15.75">
-      <c r="A323" s="14">
-        <v>1010042884</v>
+      <c r="A323" s="15">
+        <v>1010077469</v>
       </c>
       <c r="B323" s="5" t="s">
         <v>325</v>
@@ -5733,8 +5788,8 @@
       </c>
     </row>
     <row r="324" spans="1:3" ht="15.75">
-      <c r="A324" s="15">
-        <v>1040043537</v>
+      <c r="A324" s="19">
+        <v>1010077470</v>
       </c>
       <c r="B324" s="5" t="s">
         <v>326</v>
@@ -5745,9 +5800,9 @@
     </row>
     <row r="325" spans="1:3" ht="15.75">
       <c r="A325" s="15">
-        <v>1010046401</v>
-      </c>
-      <c r="B325" s="5" t="s">
+        <v>1010084519</v>
+      </c>
+      <c r="B325" s="7" t="s">
         <v>327</v>
       </c>
       <c r="C325" s="4" t="s">
@@ -5755,8 +5810,8 @@
       </c>
     </row>
     <row r="326" spans="1:3" ht="15.75">
-      <c r="A326" s="15">
-        <v>1010062007</v>
+      <c r="A326" s="14">
+        <v>1010084108</v>
       </c>
       <c r="B326" s="5" t="s">
         <v>328</v>
@@ -5766,8 +5821,8 @@
       </c>
     </row>
     <row r="327" spans="1:3" ht="15.75">
-      <c r="A327" s="15">
-        <v>1010051284</v>
+      <c r="A327" s="14">
+        <v>1010042884</v>
       </c>
       <c r="B327" s="5" t="s">
         <v>329</v>
@@ -5777,8 +5832,8 @@
       </c>
     </row>
     <row r="328" spans="1:3" ht="15.75">
-      <c r="A328" s="15">
-        <v>1010027788</v>
+      <c r="A328" s="14">
+        <v>1010086877</v>
       </c>
       <c r="B328" s="5" t="s">
         <v>330</v>
@@ -5789,7 +5844,7 @@
     </row>
     <row r="329" spans="1:3" ht="15.75">
       <c r="A329" s="15">
-        <v>1010027786</v>
+        <v>1040043537</v>
       </c>
       <c r="B329" s="5" t="s">
         <v>331</v>
@@ -5800,7 +5855,7 @@
     </row>
     <row r="330" spans="1:3" ht="15.75">
       <c r="A330" s="15">
-        <v>1010026889</v>
+        <v>1010046401</v>
       </c>
       <c r="B330" s="5" t="s">
         <v>332</v>
@@ -5810,8 +5865,8 @@
       </c>
     </row>
     <row r="331" spans="1:3" ht="15.75">
-      <c r="A331" s="24">
-        <v>1010042358</v>
+      <c r="A331" s="15">
+        <v>1010062007</v>
       </c>
       <c r="B331" s="5" t="s">
         <v>333</v>
@@ -5822,7 +5877,7 @@
     </row>
     <row r="332" spans="1:3" ht="15.75">
       <c r="A332" s="15">
-        <v>1040023848</v>
+        <v>1010051284</v>
       </c>
       <c r="B332" s="5" t="s">
         <v>334</v>
@@ -5833,7 +5888,7 @@
     </row>
     <row r="333" spans="1:3" ht="15.75">
       <c r="A333" s="15">
-        <v>1010042341</v>
+        <v>1010027788</v>
       </c>
       <c r="B333" s="5" t="s">
         <v>335</v>
@@ -5844,7 +5899,7 @@
     </row>
     <row r="334" spans="1:3" ht="15.75">
       <c r="A334" s="15">
-        <v>1040023858</v>
+        <v>1010027786</v>
       </c>
       <c r="B334" s="5" t="s">
         <v>336</v>
@@ -5855,7 +5910,7 @@
     </row>
     <row r="335" spans="1:3" ht="15.75">
       <c r="A335" s="15">
-        <v>1040098396</v>
+        <v>1010026889</v>
       </c>
       <c r="B335" s="5" t="s">
         <v>337</v>
@@ -5865,8 +5920,8 @@
       </c>
     </row>
     <row r="336" spans="1:3" ht="15.75">
-      <c r="A336" s="15">
-        <v>1010087281</v>
+      <c r="A336" s="24">
+        <v>1010042358</v>
       </c>
       <c r="B336" s="5" t="s">
         <v>338</v>
@@ -5877,7 +5932,7 @@
     </row>
     <row r="337" spans="1:3" ht="15.75">
       <c r="A337" s="15">
-        <v>1040041006</v>
+        <v>1040023848</v>
       </c>
       <c r="B337" s="5" t="s">
         <v>339</v>
@@ -5888,7 +5943,7 @@
     </row>
     <row r="338" spans="1:3" ht="15.75">
       <c r="A338" s="15">
-        <v>1040101931</v>
+        <v>1010042341</v>
       </c>
       <c r="B338" s="5" t="s">
         <v>340</v>
@@ -5899,7 +5954,7 @@
     </row>
     <row r="339" spans="1:3" ht="15.75">
       <c r="A339" s="15">
-        <v>1040023843</v>
+        <v>1040023858</v>
       </c>
       <c r="B339" s="5" t="s">
         <v>341</v>
@@ -5910,7 +5965,7 @@
     </row>
     <row r="340" spans="1:3" ht="15.75">
       <c r="A340" s="15">
-        <v>1040077411</v>
+        <v>1040098396</v>
       </c>
       <c r="B340" s="5" t="s">
         <v>342</v>
@@ -5921,7 +5976,7 @@
     </row>
     <row r="341" spans="1:3" ht="15.75">
       <c r="A341" s="15">
-        <v>1040077410</v>
+        <v>1010087281</v>
       </c>
       <c r="B341" s="5" t="s">
         <v>343</v>
@@ -5932,7 +5987,7 @@
     </row>
     <row r="342" spans="1:3" ht="15.75">
       <c r="A342" s="15">
-        <v>1010062008</v>
+        <v>1040041006</v>
       </c>
       <c r="B342" s="5" t="s">
         <v>344</v>
@@ -5942,8 +5997,8 @@
       </c>
     </row>
     <row r="343" spans="1:3" ht="15.75">
-      <c r="A343" s="19">
-        <v>1040040960</v>
+      <c r="A343" s="15">
+        <v>1040101931</v>
       </c>
       <c r="B343" s="5" t="s">
         <v>345</v>
@@ -5954,9 +6009,9 @@
     </row>
     <row r="344" spans="1:3" ht="15.75">
       <c r="A344" s="15">
-        <v>1010031536</v>
-      </c>
-      <c r="B344" s="7" t="s">
+        <v>1040023843</v>
+      </c>
+      <c r="B344" s="5" t="s">
         <v>346</v>
       </c>
       <c r="C344" s="4" t="s">
@@ -5965,9 +6020,9 @@
     </row>
     <row r="345" spans="1:3" ht="15.75">
       <c r="A345" s="15">
-        <v>1010031545</v>
-      </c>
-      <c r="B345" s="7" t="s">
+        <v>1040077411</v>
+      </c>
+      <c r="B345" s="5" t="s">
         <v>347</v>
       </c>
       <c r="C345" s="4" t="s">
@@ -5975,8 +6030,8 @@
       </c>
     </row>
     <row r="346" spans="1:3" ht="15.75">
-      <c r="A346" s="30">
-        <v>1010084767</v>
+      <c r="A346" s="15">
+        <v>1040077410</v>
       </c>
       <c r="B346" s="5" t="s">
         <v>348</v>
@@ -5987,7 +6042,7 @@
     </row>
     <row r="347" spans="1:3" ht="15.75">
       <c r="A347" s="15">
-        <v>1040077360</v>
+        <v>1010062008</v>
       </c>
       <c r="B347" s="5" t="s">
         <v>349</v>
@@ -5997,8 +6052,8 @@
       </c>
     </row>
     <row r="348" spans="1:3" ht="15.75">
-      <c r="A348" s="15">
-        <v>1010064470</v>
+      <c r="A348" s="19">
+        <v>1040040960</v>
       </c>
       <c r="B348" s="5" t="s">
         <v>350</v>
@@ -6009,9 +6064,9 @@
     </row>
     <row r="349" spans="1:3" ht="15.75">
       <c r="A349" s="15">
-        <v>1010021991</v>
-      </c>
-      <c r="B349" s="5" t="s">
+        <v>1010031536</v>
+      </c>
+      <c r="B349" s="7" t="s">
         <v>351</v>
       </c>
       <c r="C349" s="4" t="s">
@@ -6020,9 +6075,9 @@
     </row>
     <row r="350" spans="1:3" ht="15.75">
       <c r="A350" s="15">
-        <v>1010021960</v>
-      </c>
-      <c r="B350" s="5" t="s">
+        <v>1010031545</v>
+      </c>
+      <c r="B350" s="7" t="s">
         <v>352</v>
       </c>
       <c r="C350" s="4" t="s">
@@ -6030,8 +6085,8 @@
       </c>
     </row>
     <row r="351" spans="1:3" ht="15.75">
-      <c r="A351" s="15">
-        <v>1010031690</v>
+      <c r="A351" s="30">
+        <v>1010084767</v>
       </c>
       <c r="B351" s="5" t="s">
         <v>353</v>
@@ -6042,7 +6097,7 @@
     </row>
     <row r="352" spans="1:3" ht="15.75">
       <c r="A352" s="15">
-        <v>1010022590</v>
+        <v>1040077360</v>
       </c>
       <c r="B352" s="5" t="s">
         <v>354</v>
@@ -6053,7 +6108,7 @@
     </row>
     <row r="353" spans="1:3" ht="15.75">
       <c r="A353" s="15">
-        <v>1040098643</v>
+        <v>1010064470</v>
       </c>
       <c r="B353" s="5" t="s">
         <v>355</v>
@@ -6064,7 +6119,7 @@
     </row>
     <row r="354" spans="1:3" ht="15.75">
       <c r="A354" s="15">
-        <v>1010086020</v>
+        <v>1010021991</v>
       </c>
       <c r="B354" s="5" t="s">
         <v>356</v>
@@ -6075,7 +6130,7 @@
     </row>
     <row r="355" spans="1:3" ht="15.75">
       <c r="A355" s="15">
-        <v>1010046550</v>
+        <v>1010021960</v>
       </c>
       <c r="B355" s="5" t="s">
         <v>357</v>
@@ -6086,7 +6141,7 @@
     </row>
     <row r="356" spans="1:3" ht="15.75">
       <c r="A356" s="15">
-        <v>1010046402</v>
+        <v>1010031690</v>
       </c>
       <c r="B356" s="5" t="s">
         <v>358</v>
@@ -6097,7 +6152,7 @@
     </row>
     <row r="357" spans="1:3" ht="15.75">
       <c r="A357" s="15">
-        <v>1010060291</v>
+        <v>1010022590</v>
       </c>
       <c r="B357" s="5" t="s">
         <v>359</v>
@@ -6108,7 +6163,7 @@
     </row>
     <row r="358" spans="1:3" ht="15.75">
       <c r="A358" s="15">
-        <v>1010050920</v>
+        <v>1040098643</v>
       </c>
       <c r="B358" s="5" t="s">
         <v>360</v>
@@ -6119,7 +6174,7 @@
     </row>
     <row r="359" spans="1:3" ht="15.75">
       <c r="A359" s="15">
-        <v>1040077412</v>
+        <v>1010086020</v>
       </c>
       <c r="B359" s="5" t="s">
         <v>361</v>
@@ -6130,7 +6185,7 @@
     </row>
     <row r="360" spans="1:3" ht="15.75">
       <c r="A360" s="15">
-        <v>1010042609</v>
+        <v>1010046550</v>
       </c>
       <c r="B360" s="5" t="s">
         <v>362</v>
@@ -6141,7 +6196,7 @@
     </row>
     <row r="361" spans="1:3" ht="15.75">
       <c r="A361" s="15">
-        <v>417701</v>
+        <v>1010046402</v>
       </c>
       <c r="B361" s="5" t="s">
         <v>363</v>
@@ -6152,7 +6207,7 @@
     </row>
     <row r="362" spans="1:3" ht="15.75">
       <c r="A362" s="15">
-        <v>399384</v>
+        <v>1010060291</v>
       </c>
       <c r="B362" s="5" t="s">
         <v>364</v>
@@ -6163,7 +6218,7 @@
     </row>
     <row r="363" spans="1:3" ht="15.75">
       <c r="A363" s="15">
-        <v>1010024086</v>
+        <v>1010050920</v>
       </c>
       <c r="B363" s="5" t="s">
         <v>365</v>
@@ -6174,7 +6229,7 @@
     </row>
     <row r="364" spans="1:3" ht="15.75">
       <c r="A364" s="15">
-        <v>1040077345</v>
+        <v>1040077412</v>
       </c>
       <c r="B364" s="5" t="s">
         <v>366</v>
@@ -6185,7 +6240,7 @@
     </row>
     <row r="365" spans="1:3" ht="15.75">
       <c r="A365" s="15">
-        <v>1040077368</v>
+        <v>1010042609</v>
       </c>
       <c r="B365" s="5" t="s">
         <v>367</v>
@@ -6196,7 +6251,7 @@
     </row>
     <row r="366" spans="1:3" ht="15.75">
       <c r="A366" s="15">
-        <v>399253</v>
+        <v>417701</v>
       </c>
       <c r="B366" s="5" t="s">
         <v>368</v>
@@ -6207,7 +6262,7 @@
     </row>
     <row r="367" spans="1:3" ht="15.75">
       <c r="A367" s="15">
-        <v>1010084317</v>
+        <v>399384</v>
       </c>
       <c r="B367" s="5" t="s">
         <v>369</v>
@@ -6217,8 +6272,8 @@
       </c>
     </row>
     <row r="368" spans="1:3" ht="15.75">
-      <c r="A368" s="25">
-        <v>1010085369</v>
+      <c r="A368" s="15">
+        <v>1010024086</v>
       </c>
       <c r="B368" s="5" t="s">
         <v>370</v>
@@ -6229,7 +6284,7 @@
     </row>
     <row r="369" spans="1:3" ht="15.75">
       <c r="A369" s="15">
-        <v>1010085370</v>
+        <v>1040077345</v>
       </c>
       <c r="B369" s="5" t="s">
         <v>371</v>
@@ -6240,7 +6295,7 @@
     </row>
     <row r="370" spans="1:3" ht="15.75">
       <c r="A370" s="15">
-        <v>1010085204</v>
+        <v>1040077368</v>
       </c>
       <c r="B370" s="5" t="s">
         <v>372</v>
@@ -6251,7 +6306,7 @@
     </row>
     <row r="371" spans="1:3" ht="15.75">
       <c r="A371" s="15">
-        <v>1010003966</v>
+        <v>399253</v>
       </c>
       <c r="B371" s="5" t="s">
         <v>373</v>
@@ -6262,7 +6317,7 @@
     </row>
     <row r="372" spans="1:3" ht="15.75">
       <c r="A372" s="15">
-        <v>1010003967</v>
+        <v>1010084317</v>
       </c>
       <c r="B372" s="5" t="s">
         <v>374</v>
@@ -6272,8 +6327,8 @@
       </c>
     </row>
     <row r="373" spans="1:3" ht="15.75">
-      <c r="A373" s="15">
-        <v>65219</v>
+      <c r="A373" s="25">
+        <v>1010085369</v>
       </c>
       <c r="B373" s="5" t="s">
         <v>375</v>
@@ -6284,7 +6339,7 @@
     </row>
     <row r="374" spans="1:3" ht="15.75">
       <c r="A374" s="15">
-        <v>10168</v>
+        <v>1010085370</v>
       </c>
       <c r="B374" s="5" t="s">
         <v>376</v>
@@ -6295,7 +6350,7 @@
     </row>
     <row r="375" spans="1:3" ht="15.75">
       <c r="A375" s="15">
-        <v>1010083792</v>
+        <v>1010085204</v>
       </c>
       <c r="B375" s="5" t="s">
         <v>377</v>
@@ -6306,7 +6361,7 @@
     </row>
     <row r="376" spans="1:3" ht="15.75">
       <c r="A376" s="15">
-        <v>1040077414</v>
+        <v>1010003966</v>
       </c>
       <c r="B376" s="5" t="s">
         <v>378</v>
@@ -6317,7 +6372,7 @@
     </row>
     <row r="377" spans="1:3" ht="15.75">
       <c r="A377" s="15">
-        <v>1010018482</v>
+        <v>1010003967</v>
       </c>
       <c r="B377" s="5" t="s">
         <v>379</v>
@@ -6328,7 +6383,7 @@
     </row>
     <row r="378" spans="1:3" ht="15.75">
       <c r="A378" s="15">
-        <v>1010084320</v>
+        <v>65219</v>
       </c>
       <c r="B378" s="5" t="s">
         <v>380</v>
@@ -6339,7 +6394,7 @@
     </row>
     <row r="379" spans="1:3" ht="15.75">
       <c r="A379" s="15">
-        <v>1010084532</v>
+        <v>10168</v>
       </c>
       <c r="B379" s="5" t="s">
         <v>381</v>
@@ -6350,7 +6405,7 @@
     </row>
     <row r="380" spans="1:3" ht="15.75">
       <c r="A380" s="15">
-        <v>1010027285</v>
+        <v>1010083792</v>
       </c>
       <c r="B380" s="5" t="s">
         <v>382</v>
@@ -6361,7 +6416,7 @@
     </row>
     <row r="381" spans="1:3" ht="15.75">
       <c r="A381" s="15">
-        <v>1040077413</v>
+        <v>1040077414</v>
       </c>
       <c r="B381" s="5" t="s">
         <v>383</v>
@@ -6372,7 +6427,7 @@
     </row>
     <row r="382" spans="1:3" ht="15.75">
       <c r="A382" s="15">
-        <v>1010085376</v>
+        <v>1010018482</v>
       </c>
       <c r="B382" s="5" t="s">
         <v>384</v>
@@ -6383,7 +6438,7 @@
     </row>
     <row r="383" spans="1:3" ht="15.75">
       <c r="A383" s="15">
-        <v>1010022819</v>
+        <v>1010084320</v>
       </c>
       <c r="B383" s="5" t="s">
         <v>385</v>
@@ -6394,7 +6449,7 @@
     </row>
     <row r="384" spans="1:3" ht="15.75">
       <c r="A384" s="15">
-        <v>1010052853</v>
+        <v>1010084532</v>
       </c>
       <c r="B384" s="5" t="s">
         <v>386</v>
@@ -6405,7 +6460,7 @@
     </row>
     <row r="385" spans="1:3" ht="15.75">
       <c r="A385" s="15">
-        <v>1010084377</v>
+        <v>1010027285</v>
       </c>
       <c r="B385" s="5" t="s">
         <v>387</v>
@@ -6415,1438 +6470,1494 @@
       </c>
     </row>
     <row r="386" spans="1:3" ht="15.75">
-      <c r="A386" s="26">
-        <v>1010062826</v>
+      <c r="A386" s="15">
+        <v>1040077413</v>
       </c>
       <c r="B386" s="5" t="s">
         <v>388</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>389</v>
+        <v>4</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="15.75">
       <c r="A387" s="15">
-        <v>1010002592</v>
+        <v>1010085376</v>
       </c>
       <c r="B387" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" ht="15.75">
+      <c r="A388" s="15">
+        <v>1010022819</v>
+      </c>
+      <c r="B388" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="C387" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" ht="15.75">
-      <c r="A388" s="24">
-        <v>1010001155</v>
-      </c>
-      <c r="B388" s="5" t="s">
-        <v>391</v>
-      </c>
       <c r="C388" s="4" t="s">
-        <v>389</v>
+        <v>4</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="15.75">
       <c r="A389" s="15">
-        <v>1010001062</v>
+        <v>1010052853</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>389</v>
+        <v>4</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="15.75">
       <c r="A390" s="15">
-        <v>1010084328</v>
-      </c>
-      <c r="B390" s="5" t="s">
+        <v>1010006162</v>
+      </c>
+      <c r="B390" s="34" t="s">
+        <v>392</v>
+      </c>
+      <c r="C390" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" ht="15.75">
+      <c r="A391" s="15">
+        <v>1010084377</v>
+      </c>
+      <c r="B391" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C390" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" ht="15.75">
-      <c r="A391" s="24">
-        <v>1010044502</v>
-      </c>
-      <c r="B391" s="5" t="s">
+      <c r="C391" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" ht="15.75">
+      <c r="A392" s="26">
+        <v>1010062826</v>
+      </c>
+      <c r="B392" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="C391" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="15.75">
-      <c r="A392" s="15">
-        <v>1010053692</v>
-      </c>
-      <c r="B392" s="5" t="s">
+      <c r="C392" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="C392" s="4" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="15.75">
       <c r="A393" s="15">
-        <v>1010083992</v>
+        <v>1010002592</v>
       </c>
       <c r="B393" s="5" t="s">
         <v>396</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="15.75">
-      <c r="A394" s="15">
-        <v>1010008578</v>
+      <c r="A394" s="24">
+        <v>1010001155</v>
       </c>
       <c r="B394" s="5" t="s">
         <v>397</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="15.75">
       <c r="A395" s="15">
-        <v>1010031694</v>
+        <v>1010001062</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="15.75">
       <c r="A396" s="15">
-        <v>1010051997</v>
+        <v>1010084328</v>
       </c>
       <c r="B396" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" ht="15.75">
+      <c r="A397" s="24">
+        <v>1010044502</v>
+      </c>
+      <c r="B397" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="C396" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" ht="15.75">
-      <c r="A397" s="15">
-        <v>1010022601</v>
-      </c>
-      <c r="B397" s="5" t="s">
-        <v>401</v>
-      </c>
       <c r="C397" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="15.75">
       <c r="A398" s="15">
-        <v>1010054278</v>
+        <v>1010053692</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="15.75">
       <c r="A399" s="15">
-        <v>1010083462</v>
+        <v>1010083992</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="15.75">
       <c r="A400" s="15">
-        <v>1010027772</v>
+        <v>1010008578</v>
       </c>
       <c r="B400" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C400" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="C400" s="4" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75">
       <c r="A401" s="15">
-        <v>1010084144</v>
+        <v>1010031694</v>
       </c>
       <c r="B401" s="5" t="s">
         <v>405</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="15.75">
-      <c r="A402" s="19">
-        <v>1010084958</v>
-      </c>
-      <c r="B402" s="7" t="s">
+      <c r="A402" s="15">
+        <v>1010051997</v>
+      </c>
+      <c r="B402" s="5" t="s">
         <v>406</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="15.75">
-      <c r="A403" s="19">
-        <v>1010084720</v>
-      </c>
-      <c r="B403" s="7" t="s">
+      <c r="A403" s="15">
+        <v>1010022601</v>
+      </c>
+      <c r="B403" s="5" t="s">
         <v>407</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="D403" s="29"/>
+        <v>404</v>
+      </c>
     </row>
     <row r="404" spans="1:4" ht="15.75">
-      <c r="A404" s="18">
-        <v>1010021956</v>
-      </c>
-      <c r="B404" s="7" t="s">
+      <c r="A404" s="15">
+        <v>1010054278</v>
+      </c>
+      <c r="B404" s="5" t="s">
         <v>408</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="15.75">
-      <c r="A405" s="18">
-        <v>1010026464</v>
-      </c>
-      <c r="B405" s="7" t="s">
+      <c r="A405" s="15">
+        <v>1010083462</v>
+      </c>
+      <c r="B405" s="5" t="s">
         <v>409</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="15.75">
-      <c r="A406" s="14">
-        <v>1010021957</v>
+      <c r="A406" s="15">
+        <v>1010027772</v>
       </c>
       <c r="B406" s="5" t="s">
         <v>410</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="15.75">
       <c r="A407" s="15">
-        <v>1010026462</v>
+        <v>1010084144</v>
       </c>
       <c r="B407" s="5" t="s">
         <v>411</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="15.75">
-      <c r="A408" s="15">
-        <v>1010026551</v>
-      </c>
-      <c r="B408" s="5" t="s">
+      <c r="A408" s="19">
+        <v>1010084958</v>
+      </c>
+      <c r="B408" s="7" t="s">
         <v>412</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="15.75">
-      <c r="A409" s="15">
-        <v>1010042554</v>
-      </c>
-      <c r="B409" s="5" t="s">
+      <c r="A409" s="19">
+        <v>1010084720</v>
+      </c>
+      <c r="B409" s="7" t="s">
         <v>413</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>398</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="D409" s="29"/>
     </row>
     <row r="410" spans="1:4" ht="15.75">
-      <c r="A410" s="15">
-        <v>1010039904</v>
-      </c>
-      <c r="B410" s="5" t="s">
+      <c r="A410" s="18">
+        <v>1010021956</v>
+      </c>
+      <c r="B410" s="7" t="s">
         <v>414</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="15.75">
-      <c r="A411" s="15">
-        <v>1010060205</v>
-      </c>
-      <c r="B411" s="5" t="s">
+      <c r="A411" s="18">
+        <v>1010026464</v>
+      </c>
+      <c r="B411" s="7" t="s">
         <v>415</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="15.75">
-      <c r="A412" s="15">
-        <v>1010060206</v>
+      <c r="A412" s="14">
+        <v>1010021957</v>
       </c>
       <c r="B412" s="5" t="s">
         <v>416</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="413" spans="1:4" ht="15.75">
       <c r="A413" s="15">
-        <v>1010077431</v>
+        <v>1010026462</v>
       </c>
       <c r="B413" s="5" t="s">
         <v>417</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="15.75">
       <c r="A414" s="15">
-        <v>1010077503</v>
+        <v>1010026551</v>
       </c>
       <c r="B414" s="5" t="s">
         <v>418</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="415" spans="1:4" ht="15.75">
       <c r="A415" s="15">
-        <v>1010084187</v>
+        <v>1010042554</v>
       </c>
       <c r="B415" s="5" t="s">
         <v>419</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="416" spans="1:4" ht="15.75">
       <c r="A416" s="15">
-        <v>1010080958</v>
+        <v>1010039904</v>
       </c>
       <c r="B416" s="5" t="s">
         <v>420</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15.75">
       <c r="A417" s="15">
-        <v>1010026032</v>
+        <v>1010060205</v>
       </c>
       <c r="B417" s="5" t="s">
         <v>421</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="15.75">
       <c r="A418" s="15">
-        <v>1010085384</v>
+        <v>1010060206</v>
       </c>
       <c r="B418" s="5" t="s">
         <v>422</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15.75">
       <c r="A419" s="15">
-        <v>1010006347</v>
+        <v>1010077431</v>
       </c>
       <c r="B419" s="5" t="s">
         <v>423</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="15.75">
       <c r="A420" s="15">
-        <v>1010085179</v>
+        <v>1010077503</v>
       </c>
       <c r="B420" s="5" t="s">
         <v>424</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15.75">
       <c r="A421" s="15">
-        <v>1010024158</v>
-      </c>
-      <c r="B421" s="8" t="s">
+        <v>1010084187</v>
+      </c>
+      <c r="B421" s="5" t="s">
         <v>425</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="15.75">
       <c r="A422" s="15">
-        <v>1010024131</v>
-      </c>
-      <c r="B422" s="8" t="s">
+        <v>1010080958</v>
+      </c>
+      <c r="B422" s="5" t="s">
         <v>426</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15.75">
       <c r="A423" s="15">
-        <v>1010007160</v>
+        <v>1010026032</v>
       </c>
       <c r="B423" s="5" t="s">
         <v>427</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15.75">
       <c r="A424" s="15">
-        <v>1010023642</v>
+        <v>1010085384</v>
       </c>
       <c r="B424" s="5" t="s">
         <v>428</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="15.75">
       <c r="A425" s="15">
-        <v>1010007193</v>
-      </c>
-      <c r="B425" s="6" t="s">
+        <v>1010006347</v>
+      </c>
+      <c r="B425" s="5" t="s">
         <v>429</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15.75">
       <c r="A426" s="15">
-        <v>1010042637</v>
+        <v>1010085179</v>
       </c>
       <c r="B426" s="5" t="s">
         <v>430</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="15.75">
       <c r="A427" s="15">
-        <v>1040075323</v>
-      </c>
-      <c r="B427" s="5" t="s">
+        <v>1010024158</v>
+      </c>
+      <c r="B427" s="8" t="s">
         <v>431</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="15.75">
       <c r="A428" s="15">
-        <v>1040075324</v>
+        <v>1010024131</v>
       </c>
       <c r="B428" s="8" t="s">
         <v>432</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="15.75">
-      <c r="A429" s="27">
+      <c r="A429" s="15">
+        <v>1010007160</v>
+      </c>
+      <c r="B429" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C429" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" ht="15.75">
+      <c r="A430" s="15">
+        <v>1010023642</v>
+      </c>
+      <c r="B430" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="C430" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="15.75">
+      <c r="A431" s="15">
+        <v>1010007193</v>
+      </c>
+      <c r="B431" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="15.75">
+      <c r="A432" s="15">
+        <v>1010042637</v>
+      </c>
+      <c r="B432" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C432" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" ht="15.75">
+      <c r="A433" s="15">
+        <v>1040075323</v>
+      </c>
+      <c r="B433" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" ht="15.75">
+      <c r="A434" s="15">
+        <v>1040075324</v>
+      </c>
+      <c r="B434" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" ht="15.75">
+      <c r="A435" s="27">
         <v>1040074827</v>
       </c>
-      <c r="B429" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="C429" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" ht="15.75">
-      <c r="A430" s="27">
+      <c r="B435" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="C435" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" ht="15.75">
+      <c r="A436" s="27">
         <v>1040099488</v>
       </c>
-      <c r="B430" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="C430" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" ht="15.75">
-      <c r="A431" s="27">
+      <c r="B436" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="C436" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" ht="15.75">
+      <c r="A437" s="27">
         <v>1040083312</v>
       </c>
-      <c r="B431" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="C431" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="15.75">
-      <c r="A432" s="27">
+      <c r="B437" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C437" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" ht="15.75">
+      <c r="A438" s="27">
         <v>1040077661</v>
       </c>
-      <c r="B432" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="C432" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="15.75">
-      <c r="A433" s="27">
+      <c r="B438" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" ht="15.75">
+      <c r="A439" s="27">
         <v>1010085180</v>
       </c>
-      <c r="B433" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="C433" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" ht="15.75">
-      <c r="A434" s="14">
+      <c r="B439" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="C439" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" ht="15.75">
+      <c r="A440" s="14">
         <v>1040017489</v>
       </c>
-      <c r="B434" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="15.75">
-      <c r="A435" s="14">
+      <c r="B440" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="C440" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" ht="15.75">
+      <c r="A441" s="14">
         <v>1010085181</v>
-      </c>
-      <c r="B435" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="C435" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" ht="15.75">
-      <c r="A436" s="15">
-        <v>400175</v>
-      </c>
-      <c r="B436" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="C436" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" ht="15.75">
-      <c r="A437" s="15">
-        <v>1040017505</v>
-      </c>
-      <c r="B437" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="C437" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" ht="15.75">
-      <c r="A438" s="15">
-        <v>1040017503</v>
-      </c>
-      <c r="B438" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="C438" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" ht="15.75">
-      <c r="A439" s="15">
-        <v>1010046445</v>
-      </c>
-      <c r="B439" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="C439" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" ht="15.75">
-      <c r="A440" s="15">
-        <v>1010021033</v>
-      </c>
-      <c r="B440" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C440" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" ht="15.75">
-      <c r="A441" s="15">
-        <v>1010057142</v>
       </c>
       <c r="B441" s="5" t="s">
         <v>445</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="15.75">
       <c r="A442" s="15">
-        <v>1010016356</v>
+        <v>400175</v>
       </c>
       <c r="B442" s="5" t="s">
         <v>446</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="15.75">
       <c r="A443" s="15">
-        <v>1010084363</v>
+        <v>1040017505</v>
       </c>
       <c r="B443" s="5" t="s">
         <v>447</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="15.75">
       <c r="A444" s="15">
-        <v>1010052021</v>
+        <v>1040017503</v>
       </c>
       <c r="B444" s="5" t="s">
         <v>448</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="15.75">
       <c r="A445" s="15">
-        <v>1040091721</v>
+        <v>1010046445</v>
       </c>
       <c r="B445" s="5" t="s">
         <v>449</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="15.75">
       <c r="A446" s="15">
-        <v>1010062022</v>
+        <v>1010021033</v>
       </c>
       <c r="B446" s="5" t="s">
         <v>450</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="15.75">
       <c r="A447" s="15">
-        <v>18336</v>
+        <v>1010057142</v>
       </c>
       <c r="B447" s="5" t="s">
         <v>451</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="15.75">
       <c r="A448" s="15">
-        <v>229205</v>
+        <v>1010016356</v>
       </c>
       <c r="B448" s="5" t="s">
         <v>452</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="15.75">
       <c r="A449" s="15">
-        <v>60671</v>
+        <v>1010084363</v>
       </c>
       <c r="B449" s="5" t="s">
         <v>453</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="15.75">
       <c r="A450" s="15">
-        <v>1010059726</v>
+        <v>1010052021</v>
       </c>
       <c r="B450" s="5" t="s">
         <v>454</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="15.75">
       <c r="A451" s="15">
-        <v>1010008144</v>
+        <v>1040091721</v>
       </c>
       <c r="B451" s="5" t="s">
         <v>455</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="15.75">
       <c r="A452" s="15">
-        <v>1010007244</v>
+        <v>1010062022</v>
       </c>
       <c r="B452" s="5" t="s">
         <v>456</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="15.75">
       <c r="A453" s="15">
-        <v>1010006827</v>
+        <v>18336</v>
       </c>
       <c r="B453" s="5" t="s">
         <v>457</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="15.75">
       <c r="A454" s="15">
-        <v>1040075426</v>
+        <v>229205</v>
       </c>
       <c r="B454" s="5" t="s">
         <v>458</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="15.75">
       <c r="A455" s="15">
-        <v>1040075427</v>
+        <v>60671</v>
       </c>
       <c r="B455" s="5" t="s">
         <v>459</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="15.75">
       <c r="A456" s="15">
-        <v>1010084313</v>
+        <v>1010059726</v>
       </c>
       <c r="B456" s="5" t="s">
         <v>460</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="15.75">
       <c r="A457" s="15">
-        <v>403459</v>
+        <v>1010008144</v>
       </c>
       <c r="B457" s="5" t="s">
         <v>461</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="15.75">
       <c r="A458" s="15">
-        <v>1010044828</v>
+        <v>1010007244</v>
       </c>
       <c r="B458" s="5" t="s">
         <v>462</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="15.75">
       <c r="A459" s="15">
-        <v>1010026973</v>
+        <v>1010006827</v>
       </c>
       <c r="B459" s="5" t="s">
         <v>463</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="15.75">
       <c r="A460" s="15">
-        <v>1040017204</v>
+        <v>1040075426</v>
       </c>
       <c r="B460" s="5" t="s">
         <v>464</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="15.75">
-      <c r="A461" s="24">
-        <v>1010022119</v>
-      </c>
-      <c r="B461" s="6" t="s">
+      <c r="A461" s="15">
+        <v>1040075427</v>
+      </c>
+      <c r="B461" s="5" t="s">
         <v>465</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>466</v>
+        <v>404</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="15.75">
       <c r="A462" s="15">
-        <v>1010058709</v>
+        <v>1010084313</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>466</v>
+        <v>404</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="15.75">
       <c r="A463" s="15">
-        <v>1010025711</v>
+        <v>403459</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>466</v>
+        <v>404</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="15.75">
       <c r="A464" s="15">
-        <v>1010059684</v>
+        <v>1010044828</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>466</v>
+        <v>404</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="15.75">
       <c r="A465" s="15">
-        <v>427341</v>
+        <v>1010026973</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>466</v>
+        <v>404</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="15.75">
       <c r="A466" s="15">
-        <v>392696</v>
+        <v>1040017204</v>
       </c>
       <c r="B466" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C466" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="15.75">
+      <c r="A467" s="24">
+        <v>1010022119</v>
+      </c>
+      <c r="B467" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="C466" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" ht="15.75">
-      <c r="A467" s="15">
-        <v>1010085279</v>
-      </c>
-      <c r="B467" s="5" t="s">
+      <c r="C467" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="C467" s="4" t="s">
-        <v>466</v>
-      </c>
     </row>
     <row r="468" spans="1:3" ht="15.75">
-      <c r="A468" s="19">
-        <v>1010022588</v>
+      <c r="A468" s="14">
+        <v>1010084591</v>
       </c>
       <c r="B468" s="5" t="s">
         <v>473</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="15.75">
       <c r="A469" s="15">
-        <v>1010026864</v>
-      </c>
-      <c r="B469" s="7" t="s">
+        <v>1010058709</v>
+      </c>
+      <c r="B469" s="5" t="s">
         <v>474</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="15.75">
-      <c r="A470" s="14">
-        <v>1010030946</v>
-      </c>
-      <c r="B470" s="7" t="s">
+      <c r="A470" s="15">
+        <v>1010025711</v>
+      </c>
+      <c r="B470" s="5" t="s">
         <v>475</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="15.75">
-      <c r="A471" s="14">
-        <v>1010022589</v>
+      <c r="A471" s="15">
+        <v>1010059684</v>
       </c>
       <c r="B471" s="5" t="s">
         <v>476</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="15.75">
       <c r="A472" s="15">
-        <v>1040090143</v>
+        <v>427341</v>
       </c>
       <c r="B472" s="5" t="s">
         <v>477</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="15.75">
       <c r="A473" s="15">
-        <v>1040090138</v>
+        <v>392696</v>
       </c>
       <c r="B473" s="5" t="s">
         <v>478</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="15.75">
       <c r="A474" s="15">
-        <v>1030001314</v>
+        <v>1010085279</v>
       </c>
       <c r="B474" s="5" t="s">
         <v>479</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="15.75">
-      <c r="A475" s="15">
-        <v>1010052319</v>
+      <c r="A475" s="19">
+        <v>1010022588</v>
       </c>
       <c r="B475" s="5" t="s">
         <v>480</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15.75">
       <c r="A476" s="15">
-        <v>1010052320</v>
-      </c>
-      <c r="B476" s="5" t="s">
+        <v>1010026864</v>
+      </c>
+      <c r="B476" s="7" t="s">
         <v>481</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="15.75">
-      <c r="A477" s="15">
-        <v>1030000370</v>
-      </c>
-      <c r="B477" s="5" t="s">
+      <c r="A477" s="14">
+        <v>1010030946</v>
+      </c>
+      <c r="B477" s="7" t="s">
         <v>482</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15.75">
-      <c r="A478" s="15">
-        <v>1030000366</v>
+      <c r="A478" s="14">
+        <v>1010022589</v>
       </c>
       <c r="B478" s="5" t="s">
         <v>483</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="15.75">
       <c r="A479" s="15">
-        <v>1030000368</v>
+        <v>1040090143</v>
       </c>
       <c r="B479" s="5" t="s">
         <v>484</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15.75">
       <c r="A480" s="15">
-        <v>1030000369</v>
+        <v>1040090138</v>
       </c>
       <c r="B480" s="5" t="s">
         <v>485</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="15.75">
       <c r="A481" s="15">
-        <v>1030000489</v>
+        <v>1030001314</v>
       </c>
       <c r="B481" s="5" t="s">
         <v>486</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="15.75">
       <c r="A482" s="15">
-        <v>1030000490</v>
+        <v>1010052319</v>
       </c>
       <c r="B482" s="5" t="s">
         <v>487</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="15.75">
       <c r="A483" s="15">
-        <v>1030000821</v>
+        <v>1010052320</v>
       </c>
       <c r="B483" s="5" t="s">
         <v>488</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="15.75">
       <c r="A484" s="15">
-        <v>1030000511</v>
-      </c>
-      <c r="B484" s="8" t="s">
+        <v>1030000370</v>
+      </c>
+      <c r="B484" s="5" t="s">
         <v>489</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="15.75">
-      <c r="A485" s="16">
-        <v>1010084279</v>
-      </c>
-      <c r="B485" s="8" t="s">
+      <c r="A485" s="15">
+        <v>1030000366</v>
+      </c>
+      <c r="B485" s="5" t="s">
         <v>490</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="15.75">
-      <c r="A486" s="16">
-        <v>1010004281</v>
+      <c r="A486" s="15">
+        <v>1030000368</v>
       </c>
       <c r="B486" s="5" t="s">
         <v>491</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="15.75">
       <c r="A487" s="15">
-        <v>1010022118</v>
-      </c>
-      <c r="B487" s="9" t="s">
+        <v>1030000369</v>
+      </c>
+      <c r="B487" s="5" t="s">
         <v>492</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="15.75">
       <c r="A488" s="15">
-        <v>1010028657</v>
+        <v>1030000489</v>
       </c>
       <c r="B488" s="5" t="s">
         <v>493</v>
       </c>
       <c r="C488" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" ht="15.75">
+      <c r="A489" s="15">
+        <v>1030000490</v>
+      </c>
+      <c r="B489" s="5" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="489" spans="1:3" ht="15.75">
-      <c r="A489" s="18">
-        <v>1010028655</v>
-      </c>
-      <c r="B489" s="5" t="s">
+      <c r="C489" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" ht="15.75">
+      <c r="A490" s="15">
+        <v>1030000821</v>
+      </c>
+      <c r="B490" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="C489" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" ht="15.75">
-      <c r="A490" s="18">
-        <v>145165</v>
-      </c>
-      <c r="B490" s="5" t="s">
-        <v>496</v>
-      </c>
       <c r="C490" s="4" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="15.75">
       <c r="A491" s="15">
-        <v>51666</v>
-      </c>
-      <c r="B491" s="5" t="s">
+        <v>1030000511</v>
+      </c>
+      <c r="B491" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C491" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" ht="15.75">
+      <c r="A492" s="16">
+        <v>1010084279</v>
+      </c>
+      <c r="B492" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="C491" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" ht="15.75">
-      <c r="A492" s="18">
-        <v>1010080930</v>
-      </c>
-      <c r="B492" s="5" t="s">
+      <c r="C492" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" ht="15.75">
+      <c r="A493" s="16">
+        <v>1010004281</v>
+      </c>
+      <c r="B493" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="C492" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" ht="15.75">
-      <c r="A493" s="15">
-        <v>161055</v>
-      </c>
-      <c r="B493" s="5" t="s">
-        <v>499</v>
-      </c>
       <c r="C493" s="4" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="15.75">
       <c r="A494" s="15">
-        <v>1010050517</v>
-      </c>
-      <c r="B494" s="5" t="s">
-        <v>500</v>
+        <v>1010022118</v>
+      </c>
+      <c r="B494" s="9" t="s">
+        <v>499</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="15.75">
       <c r="A495" s="15">
-        <v>1010084190</v>
+        <v>1010028657</v>
       </c>
       <c r="B495" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C495" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="C495" s="4" t="s">
-        <v>494</v>
-      </c>
     </row>
     <row r="496" spans="1:3" ht="15.75">
-      <c r="A496" s="15">
-        <v>1010084195</v>
+      <c r="A496" s="18">
+        <v>1010028655</v>
       </c>
       <c r="B496" s="5" t="s">
         <v>502</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="15.75">
-      <c r="A497" s="15">
-        <v>1010001400</v>
+      <c r="A497" s="18">
+        <v>145165</v>
       </c>
       <c r="B497" s="5" t="s">
         <v>503</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="15.75">
-      <c r="A498" s="17">
-        <v>1010008416</v>
+      <c r="A498" s="15">
+        <v>51666</v>
       </c>
       <c r="B498" s="5" t="s">
         <v>504</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="15.75">
-      <c r="A499" s="28">
-        <v>1010018372</v>
+      <c r="A499" s="18">
+        <v>1010080930</v>
       </c>
       <c r="B499" s="5" t="s">
         <v>505</v>
       </c>
       <c r="C499" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="15.75">
-      <c r="A500" s="28">
-        <v>1010018361</v>
-      </c>
-      <c r="B500" s="8" t="s">
+      <c r="A500" s="15">
+        <v>161055</v>
+      </c>
+      <c r="B500" s="5" t="s">
         <v>506</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="15.75">
-      <c r="A501" s="16">
-        <v>1010055398</v>
-      </c>
-      <c r="B501" s="11" t="s">
+      <c r="A501" s="15">
+        <v>1010050517</v>
+      </c>
+      <c r="B501" s="5" t="s">
         <v>507</v>
       </c>
       <c r="C501" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="15.75">
       <c r="A502" s="15">
-        <v>422131</v>
+        <v>1010084190</v>
       </c>
       <c r="B502" s="5" t="s">
         <v>508</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="15.75">
       <c r="A503" s="15">
-        <v>1010084370</v>
+        <v>1010084195</v>
       </c>
       <c r="B503" s="5" t="s">
         <v>509</v>
       </c>
       <c r="C503" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="15.75">
       <c r="A504" s="15">
-        <v>422759</v>
+        <v>1010001400</v>
       </c>
       <c r="B504" s="5" t="s">
         <v>510</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="15.75">
-      <c r="A505" s="15">
-        <v>120955</v>
+      <c r="A505" s="17">
+        <v>1010008416</v>
       </c>
       <c r="B505" s="5" t="s">
         <v>511</v>
       </c>
       <c r="C505" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="15.75">
-      <c r="A506" s="15">
-        <v>1010000896</v>
+      <c r="A506" s="28">
+        <v>1010018372</v>
       </c>
       <c r="B506" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="C506" s="13" t="s">
-        <v>494</v>
+      <c r="C506" s="4" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="15.75">
-      <c r="A507" s="15">
+      <c r="A507" s="28">
+        <v>1010018361</v>
+      </c>
+      <c r="B507" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C507" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" ht="15.75">
+      <c r="A508" s="16">
+        <v>1010055398</v>
+      </c>
+      <c r="B508" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="C508" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" ht="15.75">
+      <c r="A509" s="15">
+        <v>422131</v>
+      </c>
+      <c r="B509" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C509" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" ht="15.75">
+      <c r="A510" s="15">
+        <v>1010084370</v>
+      </c>
+      <c r="B510" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="C510" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" ht="15.75">
+      <c r="A511" s="15">
+        <v>422759</v>
+      </c>
+      <c r="B511" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="C511" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" ht="15.75">
+      <c r="A512" s="15">
+        <v>120955</v>
+      </c>
+      <c r="B512" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="C512" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" ht="15.75">
+      <c r="A513" s="15">
+        <v>1010000896</v>
+      </c>
+      <c r="B513" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="C513" s="13" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" ht="15.75">
+      <c r="A514" s="15">
         <v>1010084308</v>
       </c>
-      <c r="B507" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="C507" s="13" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" ht="15.75">
-      <c r="A508" s="15">
+      <c r="B514" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C514" s="13" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" ht="15.75">
+      <c r="A515" s="19">
         <v>1010084035</v>
       </c>
-      <c r="B508" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="C508" s="13" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" ht="15.75">
-      <c r="A509" s="2"/>
-      <c r="B509" s="2"/>
-    </row>
-    <row r="510" spans="1:3" ht="15.75">
-      <c r="A510" s="2"/>
-      <c r="B510" s="2"/>
-    </row>
-    <row r="511" spans="1:3" ht="15.75">
-      <c r="A511" s="2"/>
-      <c r="B511" s="2"/>
-    </row>
-    <row r="512" spans="1:3" ht="15.75">
-      <c r="A512" s="2"/>
-      <c r="B512" s="2"/>
-    </row>
-    <row r="513" spans="1:2" ht="15.75">
-      <c r="A513" s="2"/>
-      <c r="B513" s="2"/>
-    </row>
-    <row r="514" spans="1:2" ht="15.75">
-      <c r="A514" s="2"/>
-      <c r="B514" s="2"/>
-    </row>
-    <row r="515" spans="1:2" ht="15.75">
-      <c r="A515" s="2"/>
-      <c r="B515" s="2"/>
-    </row>
-    <row r="516" spans="1:2" ht="15.75">
-      <c r="A516" s="2"/>
-      <c r="B516" s="2"/>
-    </row>
-    <row r="517" spans="1:2" ht="15.75">
+      <c r="B515" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="C515" s="31" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" ht="15.75">
+      <c r="A516" s="4">
+        <v>1010029427</v>
+      </c>
+      <c r="B516" s="32" t="s">
+        <v>522</v>
+      </c>
+      <c r="C516" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" ht="15.75">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
     </row>
-    <row r="518" spans="1:2" ht="15.75">
+    <row r="518" spans="1:3" ht="15.75">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
     </row>
-    <row r="519" spans="1:2" ht="15.75">
+    <row r="519" spans="1:3" ht="15.75">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
     </row>
-    <row r="520" spans="1:2" ht="15.75">
+    <row r="520" spans="1:3" ht="15.75">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
     </row>
-    <row r="521" spans="1:2" ht="15.75">
+    <row r="521" spans="1:3" ht="15.75">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
     </row>
-    <row r="522" spans="1:2" ht="15.75">
+    <row r="522" spans="1:3" ht="15.75">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
     </row>
-    <row r="523" spans="1:2" ht="15.75">
+    <row r="523" spans="1:3" ht="15.75">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
     </row>
-    <row r="524" spans="1:2" ht="15.75">
+    <row r="524" spans="1:3" ht="15.75">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
     </row>
-    <row r="525" spans="1:2" ht="15.75">
+    <row r="525" spans="1:3" ht="15.75">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
     </row>
-    <row r="526" spans="1:2" ht="15.75">
+    <row r="526" spans="1:3" ht="15.75">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
     </row>
-    <row r="527" spans="1:2" ht="15.75">
+    <row r="527" spans="1:3" ht="15.75">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
     </row>
-    <row r="528" spans="1:2" ht="15.75">
+    <row r="528" spans="1:3" ht="15.75">
       <c r="A528" s="2"/>
-      <c r="B528" s="2"/>
+      <c r="B528" s="33"/>
     </row>
     <row r="529" spans="1:2" ht="15.75">
       <c r="A529" s="2"/>
@@ -9526,31 +9637,31 @@
     </row>
     <row r="948" spans="1:2" ht="15.75">
       <c r="A948" s="2"/>
-      <c r="B948" s="1"/>
+      <c r="B948" s="2"/>
     </row>
     <row r="949" spans="1:2" ht="15.75">
       <c r="A949" s="2"/>
-      <c r="B949" s="1"/>
+      <c r="B949" s="2"/>
     </row>
     <row r="950" spans="1:2" ht="15.75">
       <c r="A950" s="2"/>
-      <c r="B950" s="1"/>
+      <c r="B950" s="2"/>
     </row>
     <row r="951" spans="1:2" ht="15.75">
       <c r="A951" s="2"/>
-      <c r="B951" s="1"/>
+      <c r="B951" s="2"/>
     </row>
     <row r="952" spans="1:2" ht="15.75">
       <c r="A952" s="2"/>
-      <c r="B952" s="1"/>
+      <c r="B952" s="2"/>
     </row>
     <row r="953" spans="1:2" ht="15.75">
       <c r="A953" s="2"/>
-      <c r="B953" s="1"/>
+      <c r="B953" s="2"/>
     </row>
     <row r="954" spans="1:2" ht="15.75">
       <c r="A954" s="2"/>
-      <c r="B954" s="1"/>
+      <c r="B954" s="2"/>
     </row>
     <row r="955" spans="1:2" ht="15.75">
       <c r="A955" s="2"/>
@@ -9797,31 +9908,31 @@
       <c r="B1015" s="1"/>
     </row>
     <row r="1016" spans="1:2" ht="15.75">
-      <c r="A1016" s="1"/>
+      <c r="A1016" s="2"/>
       <c r="B1016" s="1"/>
     </row>
     <row r="1017" spans="1:2" ht="15.75">
-      <c r="A1017" s="1"/>
+      <c r="A1017" s="2"/>
       <c r="B1017" s="1"/>
     </row>
     <row r="1018" spans="1:2" ht="15.75">
-      <c r="A1018" s="1"/>
+      <c r="A1018" s="2"/>
       <c r="B1018" s="1"/>
     </row>
     <row r="1019" spans="1:2" ht="15.75">
-      <c r="A1019" s="1"/>
+      <c r="A1019" s="2"/>
       <c r="B1019" s="1"/>
     </row>
     <row r="1020" spans="1:2" ht="15.75">
-      <c r="A1020" s="1"/>
+      <c r="A1020" s="2"/>
       <c r="B1020" s="1"/>
     </row>
     <row r="1021" spans="1:2" ht="15.75">
-      <c r="A1021" s="1"/>
+      <c r="A1021" s="2"/>
       <c r="B1021" s="1"/>
     </row>
     <row r="1022" spans="1:2" ht="15.75">
-      <c r="A1022" s="1"/>
+      <c r="A1022" s="2"/>
       <c r="B1022" s="1"/>
     </row>
     <row r="1023" spans="1:2" ht="15.75">
@@ -10575,6 +10686,34 @@
     <row r="1210" spans="1:2" ht="15.75">
       <c r="A1210" s="1"/>
       <c r="B1210" s="1"/>
+    </row>
+    <row r="1211" spans="1:2" ht="15.75">
+      <c r="A1211" s="1"/>
+      <c r="B1211" s="1"/>
+    </row>
+    <row r="1212" spans="1:2" ht="15.75">
+      <c r="A1212" s="1"/>
+      <c r="B1212" s="1"/>
+    </row>
+    <row r="1213" spans="1:2" ht="15.75">
+      <c r="A1213" s="1"/>
+      <c r="B1213" s="1"/>
+    </row>
+    <row r="1214" spans="1:2" ht="15.75">
+      <c r="A1214" s="1"/>
+      <c r="B1214" s="1"/>
+    </row>
+    <row r="1215" spans="1:2" ht="15.75">
+      <c r="A1215" s="1"/>
+      <c r="B1215" s="1"/>
+    </row>
+    <row r="1216" spans="1:2" ht="15.75">
+      <c r="A1216" s="1"/>
+      <c r="B1216" s="1"/>
+    </row>
+    <row r="1217" spans="1:2" ht="15.75">
+      <c r="A1217" s="1"/>
+      <c r="B1217" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10603,22 +10742,22 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="332" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D8165A2-D382-4E56-AC07-AD791523EB0C}"/>
+  <xr:revisionPtr revIDLastSave="335" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEDDAD3F-D55D-4BEB-B6A5-373E8902257D}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="383" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C2016AA-C216-412C-BAB3-E96A8FBBC600}"/>
+  <xr:revisionPtr revIDLastSave="404" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16A9AE3A-6F3E-4BA1-B9F6-2B8EB8687FB9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294903033" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="528">
   <si>
     <t>material</t>
   </si>
@@ -52,12 +52,15 @@
     <t>categoria</t>
   </si>
   <si>
+    <t>ABRAÇADEIRA</t>
+  </si>
+  <si>
+    <t>Mecânica</t>
+  </si>
+  <si>
     <t>ABRAÇADEIRA PARALAMA VOLVO</t>
   </si>
   <si>
-    <t>Mecânica</t>
-  </si>
-  <si>
     <t>ACABAMENTO/MOLDURA PARALAMA LD</t>
   </si>
   <si>
@@ -67,97 +70,178 @@
     <t>ADAPTADOR MACHO/FEMEA 16MM</t>
   </si>
   <si>
+    <t>ALONGADOR (EXTENSOR DE BICO)</t>
+  </si>
+  <si>
+    <t>Borracharia</t>
+  </si>
+  <si>
+    <t>AMORTECEDOR DIANT COMPLETO VOLVO</t>
+  </si>
+  <si>
+    <t>AMORTECEDOR TRANSVERSAL DA VOLVO</t>
+  </si>
+  <si>
+    <t>AMORTECEDOR TRAS COMPLETO VOLVO</t>
+  </si>
+  <si>
     <t>ANEL DE REPARO (MENOR)</t>
   </si>
   <si>
+    <t>ANEL DE VEDAÇÃO CUBO FACCHINI</t>
+  </si>
+  <si>
+    <t>ANEL ORING (MAIOR)</t>
+  </si>
+  <si>
+    <t>ANEL PISTA CARRETA RANDON</t>
+  </si>
+  <si>
+    <t>ANILHA 16MM</t>
+  </si>
+  <si>
+    <t>ANILHA 8MM</t>
+  </si>
+  <si>
+    <t>APARA BARRO CARRETA LIBRELATO</t>
+  </si>
+  <si>
+    <t>APARA BARRO CARRETA RANDON</t>
+  </si>
+  <si>
+    <t>APARA BARRO CAVALO SCANIA</t>
+  </si>
+  <si>
+    <t>APARA BARRO CAVALO VOLVO</t>
+  </si>
+  <si>
+    <t>APARABARRO CARRETA FACCHINI</t>
+  </si>
+  <si>
+    <t>ARCO ENLONAR CARRETA BASCULANTE</t>
+  </si>
+  <si>
     <t>ARCO ENLONAR CARRETA GRANELEIRO</t>
   </si>
   <si>
-    <t>ARCO ENLONAR CARRETA BASCULANTE</t>
-  </si>
-  <si>
-    <t>ANEL ORING (MAIOR)</t>
-  </si>
-  <si>
-    <t>ANEL PISTA CARRETA RANDON</t>
-  </si>
-  <si>
-    <t>ANEL DE VEDAÇÃO CUBO FACCHINI</t>
-  </si>
-  <si>
-    <t>APARA BARRO CARRETA RANDON</t>
-  </si>
-  <si>
-    <t>APARA BARRO CAVALO SCANIA</t>
-  </si>
-  <si>
-    <t>APARA BARRO CARRETA LIBRELATO</t>
-  </si>
-  <si>
-    <t>APARABARRO CARRETA FACCHINI</t>
-  </si>
-  <si>
-    <t>APARA BARRO CAVALO VOLVO</t>
+    <t>ARRUELA 1/2</t>
+  </si>
+  <si>
+    <t>ARRUELA 16MM</t>
+  </si>
+  <si>
+    <t>ARRUELA 24MM</t>
+  </si>
+  <si>
+    <t>ARRUELA 6MM</t>
+  </si>
+  <si>
+    <t>ARRUELA 8MM</t>
+  </si>
+  <si>
+    <t>ARRUELA ABA LARGA</t>
+  </si>
+  <si>
+    <t>ARRUELA AJUSTE PARALAMA TRAÇÃO VOLVO</t>
+  </si>
+  <si>
+    <t>ARRUELA CON 5/16P</t>
+  </si>
+  <si>
+    <t>ARRUELA CONICA</t>
   </si>
   <si>
     <t>ARRUELA DE FIXAÇÃO DO AMORTECEDOR VOLVO</t>
   </si>
   <si>
+    <t>ARRUELA DO "S" G</t>
+  </si>
+  <si>
+    <t>ARRUELA DO "S" M</t>
+  </si>
+  <si>
+    <t>ARRUELA DO "S" P</t>
+  </si>
+  <si>
+    <t>ARRUELA LISA CUBO RANDON</t>
+  </si>
+  <si>
     <t>ARRUELA TRAVA LISA LIBRELATO</t>
   </si>
   <si>
-    <t>ARRUELA LISA CUBO RANDON</t>
-  </si>
-  <si>
-    <t>ARRUELA AJUSTE PARALAMA TRAÇÃO VOLVO</t>
-  </si>
-  <si>
-    <t>ARRUELA 6MM</t>
-  </si>
-  <si>
-    <t>ARRUELA 8MM</t>
-  </si>
-  <si>
-    <t>ARRUELA 24MM</t>
-  </si>
-  <si>
-    <t>ARRUELA 1/2</t>
-  </si>
-  <si>
-    <t>ARRUELA ABA LARGA</t>
-  </si>
-  <si>
-    <t>ARRUELA DO "S" P</t>
-  </si>
-  <si>
-    <t>ARRUELA DO "S" M</t>
-  </si>
-  <si>
-    <t>ARRUELA DO "S" G</t>
-  </si>
-  <si>
-    <t>ARRUELA CONICA</t>
-  </si>
-  <si>
-    <t>ARRUELA CON 5/16P</t>
-  </si>
-  <si>
-    <t>ARRUELA 16MM</t>
-  </si>
-  <si>
-    <t>AMORTECEDOR DIANT COMPLETO VOLVO</t>
-  </si>
-  <si>
-    <t>AMORTECEDOR TRAS COMPLETO VOLVO</t>
-  </si>
-  <si>
-    <t>AMORTECEDOR TRANSVERSAL DA VOLVO</t>
-  </si>
-  <si>
-    <t>ANILHA 16MM</t>
-  </si>
-  <si>
-    <t>ANILHA 8MM</t>
+    <t xml:space="preserve">BALANÇA CARRETA RANDON: 100000169562 </t>
+  </si>
+  <si>
+    <t>BARRA CICLISTA LIBRELATO</t>
+  </si>
+  <si>
+    <t>BARRA CICLISTA RANDON</t>
+  </si>
+  <si>
+    <t>BARRA CURTA DIREÇÃO 898MM VOLVO</t>
+  </si>
+  <si>
+    <t>BARRA CURTA DIREÇÃO SCANIA</t>
+  </si>
+  <si>
+    <t>BARRA TRAVAMENTO DA 5ª RODA</t>
+  </si>
+  <si>
+    <t>BATENTE BORRACHA CAÇAMBA</t>
+  </si>
+  <si>
+    <t>BATENTE CABINE CAMINHAO VOLVO</t>
+  </si>
+  <si>
+    <t>BATENTE MOLA DIANTEIRA CAMINHAO VOLVO</t>
+  </si>
+  <si>
+    <t>BATENTE SUPORTE PARALAMA VOLVO</t>
+  </si>
+  <si>
+    <t>BATERIA 180AMP (SCANIA R500)</t>
+  </si>
+  <si>
+    <t>Elétrica</t>
+  </si>
+  <si>
+    <t>BATERIA 220AMP MOURA (VOLVO SCANIA SUPER)</t>
+  </si>
+  <si>
+    <t>BATERIA 225AMP (VOLVO e SCANIA SUPER)</t>
+  </si>
+  <si>
+    <t>BICO DE RODA CAVALO</t>
+  </si>
+  <si>
+    <t>BICO PNEU (RODA FERRO CARRETA)</t>
+  </si>
+  <si>
+    <t>BOCA GRANELEIRA (BICA) + 6 paraf</t>
+  </si>
+  <si>
+    <t>BOLSA AMORTECEDOR CABINE DIANTEIRA VOLVO (BEXIGA</t>
+  </si>
+  <si>
+    <t>BOLSA AMORTECEDOR CABINE TRASEIRA VOLVO (BEXIGA)</t>
+  </si>
+  <si>
+    <t>BOMBA DO INTERCLIMA VOLVO</t>
+  </si>
+  <si>
+    <t>BOMBA INTERCLIMA SCANIA</t>
+  </si>
+  <si>
+    <t>BOMBA LIMPADOR PARABRISA SCANIA</t>
+  </si>
+  <si>
+    <t>BROCA 10MM</t>
+  </si>
+  <si>
+    <t>BROCA 12MM</t>
+  </si>
+  <si>
+    <t>BROCA 16MM</t>
   </si>
   <si>
     <t>BROCA 6MM</t>
@@ -166,78 +250,30 @@
     <t>BROCA 8MM</t>
   </si>
   <si>
-    <t>BROCA 10MM</t>
-  </si>
-  <si>
-    <t>BROCA 12MM</t>
-  </si>
-  <si>
-    <t>BROCA 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BALANÇA CARRETA RANDON: 100000169562 </t>
-  </si>
-  <si>
-    <t>BATENTE CABINE CAMINHAO VOLVO</t>
-  </si>
-  <si>
-    <t>BATENTE MOLA DIANTEIRA CAMINHAO VOLVO</t>
-  </si>
-  <si>
-    <t>BATENTE BORRACHA CAÇAMBA</t>
-  </si>
-  <si>
-    <t>BATENTE SUPORTE PARALAMA VOLVO</t>
-  </si>
-  <si>
-    <t>BARRA CICLISTA RANDON</t>
-  </si>
-  <si>
-    <t>BARRA CICLISTA LIBRELATO</t>
-  </si>
-  <si>
-    <t>BARRA CURTA DIREÇÃO SCANIA</t>
-  </si>
-  <si>
-    <t>BARRA CURTA DIREÇÃO 898MM VOLVO</t>
-  </si>
-  <si>
-    <t>BARRA TRAVAMENTO DA 5ª RODA</t>
-  </si>
-  <si>
-    <t>BOCA GRANELEIRA (BICA) + 6 paraf: 1040046638</t>
-  </si>
-  <si>
     <t>BUCHA AÇO PINO SAPATA (BUCHA DA FLANGE)</t>
   </si>
   <si>
+    <t>BUCHA BARR ESTAB CAMINHAO SCANIA</t>
+  </si>
+  <si>
     <t>BUCHA DA BALANÇA CARRETA</t>
   </si>
   <si>
+    <t>BUCHA DA BARRA ESTAB CABINE DIANT VOLVO</t>
+  </si>
+  <si>
     <t>BUCHA DA CABINE SCANIA</t>
   </si>
   <si>
-    <t>BUCHA DA BARRA ESTAB CABINE DIANT VOLVO</t>
-  </si>
-  <si>
-    <t>BUCHA BARR ESTAB CAMINHAO SCANIA</t>
+    <t>BUCHA DO TIRANTE LIBRELATO</t>
+  </si>
+  <si>
+    <t>BUCHA DO TIRANTE RANDON</t>
   </si>
   <si>
     <t>BUCHA MOLA DIANT SCANIA (TIRANTE DA CABINE)</t>
   </si>
   <si>
-    <t>BOLSA AMORTECEDOR CABINE TRASEIRA VOLVO (BEXIGA)</t>
-  </si>
-  <si>
-    <t>BOLSA AMORTECEDOR CABINE DIANTEIRA VOLVO (BEXIGA</t>
-  </si>
-  <si>
-    <t>BUCHA DO TIRANTE RANDON</t>
-  </si>
-  <si>
-    <t>BUCHA DO TIRANTE LIBRELATO</t>
-  </si>
-  <si>
     <t>BUJÃO (TAMPÃO)  (M16)</t>
   </si>
   <si>
@@ -247,27 +283,45 @@
     <t>BUJÃO DE AR CARRETA 77LTS</t>
   </si>
   <si>
-    <t>TAMBOR DE FREIO RANDON (CAMPANA FREIO)</t>
+    <t>CABO 2X1 (LANÇAR POR METRO)</t>
+  </si>
+  <si>
+    <t>CABO 7X1 (LANÇAR POR METRO)</t>
+  </si>
+  <si>
+    <t>CABO P/RASTR RASTR AUTOTRAC/2730</t>
+  </si>
+  <si>
+    <t>CADEADO 25MM</t>
+  </si>
+  <si>
+    <t>CAIXA LAD DIR LANTERNA RANDON</t>
+  </si>
+  <si>
+    <t>CAIXA LAD ESQ LANTERNA RANDON</t>
+  </si>
+  <si>
+    <t>CALIBRADOR PR C/HAST INDIC;FIX ANG;7188F</t>
+  </si>
+  <si>
+    <t>CAPA AUX L/D RETROVISOR SCANIA</t>
+  </si>
+  <si>
+    <t>CAPA AUX L/E RETROVISOR SCANIA</t>
+  </si>
+  <si>
+    <t>CAPA BANCO SCANIA</t>
   </si>
   <si>
     <t>CAPA BANCO VOLVO</t>
   </si>
   <si>
-    <t>CAPA BANCO SCANIA</t>
-  </si>
-  <si>
-    <t>CAPA AUX L/D RETROVISOR SCANIA</t>
-  </si>
-  <si>
-    <t>CAPA AUX L/E RETROVISOR SCANIA</t>
+    <t>CAPA PRENS P/MANG 1/2POL</t>
   </si>
   <si>
     <t>CAPA PRENS P/MANG 1/4POL</t>
   </si>
   <si>
-    <t>CAPA PRENS P/MANG 1/2POL</t>
-  </si>
-  <si>
     <t>CAPA PRENS P/MANG 1POL</t>
   </si>
   <si>
@@ -283,19 +337,58 @@
     <t>CATRACA FREIO CAVALO DIANT (L/E)</t>
   </si>
   <si>
-    <t>CINTA BUJÃO DE AR DOLLY</t>
-  </si>
-  <si>
-    <t>CINTA DO BUJÃO DE AR CARRETA</t>
+    <t>CHICOTE 2 VIAS INJEÇÃO ELETRONICA</t>
+  </si>
+  <si>
+    <t>CHICOTE 4 VIAS RAINHA (ABS)</t>
+  </si>
+  <si>
+    <t>CHICOTE 7 P COBR/PLAST CARR DNI/DNI8355 (CHICOTE ABS COMPLETO)</t>
+  </si>
+  <si>
+    <t>CHICOTE 7 VIAS LANTERNA CAVALO</t>
+  </si>
+  <si>
+    <t>CHICOTE 7 VIAS SIMPLES (CABO ASPIRAL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHICOTE CONECTOR LANTERNA TRAS FACCHINI LD </t>
+  </si>
+  <si>
+    <t>CHICOTE CONECTOR LANTERNA TRAS FACCHINI LE</t>
+  </si>
+  <si>
+    <t>CINTA</t>
+  </si>
+  <si>
+    <t>Operação Pluma</t>
+  </si>
+  <si>
+    <t>CINTA  DO BUJÃO DE AR DOLLY 640MM</t>
+  </si>
+  <si>
+    <t>CINTA BUJÃO DE AR G VOLVO/SCANIA</t>
   </si>
   <si>
     <t>CINTA BUJÃO DE AR P</t>
   </si>
   <si>
-    <t>CINTA BUJÃO DE AR G VOLVO/SCANIA</t>
+    <t>CINTA DO BUJÃO DE AR CARRETA 850MM</t>
   </si>
   <si>
     <t>CINTA DO COROTE DE AGUA</t>
+  </si>
+  <si>
+    <t>CJ ENGATE HIDRAULICO 12. 3/4 NPT</t>
+  </si>
+  <si>
+    <t>CJ ENGATE HIDRAULICO 16. 1POL NPT</t>
+  </si>
+  <si>
+    <t>CJ ENGATE HIDRAULICO 16. 3/4 NPT</t>
+  </si>
+  <si>
+    <t>CONECTOR MACHO 12X22MM</t>
   </si>
   <si>
     <r>
@@ -314,33 +407,39 @@
     </r>
   </si>
   <si>
-    <t>CONECTOR MACHO 12X22MM</t>
-  </si>
-  <si>
     <t>CONECTOR MACHO 8X16MM</t>
   </si>
   <si>
+    <t>CONJUNTO DE EIXO MOVIMENTAÇÃO</t>
+  </si>
+  <si>
+    <t>CONTRA PESO 100G  (LANÇAR POR UND 25)</t>
+  </si>
+  <si>
+    <t>CONTRA PESO 150G  (LANÇAR POR UND 25)</t>
+  </si>
+  <si>
+    <t>CONTRA PESO 200G  (LANÇAR POR UND 25)</t>
+  </si>
+  <si>
+    <t>CONTRA PESO 250G  (LANÇAR POR UND 25)</t>
+  </si>
+  <si>
+    <t>CONTRA PESO 300G  (LANÇAR POR UND 25)</t>
+  </si>
+  <si>
     <t>CONTRA PESO 50G (LANÇAR POR UND 25)</t>
   </si>
   <si>
-    <t>CONTRA PESO 100G  (LANÇAR POR UND 25)</t>
-  </si>
-  <si>
-    <t>CONTRA PESO 150G  (LANÇAR POR UND 25)</t>
-  </si>
-  <si>
-    <t>CONTRA PESO 200G  (LANÇAR POR UND 25)</t>
-  </si>
-  <si>
-    <t>CONTRA PESO 250G  (LANÇAR POR UND 25)</t>
-  </si>
-  <si>
-    <t>CONTRA PESO 300G  (LANÇAR POR UND 25)</t>
+    <t>CORDA (METROS)</t>
   </si>
   <si>
     <t>COROTE ÁGUA 25LT</t>
   </si>
   <si>
+    <t xml:space="preserve">CORREIA BORRACHA PARALAMA VOLVO (PRESILHA TRAVA) </t>
+  </si>
+  <si>
     <t>CORRENTE (25 kg)</t>
   </si>
   <si>
@@ -350,1291 +449,1195 @@
     <t>COTOVELO MACH/FEM 16X16</t>
   </si>
   <si>
-    <t xml:space="preserve">CORREIA BORRACHA PARALAMA VOLVO (PRESILHA TRAVA) </t>
+    <t>COXIM 5ª RODA AD00342J00</t>
+  </si>
+  <si>
+    <t>COXIM 5ª RODA AD00343J00</t>
+  </si>
+  <si>
+    <t>COXIM CAIXA TRAS CAMINHAO SCANIA</t>
+  </si>
+  <si>
+    <t>COXIM DA 5ª RODA FONTAINE</t>
+  </si>
+  <si>
+    <t>COXIM MOTOR DIANT CAMINHAO SCANIA</t>
   </si>
   <si>
     <t>COXIM RESERVATORIO HIDRAULICO VOLVO</t>
   </si>
   <si>
-    <t>COXIM CAIXA TRAS CAMINHAO SCANIA</t>
-  </si>
-  <si>
-    <t>COXIM MOTOR DIANT CAMINHAO SCANIA</t>
-  </si>
-  <si>
-    <t>CONJUNTO DE EIXO MOVIMENTAÇÃO</t>
-  </si>
-  <si>
-    <t>COXIM 5ª RODA AD00342J00</t>
-  </si>
-  <si>
-    <t>COXIM 5ª RODA AD00343J00</t>
-  </si>
-  <si>
-    <t>COXIM DA 5ª RODA FONTAINE</t>
+    <t>CREMALHEIRA RANDON</t>
+  </si>
+  <si>
+    <t>CUBO LIBRELATO</t>
   </si>
   <si>
     <t>CUBO RANDON</t>
   </si>
   <si>
-    <t>CUBO LIBRELATO</t>
-  </si>
-  <si>
-    <t>CREMALHEIRA RANDON</t>
-  </si>
-  <si>
     <t>CUICÃO (CUICA 30X30)</t>
   </si>
   <si>
     <t>CX FERRAMENTA RANDON</t>
   </si>
   <si>
-    <t>CJ ENGATE HIDRAULICO 16. 1POL NPT</t>
-  </si>
-  <si>
-    <t>CJ ENGATE HIDRAULICO 16. 3/4 NPT</t>
-  </si>
-  <si>
-    <t>CJ ENGATE HIDRAULICO 12. 3/4 NPT</t>
+    <t>DESINGRIPANTE</t>
   </si>
   <si>
     <t>DESLIZANTE RANDON</t>
   </si>
   <si>
+    <t>DIAFRAGMA 7 POLEGADAS</t>
+  </si>
+  <si>
+    <t>DIAFRAGMA 8 POLEGADAS</t>
+  </si>
+  <si>
+    <t>DISCO CORTE 4 POLEGADAS DEWALT</t>
+  </si>
+  <si>
+    <t>Tintas</t>
+  </si>
+  <si>
+    <t>DISCO CORTE 7 POLEGADAS DEWALT</t>
+  </si>
+  <si>
+    <t>DISCO DE EMERGENCIA (ASSENTO CUICA)</t>
+  </si>
+  <si>
+    <t>DISCO DESBASTE 7P</t>
+  </si>
+  <si>
+    <t>DISCO FLAP 4 POLEGADAS</t>
+  </si>
+  <si>
+    <t>DISCO FLAP 7 POLEGADAS</t>
+  </si>
+  <si>
+    <t>DISCO FRICÇÃO 5ª RODA 3 FUROS FERRADURA CARRETA</t>
+  </si>
+  <si>
+    <t>DISCO FRICCÇÃO 5ª RODA 4 FUROS FERRADURA CAVALO</t>
+  </si>
+  <si>
+    <t>DISCO ROQUITE 80</t>
+  </si>
+  <si>
+    <t>DISFUSOR DE AR SCANIA LD</t>
+  </si>
+  <si>
     <t>DISFUSOR DE AR SCANIA LE</t>
   </si>
   <si>
-    <t>DISFUSOR DE AR SCANIA LD</t>
-  </si>
-  <si>
-    <t>DIAFRAGMA 7 POLEGADAS</t>
-  </si>
-  <si>
-    <t>DIAFRAGMA 8 POLEGADAS</t>
-  </si>
-  <si>
-    <t>DISCO DE EMERGENCIA (ASSENTO CUICA)</t>
-  </si>
-  <si>
-    <t>DISCO FRICÇÃO 5ª RODA 3 FUROS FERRADURA CARRETA</t>
-  </si>
-  <si>
-    <t>DISCO FRICCÇÃO 5ª RODA 4 FUROS FERRADURA CAVALO</t>
-  </si>
-  <si>
     <t>EIXO S LADO DIREITO</t>
   </si>
   <si>
     <t>EIXO S LADO ESQUERDO</t>
   </si>
   <si>
+    <t>ELETRODO 2.50MM (5KG)</t>
+  </si>
+  <si>
+    <t>ELETRODO 3.25MM (5KG)</t>
+  </si>
+  <si>
     <t>EMBOLO (CUICA) LG 30X30MM CARR MASTER  (HASTE)</t>
   </si>
   <si>
+    <t>EMBREAGEM VOLVO</t>
+  </si>
+  <si>
+    <t>EMENDA REDUÇÃO 16X16</t>
+  </si>
+  <si>
+    <t>ENGATE CORRENTE (TRAVA CORRENTE)</t>
+  </si>
+  <si>
+    <t>ENGATE FEMEA CARRETA (SUPERIOR)</t>
+  </si>
+  <si>
+    <t>ENGATE FEMEA FOMINHA RANDON (INFERIOR)</t>
+  </si>
+  <si>
+    <t>ENGATE HIDRAULICO FEMEA LIBRELATO 1POL</t>
+  </si>
+  <si>
+    <t>ENGATE HIDRAULICO MACHO LIBRELATO 1POL</t>
+  </si>
+  <si>
+    <t>ENGATE RÁPIDO 3/4 (MÃO AMIGA)</t>
+  </si>
+  <si>
+    <t>ENGATE REBOQUE SCANIA</t>
+  </si>
+  <si>
+    <t>ENGATE REBOQUE VOLVO (CJ)</t>
+  </si>
+  <si>
+    <t>ESCOVA  AÇO CABO PLAST</t>
+  </si>
+  <si>
+    <t>ESCOVA ROTATIVA 7P (P/LIXADEIRA)</t>
+  </si>
+  <si>
+    <t>ESPUMA EXPANSIVA</t>
+  </si>
+  <si>
+    <t>ESTOPA (LANÇAR POR UND)</t>
+  </si>
+  <si>
+    <t>FAIXA REFLET LD 3M HB004037105</t>
+  </si>
+  <si>
+    <t>FAIXA REFLET LE 3M HB004037097</t>
+  </si>
+  <si>
+    <t>FAIXA REFLETIVA PARACHOQUE</t>
+  </si>
+  <si>
+    <t>FILTRO DE AR EXTERNO SCANIA</t>
+  </si>
+  <si>
+    <t>FILTRO DE AR EXTERNO VOLVO</t>
+  </si>
+  <si>
+    <t>FILTRO DE AR INTERNO SCANIA</t>
+  </si>
+  <si>
+    <t>FILTRO DE AR INTERNO VOLVO</t>
+  </si>
+  <si>
+    <t>FITA CREPE LARGA</t>
+  </si>
+  <si>
+    <t>FITA DUPLA FACE 3M</t>
+  </si>
+  <si>
+    <t>FITA DUREX</t>
+  </si>
+  <si>
+    <t>FITA ISOLANTE</t>
+  </si>
+  <si>
+    <t>FITA TACÓGRAFO VOLVO EURO 5 (BOBINA)</t>
+  </si>
+  <si>
+    <t>FITA TACÓGRAFO VOLVO EURO 6 (BOBINA)</t>
+  </si>
+  <si>
+    <t>FITA VEDA ROSCA</t>
+  </si>
+  <si>
+    <t>FITA ZEBRADA</t>
+  </si>
+  <si>
+    <t>FIXADOR SUPORTE PARALAMA VOLVO</t>
+  </si>
+  <si>
+    <t>FLEXIVEL</t>
+  </si>
+  <si>
+    <t>FOLE PNEUM LIBRELATO (BEXIGA)</t>
+  </si>
+  <si>
+    <t>FORQUILHA CUICA</t>
+  </si>
+  <si>
+    <t>FUSIVEL 10 AMPERES</t>
+  </si>
+  <si>
+    <t>FUSIVEL 15 AMPERES</t>
+  </si>
+  <si>
+    <t>FUSIVEL VAMPIRINHO 10A (VOLVO)</t>
+  </si>
+  <si>
+    <t>FUSIVEL VAMPIRINHO 20A (VOLVO)</t>
+  </si>
+  <si>
+    <t>GANCHO DE LONA (LIGA)</t>
+  </si>
+  <si>
+    <t>GANCHO FECHAMENTO ESFERICO</t>
+  </si>
+  <si>
+    <t>GAVIÃO 5ª RODA</t>
+  </si>
+  <si>
+    <t>GRAMPO MOLEJO 7/8 (38)</t>
+  </si>
+  <si>
+    <t>GRAMPO PNEUMÁTICO</t>
+  </si>
+  <si>
+    <t>GRAMPO U TRAVA SEGURANÇA CAÇAMBA</t>
+  </si>
+  <si>
+    <t>GRAXA LITIO 20KG (LANÇAR POR KG)</t>
+  </si>
+  <si>
+    <t>GRAXA TEXACO 170KG</t>
+  </si>
+  <si>
+    <t>GUIA PARAF REGULAGEM 5ª RODA</t>
+  </si>
+  <si>
+    <t>INFLADOR DE ENCHER PNEU</t>
+  </si>
+  <si>
+    <t>INSERT 16MM</t>
+  </si>
+  <si>
+    <t>INSERT 6MM</t>
+  </si>
+  <si>
+    <t>INSERT 8MM</t>
+  </si>
+  <si>
+    <t>JG DE LONA CARRETA LIBRELATO</t>
+  </si>
+  <si>
+    <t>JG DE LONA CARRETA RANDON</t>
+  </si>
+  <si>
+    <t>JG DE LONA DIANTEIRA CAVALO SCANIA</t>
+  </si>
+  <si>
+    <t>JG DE LONA TRAÇÃO CAVALO SCANIA</t>
+  </si>
+  <si>
+    <t>JUNTA 4 FUROS (LIBRELATO)</t>
+  </si>
+  <si>
+    <t>JUNTA CUBO 5 FUROS GRANDE RANDON</t>
+  </si>
+  <si>
+    <t>JUNTA CUBO 5 FUROS PEQ RANDON</t>
+  </si>
+  <si>
+    <t>KIT DE EMBREAGEM SCANIA</t>
+  </si>
+  <si>
+    <t>KIT REPARO CATRACA FREIO AUTOMATICA</t>
+  </si>
+  <si>
+    <t>KIT REPARO EIXO S (BUCHA EIXO S)</t>
+  </si>
+  <si>
+    <t>KIT TAPA PO FACCHINI LD (ESPELHO)</t>
+  </si>
+  <si>
+    <t>KIT TAPA PO FACCHINI LE (ESPELHO)</t>
+  </si>
+  <si>
+    <t>KIT TAPA PO RANDON (PAR DE ESPELHO)</t>
+  </si>
+  <si>
+    <t>LAMPADA H7</t>
+  </si>
+  <si>
+    <t>LAMPADA MEIA LUZ VOLVO (LAMP 67)</t>
+  </si>
+  <si>
+    <t>LÂMPADA MINIAT1141</t>
+  </si>
+  <si>
+    <t>LANT TRASEIRA SCANIA R500  LE</t>
+  </si>
+  <si>
+    <t>LANT TRASEIRA SCANIA R500 LD</t>
+  </si>
+  <si>
+    <t>LANT TRASEIRA VOLVO LD</t>
+  </si>
+  <si>
+    <t>LANT TRASEIRA VOLVO LE</t>
+  </si>
+  <si>
+    <t>LANTERNA CRISTAL LIBRELATO</t>
+  </si>
+  <si>
+    <t>LANTERNA CRISTAL RANDON</t>
+  </si>
+  <si>
+    <t>LANTERNA DE PLACA</t>
+  </si>
+  <si>
+    <t>LANTERNA DO ABS (LANTERNA VERDE)</t>
+  </si>
+  <si>
+    <t>LANTERNA LAT C/SUPORTE LIBRELATO</t>
+  </si>
+  <si>
+    <t>LANTERNA LAT C/SUPORTE RANDON</t>
+  </si>
+  <si>
+    <t>LANTERNA LAT S/SUPORTE LIBRELATO</t>
+  </si>
+  <si>
+    <t>LANTERNA LAT S/SUPORTE RANDON</t>
+  </si>
+  <si>
+    <t>LANTERNA LAT TANQUE (DELIMITADORA)</t>
+  </si>
+  <si>
+    <t>LANTERNA SCANIA SUPER LD</t>
+  </si>
+  <si>
+    <t>LANTERNA SCANIA SUPER LE</t>
+  </si>
+  <si>
+    <t>LENTE LANT TRAS CAMINHAO VOLVO/20425732</t>
+  </si>
+  <si>
+    <t>LIMPA CONTATO (SO PARA ELÉTRICA)</t>
+  </si>
+  <si>
+    <t>LIXA FERRO N120 225X275MM</t>
+  </si>
+  <si>
+    <t>LIXA OURO 120</t>
+  </si>
+  <si>
+    <t>LIXA OURO 220</t>
+  </si>
+  <si>
+    <t>LOCTITTE (TRAVA PARAFUSO)</t>
+  </si>
+  <si>
+    <t>LONA EMBORRACHADA GRANELEIRO</t>
+  </si>
+  <si>
+    <t>LONA PROT COB PVC AZ - (LONA FÁCIL)</t>
+  </si>
+  <si>
+    <t>MANCAL EXT DA BALANÇA (ANEL APOIO)</t>
+  </si>
+  <si>
+    <t>MANCAL EXTERNO EIXO S</t>
+  </si>
+  <si>
+    <t>MANCAL INT DA BALANÇA (ANEL ACO PIN)</t>
+  </si>
+  <si>
+    <t>MANCAL INTERNO EIXO S (SPIDER)</t>
+  </si>
+  <si>
+    <t>MANCAL SACHS/3315</t>
+  </si>
+  <si>
+    <t>MANGUEIRA 1/4</t>
+  </si>
+  <si>
+    <t>MANGUEIRA 3/4</t>
+  </si>
+  <si>
+    <t>MANGUEIRA ESPIRAL AMARELO</t>
+  </si>
+  <si>
+    <t>MANGUEIRA ESPIRAL VERMELHO</t>
+  </si>
+  <si>
+    <t>MANGUEIRA HIDR 1 POL</t>
+  </si>
+  <si>
+    <t>MANIFOLD 2 VIAS</t>
+  </si>
+  <si>
+    <t>MANIVELA ESFÉRICO ENG DOLLY (L/D)</t>
+  </si>
+  <si>
+    <t>MANIVELA ESFÉRICO ENG DOLLY (L/E)</t>
+  </si>
+  <si>
+    <t>MEIO PARALAMA DD-TE CARRETA FACCHINI</t>
+  </si>
+  <si>
+    <t>MEIO PARALAMA DE-TD CARRETA FACCHINI</t>
+  </si>
+  <si>
+    <t>MINI RELE AUXILIAR 24V</t>
+  </si>
+  <si>
+    <t>MODULO DE FREIO FACCHINI</t>
+  </si>
+  <si>
+    <t>MODULO DE FREIO RANDON</t>
+  </si>
+  <si>
+    <t>MODULO DE FREIO RANDON CAÇAMBA NEW R LD</t>
+  </si>
+  <si>
+    <t>MODULO DE FREIO RANDON CAÇAMBA NEW R LE</t>
+  </si>
+  <si>
+    <t>MOLA CUICA G</t>
+  </si>
+  <si>
+    <t>MOLA CUICA P</t>
+  </si>
+  <si>
+    <t>MOLA DUPLA 5ª RODA RETORNO</t>
+  </si>
+  <si>
+    <t>MOLA GARRA TRAVAMENTO (MOLA P/ 5ª RODA)</t>
+  </si>
+  <si>
+    <t>MOLA MESTRE (GROSSA)</t>
+  </si>
+  <si>
+    <t>MOLA MESTRE TRAÇÃO VOLVO</t>
+  </si>
+  <si>
+    <t>MOLA PATIM G</t>
+  </si>
+  <si>
+    <t>MOLA PATIM P</t>
+  </si>
+  <si>
+    <t>MOLA PNEUM CABIN R500 SCANIA DIANTEIRA</t>
+  </si>
+  <si>
+    <t>MOLA PNEUM CABIN R500 TRASEIRA (BEXIGA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOLA PNEUM G 38MM (FOLE) </t>
+  </si>
+  <si>
+    <t>MOLA PNEUM PEQ 32/33MM (FOLE)</t>
+  </si>
+  <si>
+    <t>MOLA REGULAGEM TRAVA CAÇAMBA (MOLA TAMPA)</t>
+  </si>
+  <si>
+    <t>MOTOR INTERCLIMA SCANIA</t>
+  </si>
+  <si>
+    <t>NIPLE MACHO 16MM</t>
+  </si>
+  <si>
+    <t>NÚCLEO CURTO VÁLV. PNEU</t>
+  </si>
+  <si>
+    <t>ÓLEO 68 (20L) (LANÇAR POR LITRO)</t>
+  </si>
+  <si>
+    <t>ÓLEO ATF FLUIDO DIREÇÃO</t>
+  </si>
+  <si>
+    <t>ÓLEO PNEUMÁTICO</t>
+  </si>
+  <si>
+    <t>PAINEL PNEUMÁTICO (CX DE COMANDO)</t>
+  </si>
+  <si>
+    <t>PALHA INTERCLIMA SCANIA</t>
+  </si>
+  <si>
+    <t>PALHETA PARABRISA</t>
+  </si>
+  <si>
+    <t>PARAF AJUSTE 5ª RODA (REGULAGEM)</t>
+  </si>
+  <si>
+    <t>PARAF CAB FRANC 5/16X2P 3/4</t>
+  </si>
+  <si>
+    <t>PARAF CAB FRANC PORC 5/16X3P</t>
+  </si>
+  <si>
+    <t>PARAF CAB FRANC (BICA)</t>
+  </si>
+  <si>
+    <t>PARAFUSO  16X150MM</t>
+  </si>
+  <si>
+    <t>PARAFUSO 10X30</t>
+  </si>
+  <si>
+    <t>PARAFUSO 10X40</t>
+  </si>
+  <si>
+    <t>PARAFUSO 10X60</t>
+  </si>
+  <si>
+    <t>PARAFUSO 10X60 (CUICA)</t>
+  </si>
+  <si>
+    <t>PARAFUSO 10X70</t>
+  </si>
+  <si>
+    <t>PARAFUSO 12X40</t>
+  </si>
+  <si>
+    <t>PARAFUSO 16X130MM</t>
+  </si>
+  <si>
+    <t>PARAFUSO 16X65</t>
+  </si>
+  <si>
+    <t>PARAFUSO 16X70</t>
+  </si>
+  <si>
+    <t>PARAFUSO 20X100MM</t>
+  </si>
+  <si>
+    <t>PARAFUSO 4MM</t>
+  </si>
+  <si>
+    <t>PARAFUSO 5ª RODA</t>
+  </si>
+  <si>
+    <t>PARAFUSO 6X30</t>
+  </si>
+  <si>
+    <t>PARAFUSO 6X40</t>
+  </si>
+  <si>
+    <t>PARAFUSO 6X80</t>
+  </si>
+  <si>
+    <t>PARAFUSO 8X30</t>
+  </si>
+  <si>
+    <t>PARAFUSO 8X40</t>
+  </si>
+  <si>
+    <t>PARAFUSO 8X50</t>
+  </si>
+  <si>
+    <t>PARAFUSO 8X60</t>
+  </si>
+  <si>
+    <t>PARAFUSO 8X70</t>
+  </si>
+  <si>
+    <t>PARAFUSO 8X80</t>
+  </si>
+  <si>
+    <t>PARAFUSO BARRA DE TRAVAMENTO</t>
+  </si>
+  <si>
+    <t>PARAFUSO BROCANTE</t>
+  </si>
+  <si>
+    <t>PARAFUSO DA TRAÇÃO VOLVO</t>
+  </si>
+  <si>
+    <t>PARAFUSO DE REGULAGEM DO ESFÉRICO</t>
+  </si>
+  <si>
+    <t>PARAFUSO DE RODA CARRETA LIBRELATTO</t>
+  </si>
+  <si>
+    <t>PARAFUSO DE RODA CARRETA RANDON</t>
+  </si>
+  <si>
+    <t>PARAFUSO DE RODA DIANTEIRA SCANIA</t>
+  </si>
+  <si>
+    <t>PARAFUSO DE RODA DIANTEIRA VOLVO</t>
+  </si>
+  <si>
+    <t>PARAFUSO DE RODA TRAÇÃO SCANIA</t>
+  </si>
+  <si>
+    <t>PARAFUSO DO PINO REI</t>
+  </si>
+  <si>
+    <t>PARAFUSO DO TECNIL 5ª RODA</t>
+  </si>
+  <si>
+    <t>PARAFUSO PHILLIPS 4X30MM</t>
+  </si>
+  <si>
+    <t>PARALAMA CARRETA FACCHINI</t>
+  </si>
+  <si>
+    <t>PARALAMA CARRETA LIBRELATO</t>
+  </si>
+  <si>
+    <t>PARALAMA CARRETA RANDON</t>
+  </si>
+  <si>
+    <t>PARALAMA TRAÇÃO CAVALO SCANIA</t>
+  </si>
+  <si>
+    <t>PARALAMA TRASEIRO CABINE SCANIA LD</t>
+  </si>
+  <si>
+    <t>PARALAMA VOLVO 2ª PARTE (PARTE DE CIMA)</t>
+  </si>
+  <si>
+    <t>PARALAMA VOLVO MEIO PARALAMA (PARTE DE BAIXO)</t>
+  </si>
+  <si>
+    <t>PATIM DE FREIO LIBRELATO</t>
+  </si>
+  <si>
+    <t>PATIM DE FREIO RANDON</t>
+  </si>
+  <si>
+    <t>PE APOIO DOLLY</t>
+  </si>
+  <si>
+    <t>PINCEL</t>
+  </si>
+  <si>
+    <t>PINO DA BALANÇA (PARAFUSO)</t>
+  </si>
+  <si>
+    <t>PINO DE CENTRO</t>
+  </si>
+  <si>
+    <t>PINO DO REBOQUE SCANIA</t>
+  </si>
+  <si>
+    <t>PINO ENGATE ESFÉRICO (BOLA DO ESFÉRICO)</t>
+  </si>
+  <si>
+    <t>PINO REI 2P FLANGEADO RANDON</t>
+  </si>
+  <si>
+    <t>PINO TIRANTE (TENSOR)</t>
+  </si>
+  <si>
+    <t>PISTOLA DE AR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNEU BORRACHUDO BONIN RT78 (RECAPADO) </t>
+  </si>
+  <si>
+    <t>PNEU BORRACHUDO FOX TMD (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU BORRACHUDO NOVO</t>
+  </si>
+  <si>
+    <t>PNEU BORRACHUDO VIPAL  VT100 (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU BORRACHUDO VIPAL VRT2 (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU LISO BONIN RT51 (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU LISO FOX BTL3B (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU LISO NOVO</t>
+  </si>
+  <si>
+    <t>PNEU LISO VIPAL BANDA NOVA VL130 (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU LISO VIPAL VL110 (RECAPADO)</t>
+  </si>
+  <si>
+    <t>PNEU VULCANIZADO</t>
+  </si>
+  <si>
+    <t>PONTEIRA BARRA CICLISTA LIBRELATO</t>
+  </si>
+  <si>
+    <t>PONTEIRA BARRA CICLISTA RANDON</t>
+  </si>
+  <si>
+    <t>PONTEIRA CURVA 3/4</t>
+  </si>
+  <si>
+    <t>PONTEIRA ENGATE ESFÉRICO</t>
+  </si>
+  <si>
+    <t>PONTEIRA MANGUEIRA 1POL (TERMINAL FEMEA)</t>
+  </si>
+  <si>
+    <t>PORCA 10MM TRAVANTE</t>
+  </si>
+  <si>
+    <t>PORCA 12MM TRAVANTE</t>
+  </si>
+  <si>
+    <t>PORCA 14MM TRAVANTE</t>
+  </si>
+  <si>
+    <t>PORCA 16MM TRAVANTE ROSCA FINA</t>
+  </si>
+  <si>
+    <t>PORCA 20MM TRAVANTE</t>
+  </si>
+  <si>
+    <t>PORCA 4MM SIMPLES</t>
+  </si>
+  <si>
+    <t>PORCA 6MM SIMPLES</t>
+  </si>
+  <si>
+    <t>PORCA 6MM TRAVANTE</t>
+  </si>
+  <si>
+    <t>PORCA 8MM SIMPLES</t>
+  </si>
+  <si>
+    <t>PORCA 8MM TRAVANTE</t>
+  </si>
+  <si>
+    <t>PORCA CASTELADA LIBRELATO (PORCA DO EIXO DO CUBO)</t>
+  </si>
+  <si>
+    <t>PORCA CASTELADA RANDON (PORCA DO EIXO 80)</t>
+  </si>
+  <si>
+    <t>PORCA P/GRAMPO MOLEJO (2UND)</t>
+  </si>
+  <si>
+    <t>PORCA P/GRAMPO PNEUMATICO (4UND)</t>
+  </si>
+  <si>
+    <t>PORCA PARAF DE RODA</t>
+  </si>
+  <si>
+    <t>PORCA PINO BALANÇA</t>
+  </si>
+  <si>
+    <t>PORCA PINO DE CENTRO (1UND)</t>
+  </si>
+  <si>
+    <t>PORCA PINO TIRANTE (1UND)</t>
+  </si>
+  <si>
+    <t>PORCA SEXT AUTO TRAV 16MM ROSCA GROSSA</t>
+  </si>
+  <si>
+    <t>PRATO PNEUMATICO LIBRELATO INFERIOR 38MM</t>
+  </si>
+  <si>
+    <t>PRATO PNEUMATICO LIBRELATO SUPERIOR 38MM</t>
+  </si>
+  <si>
+    <t>PRATO PNEUMATICO RANDON INFERIOR 33MM</t>
+  </si>
+  <si>
+    <t>PRATO PNEUMATICO RANDON SUPERIOR 33MM</t>
+  </si>
+  <si>
+    <t>PRESILHA DA CORRENTE "V" ESTREITO (TAMPA)</t>
+  </si>
+  <si>
+    <t>PRESILHA DA CORRENTE "V" LARGO (fueiro)</t>
+  </si>
+  <si>
+    <t>PRESILHA DO FUEIRO TIPO U (POMPOM)</t>
+  </si>
+  <si>
+    <t>REBITE ALUMINIO</t>
+  </si>
+  <si>
+    <t>REBITE DE FERRRO</t>
+  </si>
+  <si>
+    <t>REDE CONTENÇÃO PLUMA</t>
+  </si>
+  <si>
+    <t>REDUCAO MACH/FEM 22X16MM</t>
+  </si>
+  <si>
+    <t>REPARO CENTRAL DA CUICA CARRETA</t>
+  </si>
+  <si>
+    <t>REPARO CUICAO DIANTEIRA</t>
+  </si>
+  <si>
+    <t>REPARO CUICÃO TRAÇÃO</t>
+  </si>
+  <si>
+    <t>REPARO DA VALV COMANDO LIBRELATO (QA-448MP)</t>
+  </si>
+  <si>
+    <t>REPARO DA VAVULA PUSH (BOTÃO PRETO)</t>
+  </si>
+  <si>
+    <t>REPARO DESMONTAGEM CARRETA (EMERGENCIA)</t>
+  </si>
+  <si>
+    <t>RESERVATORIO INTERCLIMA</t>
+  </si>
+  <si>
+    <t>RETENTOR</t>
+  </si>
+  <si>
+    <t>RETROREFLETOR CX LADO DIREITO</t>
+  </si>
+  <si>
+    <t>RETROREFLETOR CX LADO ESQUERDO</t>
+  </si>
+  <si>
+    <t>RODA 22,5X8,25 295 10 FUROS</t>
+  </si>
+  <si>
+    <t>ROLAMENTO BARRA TORÇÃO VOLVO G</t>
+  </si>
+  <si>
+    <t>ROLAMENTO BARRA TORÇÃO VOLVO P</t>
+  </si>
+  <si>
+    <t>ROLAMENTO FACCHINI 33021</t>
+  </si>
+  <si>
+    <t>ROLAMENTO FIX ESF;30X72X19MM;AC;6306ZZC3</t>
+  </si>
+  <si>
+    <t>ROLAMENTO G (INTERNO)</t>
+  </si>
+  <si>
+    <t>ROLAMENTO P (EXTERNO)</t>
+  </si>
+  <si>
+    <t>ROLETE 32MM</t>
+  </si>
+  <si>
+    <t>ROLETE FLANGE (PINO SAPATA)</t>
+  </si>
+  <si>
+    <t>SACA VÁLVULA</t>
+  </si>
+  <si>
+    <t>SENSOR ABS CARRETA</t>
+  </si>
+  <si>
+    <t>SILICONE PRETO</t>
+  </si>
+  <si>
+    <t>SIRENE AUTOTRAC</t>
+  </si>
+  <si>
+    <t>SIRENE DE RÉ</t>
+  </si>
+  <si>
+    <t>SUPORTE ACO CARRETA RANDON (CUICA)</t>
+  </si>
+  <si>
+    <t>SUPORTE BARRA CICLISTA RANDON</t>
+  </si>
+  <si>
+    <t>SUPORTE CENTRAL PARALAMA SCANIA</t>
+  </si>
+  <si>
+    <t>SUPORTE CENTRAL PARALAMA VOLVO</t>
+  </si>
+  <si>
+    <t>SUPORTE CX FERRAMENTA  LD</t>
+  </si>
+  <si>
+    <t>SUPORTE CX FERRAMENTA LE</t>
+  </si>
+  <si>
+    <t>SUPORTE FIXO BARRA CICLISTA LIBRELATO</t>
+  </si>
+  <si>
+    <t>SUPORTE G DAS TAMPAS (ENGATE)</t>
+  </si>
+  <si>
+    <t>SUPORTE LANTERNA BASCULANTE FACCHINI LD</t>
+  </si>
+  <si>
+    <t>SUPORTE LANTERNA BASCULANTE FACCHINI LE</t>
+  </si>
+  <si>
+    <t>SUPORTE LANTERNA DIANT DOLLY FACCHINI LD</t>
+  </si>
+  <si>
+    <t>SUPORTE LANTERNA DIANT DOLLY FACCHINI LE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPORTE LANTERNA DOLLY DIANTEIRA (BRACINHO) </t>
+  </si>
+  <si>
+    <t>SUPORTE LANTERNA DOLLY TRASEIRO LD (RANDON)</t>
+  </si>
+  <si>
+    <t>SUPORTE LANTERNA DOLLY TRASEIRO LE (RANDON)</t>
+  </si>
+  <si>
+    <t>SUPORTE LANTERNA LAT LIBRELATO (BRACINHO)</t>
+  </si>
+  <si>
+    <t>SUPORTE LANTERNA LATERAL PARALAMA SCANIA</t>
+  </si>
+  <si>
+    <t>SUPORTE LANTERNA PARALAMA VOLVO</t>
+  </si>
+  <si>
+    <t>SUPORTE MANCAL CHAPA</t>
+  </si>
+  <si>
+    <t>SUPORTE MOLEJO DIANT RANDON</t>
+  </si>
+  <si>
+    <t>SUPORTE MOVEL BARRA CICLISTA LIBRELATO</t>
+  </si>
+  <si>
+    <t>SUPORTE PARALAMA CARRETA FACCHINI</t>
+  </si>
+  <si>
+    <t>SUPORTE PARALAMA CARRETA LIBRELATO</t>
+  </si>
+  <si>
+    <t>SUPORTE PARALAMA CARRETA RANDON</t>
+  </si>
+  <si>
+    <t>SUPORTE PARALAMA TRASEIRO SCANIA LD</t>
+  </si>
+  <si>
+    <t>SUPORTE PARALAMA TRASEIRO SCANIA LE</t>
+  </si>
+  <si>
+    <t>SUPORTE PARALAMA VOLVO (BASE INFERIOR)</t>
+  </si>
+  <si>
+    <t>SUPORTE PARALAMA VOLVO (BASE SUPERIOR)</t>
+  </si>
+  <si>
+    <t>SUPORTE PLACA CARRETA</t>
+  </si>
+  <si>
+    <t>SUPORTE PLACA LANTERNA VOLVO</t>
+  </si>
+  <si>
+    <t>SUPORTE SINALEIRA DIANTEIRA LIBRELATO LD</t>
+  </si>
+  <si>
+    <t>SUPORTE SINALEIRA DIANTEIRA LIBRELATO LE</t>
+  </si>
+  <si>
+    <t>SUPORTE TUBO PARALAMA VOLVO</t>
+  </si>
+  <si>
+    <t>TAMBOR DE FREIO LIBRELATO</t>
+  </si>
+  <si>
+    <t>TAMBOR DE FREIO RANDON (CAMPANA FREIO)</t>
+  </si>
+  <si>
+    <t>TAMPA ARLA SCANIA</t>
+  </si>
+  <si>
+    <t>TAMPA ARLA VOLVO (PLÁSTICO)</t>
+  </si>
+  <si>
+    <t>TAMPA COMBUSTIVEL VOLVO (PLÁSTICO)</t>
+  </si>
+  <si>
+    <t>TAMPA CATALISADOR</t>
+  </si>
+  <si>
+    <t>TAMPA COMBUSTIVEL SCANIA</t>
+  </si>
+  <si>
+    <t>TAMPA COMBUSTIVEL VOLVO</t>
+  </si>
+  <si>
+    <t>TAMPA CUBO RANDON 4 FUROS</t>
+  </si>
+  <si>
+    <t>TAMPA CUBO RANDON 5 FUROS</t>
+  </si>
+  <si>
+    <t>TAMPA CUICA (FUNDO INFERIOR)</t>
+  </si>
+  <si>
+    <t>TAMPA CUICA (FUNDO SUPERIOR) (COPO)</t>
+  </si>
+  <si>
+    <t>TAMPA DO CUBO FACCHINI</t>
+  </si>
+  <si>
+    <t>TAMPA DO CUBO LIBRELATO</t>
+  </si>
+  <si>
+    <t>TAMPA DO INTERCLIMA</t>
+  </si>
+  <si>
+    <t>TAMPA FEMEA EXTERNA (TAMPA DO MANCAL)</t>
+  </si>
+  <si>
+    <t>TAMPA LE (ACABAMENTO)</t>
+  </si>
+  <si>
+    <t>TAMPA MACHO INTERNA (TAMPA DO MANCAL)</t>
+  </si>
+  <si>
+    <t>TAMPA PROTETOR CICLISTA LIBRELATO</t>
+  </si>
+  <si>
+    <t>TAMPA PROTETOR CICLISTA RANDON</t>
+  </si>
+  <si>
+    <t>TAMPA VALVULA PNEU</t>
+  </si>
+  <si>
+    <t>TECLADO AUTOTRAC</t>
+  </si>
+  <si>
+    <t>TECNIL 5ª RODA  + 1010064470 (LANÇAR PARAFUSOS)</t>
+  </si>
+  <si>
     <t>TEE INSTANTANEO 8MM (UNIÃO T)</t>
   </si>
   <si>
-    <t>EMENDA REDUÇÃO 16X16</t>
-  </si>
-  <si>
-    <t>ENGATE CORRENTE (TRAVA CORRENTE)</t>
-  </si>
-  <si>
-    <t>ENGATE FEMEA FOMINHA RANDON (INFERIOR)</t>
-  </si>
-  <si>
-    <t>ENGATE FEMEA CARRETA (SUPERIOR)</t>
-  </si>
-  <si>
-    <t>ENGATE RÁPIDO 3/4 (MÃO AMIGA)</t>
-  </si>
-  <si>
-    <t>ENGATE REBOQUE SCANIA</t>
-  </si>
-  <si>
-    <t>ENGATE REBOQUE VOLVO (CJ)</t>
-  </si>
-  <si>
-    <t>ENGATE HIDRAULICO FEMEA LIBRELATO 1POL</t>
-  </si>
-  <si>
-    <t>ENGATE HIDRAULICO MACHO LIBRELATO 1POL</t>
-  </si>
-  <si>
-    <t>FILTRO DE AR EXTERNO SCANIA</t>
-  </si>
-  <si>
-    <t>FILTRO DE AR INTERNO SCANIA</t>
-  </si>
-  <si>
-    <t>FILTRO DE AR INTERNO VOLVO</t>
-  </si>
-  <si>
-    <t>FILTRO DE AR EXTERNO VOLVO</t>
-  </si>
-  <si>
-    <t>FITA CREPE LARGA</t>
-  </si>
-  <si>
-    <t>FITA DUPLA FACE 3M</t>
-  </si>
-  <si>
-    <t>FITA ZEBRADA</t>
-  </si>
-  <si>
-    <t>FITA DUREX</t>
-  </si>
-  <si>
-    <t>FITA TACÓGRAFO VOLVO EURO 5 (BOBINA)</t>
-  </si>
-  <si>
-    <t>FITA TACÓGRAFO VOLVO EURO 6 (BOBINA)</t>
-  </si>
-  <si>
-    <t>FLEXIVEL</t>
-  </si>
-  <si>
-    <t>FIXADOR SUPORTE PARALAMA VOLVO</t>
-  </si>
-  <si>
-    <t>FORQUILHA CUICA</t>
-  </si>
-  <si>
-    <t>FOLE PNEUM LIBRELATO (BEXIGA)</t>
-  </si>
-  <si>
-    <t>GANCHO FECHAMENTO ESFERICO</t>
-  </si>
-  <si>
-    <t>GAVIÃO 5ª RODA</t>
-  </si>
-  <si>
-    <t>GRAMPO U TRAVA SEGURANÇA CAÇAMBA</t>
-  </si>
-  <si>
-    <t>GRAMPO MOLEJO 7/8 (38)</t>
-  </si>
-  <si>
-    <t>PORCA P/GRAMPO MOLEJO (2UND)</t>
-  </si>
-  <si>
-    <t>GRAMPO PNEUMÁTICO</t>
-  </si>
-  <si>
-    <t>PORCA P/GRAMPO PNEUMATICO (4UND)</t>
-  </si>
-  <si>
-    <t>GRAXA LITIO 20KG (LANÇAR POR KG)</t>
-  </si>
-  <si>
-    <t>GRAXA TEXACO 170KG</t>
-  </si>
-  <si>
-    <t>JG DE LONA CARRETA RANDON</t>
-  </si>
-  <si>
-    <t>JG DE LONA DIANTEIRA CAVALO SCANIA</t>
-  </si>
-  <si>
-    <t>JG DE LONA TRAÇÃO CAVALO SCANIA</t>
-  </si>
-  <si>
-    <t>JG DE LONA CARRETA LIBRELATO</t>
-  </si>
-  <si>
-    <t>JUNTA 4 FUROS (LIBRELATO)</t>
-  </si>
-  <si>
-    <t>JUNTA CUBO 5 FUROS PEQ RANDON</t>
-  </si>
-  <si>
-    <t>JUNTA CUBO 5 FUROS GRANDE RANDON</t>
-  </si>
-  <si>
-    <t>KIT DE EMBREAGEM SCANIA</t>
-  </si>
-  <si>
-    <t>EMBREAGEM VOLVO</t>
+    <t>TERMINAL CONECTOR 2V</t>
+  </si>
+  <si>
+    <t>TERMINAL CONECTOR 5V</t>
+  </si>
+  <si>
+    <t>TERMINAL DE BATERIA(POLO)</t>
+  </si>
+  <si>
+    <t>TERMINAL DIREÇÃO (L/D)</t>
+  </si>
+  <si>
+    <t>TERMINAL DIREÇÃO (L/E)</t>
+  </si>
+  <si>
+    <t>TERMINAL HIDRAULICO MANG 3/4 FEMEA</t>
+  </si>
+  <si>
+    <t>TERMINAL HIDRAULICO MANG 3/4 MACHO</t>
+  </si>
+  <si>
+    <t>TERMINAL ISOL AUTOTRAC (CONECTOR PARA RELE 24V)</t>
+  </si>
+  <si>
+    <t>THINNER</t>
+  </si>
+  <si>
+    <t>TINTA BRANCO PU</t>
+  </si>
+  <si>
+    <t>TINTA PU PRETO CADILAC</t>
+  </si>
+  <si>
+    <t>TINTA SPRAY AZU 250GR</t>
+  </si>
+  <si>
+    <t>TINTA SPRAY BRANCO 250ML</t>
+  </si>
+  <si>
+    <t>TINTA SPRAY PRETO BRILHANTE</t>
+  </si>
+  <si>
+    <t>TIRA FINO RANDON</t>
+  </si>
+  <si>
+    <t>TIRANTE FIXO LIBRELATO (BRAÇO TENSOR)</t>
+  </si>
+  <si>
+    <t>TIRANTE FIXO RANDON (BRAÇO TENSOR)</t>
+  </si>
+  <si>
+    <t>TIRANTE REGULAGEM LIBRELATO (BRAÇO TENSOR)</t>
+  </si>
+  <si>
+    <t>TIRANTE REGULAGEM RANDON (BRAÇO TENSOR)</t>
+  </si>
+  <si>
+    <t>TOMADA ABS FÊMEA</t>
+  </si>
+  <si>
+    <t>TOMADA ABS MACHO</t>
+  </si>
+  <si>
+    <t>TOMADA FORÇA FÊMEA</t>
+  </si>
+  <si>
+    <t>TOMADA FORÇA MACHO</t>
+  </si>
+  <si>
+    <t>TRAVA ARANHA LIBRELATO</t>
+  </si>
+  <si>
+    <t>TRAVA ARANHA RANDON</t>
+  </si>
+  <si>
+    <t>TRAVA BICA</t>
+  </si>
+  <si>
+    <t>TRAVA CARROCERIA (PINO C/CORRENTE)</t>
+  </si>
+  <si>
+    <t>TRAVA ELASTICA</t>
+  </si>
+  <si>
+    <t>TRAVA MEIA LUA</t>
+  </si>
+  <si>
+    <t>TRAVA ROLETE</t>
+  </si>
+  <si>
+    <t>TRAVA TOMBADOR</t>
+  </si>
+  <si>
+    <t>TUBO NYLON 6MM</t>
+  </si>
+  <si>
+    <t>TUBO NYLON 8MM</t>
+  </si>
+  <si>
+    <t>UNIÃO 10 MM</t>
+  </si>
+  <si>
+    <t>UNIÃO 12MM</t>
+  </si>
+  <si>
+    <t>UNIÃO 6MM</t>
+  </si>
+  <si>
+    <t>UNIÃO 8MM</t>
+  </si>
+  <si>
+    <t>UNIÃO ANTEPARRO 8X16MM</t>
+  </si>
+  <si>
+    <t>UNIÃO T 6MM</t>
+  </si>
+  <si>
+    <t>VALVULA BLOQUEIO</t>
+  </si>
+  <si>
+    <t>VALVULA DESCARGA RAPIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVULA DRENO </t>
+  </si>
+  <si>
+    <t>VALVULA EMERGENCIA</t>
+  </si>
+  <si>
+    <t>VALVULA LIBERAÇÃO CARRETA</t>
+  </si>
+  <si>
+    <t>VALVULA PUSH PULL (ACIONAMENTO CARRETA)</t>
+  </si>
+  <si>
+    <t>VALVULA RELE</t>
+  </si>
+  <si>
+    <t>VÁLVULA RELE C/ SOLENOIDE</t>
+  </si>
+  <si>
+    <t>VALVULA RETENÇÃO FLUAIR</t>
   </si>
   <si>
     <t>VALVULA SOLEN CAM FH4 VADEN/306010041</t>
   </si>
   <si>
-    <t>ROLAMENTO FIX ESF;30X72X19MM;AC;6306ZZC3</t>
-  </si>
-  <si>
-    <t>MANCAL SACHS/3315</t>
-  </si>
-  <si>
-    <t>KIT REPARO CATRACA FREIO AUTOMATICA</t>
-  </si>
-  <si>
-    <t>KIT REPARO EIXO S (BUCHA EIXO S)</t>
-  </si>
-  <si>
-    <t>KIT TAPA PO RANDON (PAR DE ESPELHO)</t>
-  </si>
-  <si>
-    <t>KIT TAPA PO FACCHINI LE (ESPELHO)</t>
-  </si>
-  <si>
-    <t>KIT TAPA PO FACCHINI LD (ESPELHO)</t>
-  </si>
-  <si>
-    <t>LOCTITTE (TRAVA PARAFUSO)</t>
-  </si>
-  <si>
-    <t>MANIFOLD 2 VIAS</t>
-  </si>
-  <si>
-    <t>MANCAL EXTERNO EIXO S</t>
-  </si>
-  <si>
-    <t>MANCAL INTERNO EIXO S (SPIDER)</t>
-  </si>
-  <si>
-    <t>MANCAL EXT DA BALANÇA (ANEL APOIO)</t>
-  </si>
-  <si>
-    <t>MANCAL INT DA BALANÇA (ANEL ACO PIN)</t>
-  </si>
-  <si>
-    <t>MANGUEIRA ESPIRAL AMARELO</t>
-  </si>
-  <si>
-    <t>MANGUEIRA ESPIRAL VERMELHO</t>
-  </si>
-  <si>
-    <t>MANGUEIRA 3/4</t>
-  </si>
-  <si>
-    <t>MANGUEIRA 1/4</t>
-  </si>
-  <si>
-    <t>MANGUEIRA HIDR 1 POL</t>
-  </si>
-  <si>
-    <t>MANIVELA ESFÉRICO ENG DOLLY (L/D)</t>
-  </si>
-  <si>
-    <t>MANIVELA ESFÉRICO ENG DOLLY (L/E)</t>
-  </si>
-  <si>
-    <t>MEIO PARALAMA DE-TD CARRETA FACCHINI</t>
-  </si>
-  <si>
-    <t>MEIO PARALAMA DD-TE CARRETA FACCHINI</t>
-  </si>
-  <si>
-    <t>MOLA CUICA G</t>
-  </si>
-  <si>
-    <t>MOLA CUICA P</t>
-  </si>
-  <si>
-    <t>MOLA DUPLA 5ª RODA RETORNO</t>
-  </si>
-  <si>
-    <t>MOLA GARRA TRAVAMENTO (MOLA P/ 5ª RODA)</t>
-  </si>
-  <si>
-    <t>MOLA MESTRE (GROSSA)</t>
-  </si>
-  <si>
-    <t>MOLA MESTRE TRAÇÃO VOLVO</t>
-  </si>
-  <si>
-    <t>MOLA PATIM G</t>
-  </si>
-  <si>
-    <t>MOLA PATIM P</t>
-  </si>
-  <si>
-    <t>MOLA PNEUM CABIN R500 SCANIA DIANTEIRA</t>
-  </si>
-  <si>
-    <t>MOLA PNEUM CABIN R500 TRASEIRA (BEXIGA)</t>
-  </si>
-  <si>
-    <t>MOLA PNEUM PEQ 32/33MM (FOLE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOLA PNEUM G 38MM (FOLE) </t>
-  </si>
-  <si>
-    <t>MOLA REGULAGEM TRAVA CAÇAMBA (MOLA TAMPA)</t>
-  </si>
-  <si>
-    <t>NIPLE MACHO 16MM</t>
-  </si>
-  <si>
-    <t>ÓLEO 68 (20L) (LANÇAR POR LITRO)</t>
-  </si>
-  <si>
-    <t>ÓLEO ATF FLUIDO DIREÇÃO</t>
-  </si>
-  <si>
-    <t>ÓLEO PNEUMÁTICO</t>
-  </si>
-  <si>
-    <t>PAINEL PNEUMÁTICO (CX DE COMANDO)</t>
-  </si>
-  <si>
-    <t>PARAFUSO 10X30</t>
-  </si>
-  <si>
-    <t>PARAFUSO 10X40</t>
-  </si>
-  <si>
-    <t>PARAFUSO 10X60</t>
-  </si>
-  <si>
-    <t>PARAFUSO 10X60 (CUICA)</t>
-  </si>
-  <si>
-    <t>PARAFUSO 10X70</t>
-  </si>
-  <si>
-    <t>PARAFUSO 12X40</t>
-  </si>
-  <si>
-    <t>PARAFUSO 16X65</t>
-  </si>
-  <si>
-    <t>PARAFUSO 16X70</t>
-  </si>
-  <si>
-    <t>PARAFUSO 4MM</t>
-  </si>
-  <si>
-    <t>PARAFUSO 5ª RODA</t>
-  </si>
-  <si>
-    <t>PARAF AJUSTE 5ª RODA (REGULAGEM)</t>
-  </si>
-  <si>
-    <t>GUIA PARAF REGULAGEM 5ª RODA</t>
-  </si>
-  <si>
-    <t>PARAFUSO 6X30</t>
-  </si>
-  <si>
-    <t>PARAFUSO 6X40</t>
-  </si>
-  <si>
-    <t>PARAFUSO 6X80</t>
-  </si>
-  <si>
-    <t>PARAFUSO 8X30</t>
-  </si>
-  <si>
-    <t>PARAFUSO 8X40</t>
-  </si>
-  <si>
-    <t>PARAFUSO 8X50</t>
-  </si>
-  <si>
-    <t>PARAFUSO 8X60</t>
-  </si>
-  <si>
-    <t>PARAFUSO 8X70</t>
-  </si>
-  <si>
-    <t>PARAFUSO 8X80</t>
-  </si>
-  <si>
-    <t>PARAF CAB FRANC 5/16X2P 3/4</t>
-  </si>
-  <si>
-    <t>PARAF CAB FRANC PORC 5/16X3P</t>
-  </si>
-  <si>
-    <t>PARAFUSO BROCANTE</t>
-  </si>
-  <si>
-    <t>PARAFUSO PHILLIPS 4X30MM</t>
-  </si>
-  <si>
-    <t>PARAFUSO BARRA DE TRAVAMENTO</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE REGULAGEM DO ESFÉRICO</t>
-  </si>
-  <si>
-    <t>PARAFUSO 20X100MM</t>
-  </si>
-  <si>
-    <t>PARAFUSO 16X130MM</t>
-  </si>
-  <si>
-    <t>PARAFUSO  16X150MM</t>
-  </si>
-  <si>
-    <t>PARAFUSO DO PINO REI</t>
-  </si>
-  <si>
-    <t>PARALAMA CARRETA RANDON</t>
-  </si>
-  <si>
-    <t>PARALAMA TRASEIRO CABINE SCANIA LD</t>
-  </si>
-  <si>
-    <t>PARALAMA TRAÇÃO CAVALO SCANIA</t>
-  </si>
-  <si>
-    <t>PARALAMA VOLVO MEIO PARALAMA (PARTE DE BAIXO)</t>
-  </si>
-  <si>
-    <t>PARALAMA VOLVO 2ª PARTE (PARTE DE CIMA)</t>
-  </si>
-  <si>
-    <t>PARALAMA CARRETA LIBRELATO</t>
-  </si>
-  <si>
-    <t>PARALAMA CARRETA FACCHINI</t>
-  </si>
-  <si>
-    <t>PATIM DE FREIO LIBRELATO</t>
-  </si>
-  <si>
-    <t>PATIM DE FREIO RANDON</t>
-  </si>
-  <si>
-    <t>PE APOIO DOLLY</t>
-  </si>
-  <si>
-    <t>PINO DA BALANÇA (PARAFUSO)</t>
-  </si>
-  <si>
-    <t>PORCA PINO BALANÇA</t>
-  </si>
-  <si>
-    <t>PINO DE CENTRO</t>
-  </si>
-  <si>
-    <t>PORCA PINO DE CENTRO (1UND)</t>
-  </si>
-  <si>
-    <t>PINO ENGATE ESFÉRICO (BOLA DO ESFÉRICO)</t>
-  </si>
-  <si>
-    <t>PRESILHA DO FUEIRO TIPO U (POMPOM)</t>
-  </si>
-  <si>
-    <t>PISTOLA DE AR</t>
-  </si>
-  <si>
-    <t>PINO DO REBOQUE SCANIA</t>
-  </si>
-  <si>
-    <t>PINO TIRANTE (TENSOR)</t>
-  </si>
-  <si>
-    <t>PORCA PINO TIRANTE (1UND)</t>
-  </si>
-  <si>
-    <t>PONTEIRA BARRA CICLISTA RANDON</t>
-  </si>
-  <si>
-    <t>PONTEIRA BARRA CICLISTA LIBRELATO</t>
-  </si>
-  <si>
-    <t>PONTEIRA ENGATE ESFÉRICO</t>
-  </si>
-  <si>
-    <t>PONTEIRA MANGUEIRA 1POL (TERMINAL FEMEA)</t>
-  </si>
-  <si>
-    <t>PONTEIRA CURVA 3/4</t>
-  </si>
-  <si>
-    <t>PORCA 4MM SIMPLES</t>
-  </si>
-  <si>
-    <t>PORCA 6MM SIMPLES</t>
-  </si>
-  <si>
-    <t>PORCA 6MM TRAVANTE</t>
-  </si>
-  <si>
-    <t>PORCA 8MM TRAVANTE</t>
-  </si>
-  <si>
-    <t>PORCA 8MM SIMPLES</t>
-  </si>
-  <si>
-    <t>PORCA 10MM TRAVANTE</t>
-  </si>
-  <si>
-    <t>PORCA 12MM TRAVANTE</t>
-  </si>
-  <si>
-    <t>PORCA 14MM TRAVANTE</t>
-  </si>
-  <si>
-    <t>PORCA 20MM TRAVANTE</t>
-  </si>
-  <si>
-    <t>PORCA CASTELADA RANDON (PORCA DO EIXO 80)</t>
-  </si>
-  <si>
-    <t>PORCA CASTELADA LIBRELATO (PORCA DO EIXO DO CUBO)</t>
-  </si>
-  <si>
-    <t>PRATO PNEUMATICO RANDON SUPERIOR 33MM</t>
-  </si>
-  <si>
-    <t>PRATO PNEUMATICO RANDON INFERIOR 33MM</t>
-  </si>
-  <si>
-    <t>PRATO PNEUMATICO LIBRELATO INFERIOR 38MM</t>
-  </si>
-  <si>
-    <t>PRATO PNEUMATICO LIBRELATO SUPERIOR 38MM</t>
-  </si>
-  <si>
-    <t>PRESILHA DA CORRENTE "V" ESTREITO (TAMPA)</t>
-  </si>
-  <si>
-    <t>PRESILHA DA CORRENTE "V" LARGO (fueiro)</t>
-  </si>
-  <si>
-    <t>PINO REI 2P FLANGEADO RANDON</t>
-  </si>
-  <si>
-    <t>REDUCAO MACH/FEM 22X16MM</t>
-  </si>
-  <si>
-    <t>REBITE ALUMINIO</t>
-  </si>
-  <si>
-    <t>REPARO CENTRAL DA CUICA CARRETA</t>
-  </si>
-  <si>
-    <t>REPARO CUICAO DIANTEIRA</t>
-  </si>
-  <si>
-    <t>REPARO CUICÃO TRAÇÃO</t>
-  </si>
-  <si>
-    <t>REPARO DA VAVULA PUSH (BOTÃO PRETO)</t>
-  </si>
-  <si>
-    <t>REPARO DA VALV COMANDO LIBRELATO (QA-448MP)</t>
-  </si>
-  <si>
-    <t>REPARO DESMONTAGEM CARRETA (EMERGENCIA)</t>
-  </si>
-  <si>
-    <t>RETENTOR</t>
-  </si>
-  <si>
-    <t>ROLAMENTO BARRA TORÇÃO VOLVO P</t>
-  </si>
-  <si>
-    <t>ROLAMENTO BARRA TORÇÃO VOLVO G</t>
-  </si>
-  <si>
-    <t>ROLAMENTO G (INTERNO)</t>
-  </si>
-  <si>
-    <t>ROLAMENTO P (EXTERNO)</t>
-  </si>
-  <si>
-    <t>ROLAMENTO FACCHINI 33021</t>
-  </si>
-  <si>
-    <t>ROLETE 32MM</t>
-  </si>
-  <si>
-    <t>ROLETE FLANGE (PINO SAPATA)</t>
-  </si>
-  <si>
-    <t>SENSOR ABS CARRETA</t>
-  </si>
-  <si>
-    <t>SIRENE AUTOTRAC</t>
-  </si>
-  <si>
-    <t>SUPORTE MANCAL CHAPA</t>
-  </si>
-  <si>
-    <t>SUPORTE ACO CARRETA RANDON (CUICA)</t>
-  </si>
-  <si>
-    <t>SUPORTE CX FERRAMENTA LE</t>
-  </si>
-  <si>
-    <t>SUPORTE CX FERRAMENTA  LD</t>
-  </si>
-  <si>
-    <t>SUPORTE G DAS TAMPAS (ENGATE)</t>
-  </si>
-  <si>
-    <t>SUPORTE PARALAMA CARRETA RANDON</t>
-  </si>
-  <si>
-    <t>SUPORTE PARALAMA CARRETA LIBRELATO</t>
-  </si>
-  <si>
-    <t>SUPORTE PARALAMA CARRETA FACCHINI</t>
-  </si>
-  <si>
-    <t>SUPORTE CENTRAL PARALAMA SCANIA</t>
-  </si>
-  <si>
-    <t>SUPORTE CENTRAL PARALAMA VOLVO</t>
-  </si>
-  <si>
-    <t>SUPORTE TUBO PARALAMA VOLVO</t>
-  </si>
-  <si>
-    <t>SUPORTE PARALAMA VOLVO (BASE INFERIOR)</t>
-  </si>
-  <si>
-    <t>SUPORTE PARALAMA VOLVO (BASE SUPERIOR)</t>
-  </si>
-  <si>
-    <t>SUPORTE PARALAMA TRASEIRO SCANIA LD</t>
-  </si>
-  <si>
-    <t>SUPORTE PARALAMA TRASEIRO SCANIA LE</t>
-  </si>
-  <si>
-    <t>SUPORTE MOLEJO DIANT RANDON</t>
-  </si>
-  <si>
-    <t>SUPORTE PLACA CARRETA</t>
-  </si>
-  <si>
-    <t>SUPORTE PLACA LANTERNA VOLVO</t>
-  </si>
-  <si>
-    <t>SUPORTE SINALEIRA DIANTEIRA LIBRELATO LD</t>
-  </si>
-  <si>
-    <t>SUPORTE SINALEIRA DIANTEIRA LIBRELATO LE</t>
-  </si>
-  <si>
-    <t>SUPORTE LANTERNA LAT LIBRELATO (BRACINHO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE LANTERNA DOLLY DIANTEIRA (BRACINHO) </t>
-  </si>
-  <si>
-    <t>SUPORTE LANTERNA DOLLY TRASEIRO LD (RANDON)</t>
-  </si>
-  <si>
-    <t>SUPORTE LANTERNA DOLLY TRASEIRO LE (RANDON)</t>
-  </si>
-  <si>
-    <t>SUPORTE LANTERNA BASCULANTE FACCHINI LD</t>
-  </si>
-  <si>
-    <t>SUPORTE LANTERNA BASCULANTE FACCHINI LE</t>
-  </si>
-  <si>
-    <t>SUPORTE LANTERNA DIANT DOLLY FACCHINI LD</t>
-  </si>
-  <si>
-    <t>SUPORTE LANTERNA DIANT DOLLY FACCHINI LE</t>
-  </si>
-  <si>
-    <t>SUPORTE LANTERNA PARALAMA VOLVO</t>
-  </si>
-  <si>
-    <t>SUPORTE LANTERNA LATERAL PARALAMA SCANIA</t>
-  </si>
-  <si>
-    <t>SUPORTE FIXO BARRA CICLISTA LIBRELATO</t>
-  </si>
-  <si>
-    <t>SUPORTE MOVEL BARRA CICLISTA LIBRELATO</t>
-  </si>
-  <si>
-    <t>SUPORTE BARRA CICLISTA RANDON</t>
-  </si>
-  <si>
-    <t>TAMBOR DE FREIO LIBRELATO</t>
-  </si>
-  <si>
-    <t>TAMPA CUICA (FUNDO INFERIOR)</t>
-  </si>
-  <si>
-    <t>TAMPA CUICA (FUNDO SUPERIOR) (COPO)</t>
-  </si>
-  <si>
-    <t>TAMPA ARLA SCANIA</t>
-  </si>
-  <si>
-    <t>TAMPA ARLA VOLVO</t>
-  </si>
-  <si>
-    <t>TAMPA ARLA VOLVO (PLÁSTICO)</t>
-  </si>
-  <si>
-    <t>TAMPA CATALISADOR</t>
-  </si>
-  <si>
-    <t>TAMPA COMBUSTIVEL VOLVO</t>
-  </si>
-  <si>
-    <t>TAMPA COMBUSTIVEL SCANIA</t>
-  </si>
-  <si>
-    <t>TAMPA CUBO RANDON 4 FUROS</t>
-  </si>
-  <si>
-    <t>TAMPA CUBO RANDON 5 FUROS</t>
-  </si>
-  <si>
-    <t>TAMPA DO CUBO LIBRELATO</t>
-  </si>
-  <si>
-    <t>TAMPA DO CUBO FACCHINI</t>
-  </si>
-  <si>
-    <t>TAMPA LE (ACABAMENTO)</t>
-  </si>
-  <si>
-    <t>TAMPA MACHO INTERNA (TAMPA DO MANCAL)</t>
-  </si>
-  <si>
-    <t>TAMPA FEMEA EXTERNA (TAMPA DO MANCAL)</t>
-  </si>
-  <si>
-    <t>TAMPA PROTETOR CICLISTA RANDON</t>
-  </si>
-  <si>
-    <t>TAMPA PROTETOR CICLISTA LIBRELATO</t>
-  </si>
-  <si>
-    <t>TERMINAL HIDRAULICO MANG 3/4 FEMEA</t>
-  </si>
-  <si>
-    <t>TERMINAL HIDRAULICO MANG 3/4 MACHO</t>
-  </si>
-  <si>
-    <t>TECLADO AUTOTRAC</t>
-  </si>
-  <si>
-    <t>TECNIL 5ª RODA  + 1010064470 (LANÇAR PARAFUSOS)</t>
-  </si>
-  <si>
-    <t>PARAFUSO DO TECNIL 5ª RODA</t>
-  </si>
-  <si>
-    <t>TERMINAL DIREÇÃO (L/D)</t>
-  </si>
-  <si>
-    <t>TERMINAL DIREÇÃO (L/E)</t>
-  </si>
-  <si>
-    <t>TERMINAL ISOL AUTOTRAC (CONECTOR PARA RELE 24V)</t>
-  </si>
-  <si>
-    <t>TIRANTE REGULAGEM RANDON (BRAÇO TENSOR)</t>
-  </si>
-  <si>
-    <t>TIRA FINO RANDON</t>
-  </si>
-  <si>
-    <t>TIRANTE FIXO RANDON (BRAÇO TENSOR)</t>
-  </si>
-  <si>
-    <t>TIRANTE FIXO LIBRELATO (BRAÇO TENSOR)</t>
-  </si>
-  <si>
-    <t>TIRANTE REGULAGEM LIBRELATO (BRAÇO TENSOR)</t>
-  </si>
-  <si>
-    <t>TUBO NYLON 6MM</t>
-  </si>
-  <si>
-    <t>TUBO NYLON 8MM</t>
-  </si>
-  <si>
-    <t>TRAVA ARANHA RANDON</t>
-  </si>
-  <si>
-    <t>TRAVA ARANHA LIBRELATO</t>
-  </si>
-  <si>
-    <t>TRAVA BICA</t>
-  </si>
-  <si>
-    <t>TRAVA CARROCERIA (PINO C/CORRENTE)</t>
-  </si>
-  <si>
-    <t>TRAVA ELASTICA</t>
-  </si>
-  <si>
-    <t>TRAVA MEIA LUA</t>
-  </si>
-  <si>
-    <t>TRAVA ROLETE</t>
-  </si>
-  <si>
-    <t>TRAVA TOMBADOR</t>
-  </si>
-  <si>
-    <t>UNIÃO 12MM</t>
-  </si>
-  <si>
-    <t>UNIÃO 6MM</t>
-  </si>
-  <si>
-    <t>UNIÃO 8MM</t>
-  </si>
-  <si>
-    <t>UNIÃO ANTEPARRO 8X16MM</t>
-  </si>
-  <si>
-    <t>INSERT 6MM</t>
-  </si>
-  <si>
-    <t>INSERT 8MM</t>
-  </si>
-  <si>
-    <t>INSERT 16MM</t>
-  </si>
-  <si>
-    <t>UNIÃO 10 MM</t>
-  </si>
-  <si>
-    <t>UNIÃO T 6MM</t>
-  </si>
-  <si>
-    <t>VALVULA BLOQUEIO</t>
-  </si>
-  <si>
-    <t>VALVULA DESCARGA RAPIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVULA DRENO </t>
-  </si>
-  <si>
-    <t>VALVULA EMERGENCIA</t>
-  </si>
-  <si>
-    <t>VALVULA PUSH PULL (ACIONAMENTO CARRETA)</t>
-  </si>
-  <si>
-    <t>VALVULA RELE</t>
-  </si>
-  <si>
-    <t>VÁLVULA RELE C/ SOLENOIDE</t>
-  </si>
-  <si>
-    <t>VALVULA RETENÇÃO FLUAIR</t>
-  </si>
-  <si>
-    <t>VALVULA LIBERAÇÃO CARRETA</t>
-  </si>
-  <si>
-    <t>SIRENE DE RÉ</t>
-  </si>
-  <si>
     <t>VALVULA TRANSFERÊNCIA</t>
   </si>
   <si>
-    <t>CADEADO 25MM</t>
-  </si>
-  <si>
-    <t>CINTA</t>
-  </si>
-  <si>
-    <t>Operação Pluma</t>
-  </si>
-  <si>
-    <t>CORDA (METROS)</t>
-  </si>
-  <si>
-    <t>DESINGRIPANTE</t>
-  </si>
-  <si>
-    <t>ESPUMA EXPANSIVA</t>
-  </si>
-  <si>
-    <t>GANCHO DE LONA (LIGA)</t>
-  </si>
-  <si>
-    <t>LONA EMBORRACHADA GRANELEIRO</t>
-  </si>
-  <si>
-    <t>LONA PROT COB PVC AZ - (LONA FÁCIL)</t>
-  </si>
-  <si>
-    <t>REDE CONTENÇÃO PLUMA</t>
-  </si>
-  <si>
-    <t>ABRAÇADEIRA</t>
-  </si>
-  <si>
-    <t>Elétrica</t>
-  </si>
-  <si>
-    <t>BOMBA INTERCLIMA SCANIA</t>
-  </si>
-  <si>
-    <t>BOMBA DO INTERCLIMA VOLVO</t>
-  </si>
-  <si>
-    <t>BOMBA LIMPADOR PARABRISA SCANIA</t>
-  </si>
-  <si>
-    <t>BATERIA 220AMP MOURA (VOLVO SCANIA SUPER)</t>
-  </si>
-  <si>
-    <t>BATERIA 225AMP (VOLVO e SCANIA SUPER)</t>
-  </si>
-  <si>
-    <t>BATERIA 180AMP (SCANIA R500)</t>
-  </si>
-  <si>
-    <t>CABO 2X1 (LANÇAR POR METRO)</t>
-  </si>
-  <si>
-    <t>CABO 7X1 (LANÇAR POR METRO)</t>
-  </si>
-  <si>
-    <t>CABO P/RASTR RASTR AUTOTRAC/2730</t>
-  </si>
-  <si>
-    <t>CAIXA LAD DIR LANTERNA RANDON</t>
-  </si>
-  <si>
-    <t>RETROREFLETOR CX LADO DIREITO</t>
-  </si>
-  <si>
-    <t>CAIXA LAD ESQ LANTERNA RANDON</t>
-  </si>
-  <si>
-    <t>RETROREFLETOR CX LADO ESQUERDO</t>
-  </si>
-  <si>
-    <t>CHICOTE 7 P COBR/PLAST CARR DNI/DNI8355 (CHICOTE ABS COMPLETO)</t>
-  </si>
-  <si>
-    <t>CHICOTE 7 VIAS SIMPLES (CABO ASPIRAL)</t>
-  </si>
-  <si>
-    <t>CHICOTE 7 VIAS LANTERNA CAVALO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHICOTE CONECTOR LANTERNA TRAS FACCHINI LD </t>
-  </si>
-  <si>
-    <t>CHICOTE CONECTOR LANTERNA TRAS FACCHINI LE</t>
-  </si>
-  <si>
-    <t>CHICOTE 2 VIAS INJEÇÃO ELETRONICA</t>
-  </si>
-  <si>
-    <t>CHICOTE 4 VIAS RAINHA (ABS)</t>
-  </si>
-  <si>
-    <t>ELETRODO 2.50MM (5KG)</t>
-  </si>
-  <si>
-    <t>ELETRODO 3.25MM (5KG)</t>
-  </si>
-  <si>
-    <t>FITA ISOLANTE</t>
-  </si>
-  <si>
-    <t>FITA VEDA ROSCA</t>
-  </si>
-  <si>
-    <t>FUSIVEL 10 AMPERES</t>
-  </si>
-  <si>
-    <t>FUSIVEL 15 AMPERES</t>
-  </si>
-  <si>
-    <t>FUSIVEL VAMPIRINHO 20A (VOLVO)</t>
-  </si>
-  <si>
-    <t>FUSIVEL VAMPIRINHO 10A (VOLVO)</t>
-  </si>
-  <si>
-    <t>LAMPADA H7</t>
-  </si>
-  <si>
-    <t>LAMPADA MEIA LUZ VOLVO (LAMP 67)</t>
-  </si>
-  <si>
-    <t>LÂMPADA MINIAT1141</t>
-  </si>
-  <si>
-    <t>LANTERNA DE PLACA</t>
-  </si>
-  <si>
-    <t>LANT TRASEIRA SCANIA R500 LD</t>
-  </si>
-  <si>
-    <t>LANT TRASEIRA SCANIA R500  LE</t>
-  </si>
-  <si>
-    <t>LANTERNA SCANIA SUPER LD</t>
-  </si>
-  <si>
-    <t>LANTERNA SCANIA SUPER LE</t>
-  </si>
-  <si>
-    <t>LANT TRASEIRA VOLVO LE</t>
-  </si>
-  <si>
-    <t>LANT TRASEIRA VOLVO LD</t>
-  </si>
-  <si>
-    <t>LANTERNA CRISTAL RANDON</t>
-  </si>
-  <si>
-    <t>LANTERNA CRISTAL LIBRELATO</t>
-  </si>
-  <si>
-    <t>LANTERNA LAT C/SUPORTE RANDON</t>
-  </si>
-  <si>
-    <t>LANTERNA LAT S/SUPORTE RANDON</t>
-  </si>
-  <si>
-    <t>LANTERNA LAT C/SUPORTE LIBRELATO</t>
-  </si>
-  <si>
-    <t>LANTERNA LAT S/SUPORTE LIBRELATO</t>
-  </si>
-  <si>
-    <t>LANTERNA LAT TANQUE (DELIMITADORA)</t>
-  </si>
-  <si>
-    <t>LENTE LANT TRAS CAMINHAO VOLVO/20425732</t>
-  </si>
-  <si>
-    <t>LIMPA CONTATO (SO PARA ELÉTRICA)</t>
-  </si>
-  <si>
-    <t>MINI RELE AUXILIAR 24V</t>
-  </si>
-  <si>
-    <t>MODULO DE FREIO RANDON</t>
-  </si>
-  <si>
-    <t>MODULO DE FREIO FACCHINI</t>
-  </si>
-  <si>
-    <t>MODULO DE FREIO RANDON CAÇAMBA NEW R LE</t>
-  </si>
-  <si>
-    <t>MODULO DE FREIO RANDON CAÇAMBA NEW R LD</t>
-  </si>
-  <si>
-    <t>MOTOR INTERCLIMA SCANIA</t>
-  </si>
-  <si>
-    <t>PALHA INTERCLIMA SCANIA</t>
-  </si>
-  <si>
-    <t>PALHETA PARABRISA</t>
-  </si>
-  <si>
-    <t>RESERVATORIO INTERCLIMA</t>
-  </si>
-  <si>
-    <t>SILICONE PRETO</t>
-  </si>
-  <si>
-    <t>TERMINAL CONECTOR 2V</t>
-  </si>
-  <si>
-    <t>TERMINAL CONECTOR 5V</t>
-  </si>
-  <si>
-    <t>TOMADA FORÇA FÊMEA</t>
-  </si>
-  <si>
-    <t>TOMADA FORÇA MACHO</t>
-  </si>
-  <si>
-    <t>TOMADA ABS MACHO</t>
-  </si>
-  <si>
-    <t>TOMADA ABS FÊMEA</t>
-  </si>
-  <si>
-    <t>TERMINAL DE BATERIA(POLO)</t>
-  </si>
-  <si>
-    <t>TAMPA DO INTERCLIMA</t>
-  </si>
-  <si>
-    <t>LANTERNA DO ABS (LANTERNA VERDE)</t>
-  </si>
-  <si>
-    <t>ALONGADOR (EXTENSOR DE BICO)</t>
-  </si>
-  <si>
-    <t>Borracharia</t>
-  </si>
-  <si>
-    <t>BICO DE RODA CAVALO</t>
-  </si>
-  <si>
-    <t>BICO PNEU (RODA FERRO CARRETA)</t>
-  </si>
-  <si>
-    <t>CALIBRADOR PR C/HAST INDIC;FIX ANG;7188F</t>
-  </si>
-  <si>
-    <t>INFLADOR DE ENCHER PNEU</t>
-  </si>
-  <si>
-    <t>ESCOVA ROTATIVA 7P (P/LIXADEIRA)</t>
-  </si>
-  <si>
-    <t>TAMPA VALVULA PNEU</t>
-  </si>
-  <si>
-    <t>NÚCLEO CURTO VÁLV. PNEU</t>
-  </si>
-  <si>
-    <t>PORCA PARAF DE RODA</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE RODA CARRETA RANDON</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE RODA CARRETA LIBRELATTO</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE RODA DIANTEIRA SCANIA</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE RODA TRAÇÃO SCANIA</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE RODA DIANTEIRA VOLVO</t>
-  </si>
-  <si>
-    <t>PARAFUSO DA TRAÇÃO VOLVO</t>
-  </si>
-  <si>
-    <t>PNEU VULCANIZADO</t>
-  </si>
-  <si>
-    <t>PNEU LISO NOVO</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO NOVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNEU BORRACHUDO BONIN RT78 (RECAPADO) </t>
-  </si>
-  <si>
-    <t>PNEU LISO BONIN RT51 (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO FOX TMD (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO FOX BTL3B (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO VIPAL VL110 (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO VIPAL BANDA NOVA VL130 (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO VIPAL VRT2 (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO VIPAL  VT100 (RECAPADO)</t>
-  </si>
-  <si>
-    <t>RODA 22,5X8,25 295 10 FUROS</t>
-  </si>
-  <si>
-    <t>SACA VÁLVULA</t>
-  </si>
-  <si>
     <t xml:space="preserve">VASELINA VEGETAL 3KG </t>
-  </si>
-  <si>
-    <t>DISCO CORTE 7 POLEGADAS DEWALT</t>
-  </si>
-  <si>
-    <t>Tintas</t>
-  </si>
-  <si>
-    <t>DISCO CORTE 4 POLEGADAS DEWALT</t>
-  </si>
-  <si>
-    <t>DISCO FLAP 7 POLEGADAS</t>
-  </si>
-  <si>
-    <t>DISCO FLAP 4 POLEGADAS</t>
-  </si>
-  <si>
-    <t>DISCO DESBASTE 7P</t>
-  </si>
-  <si>
-    <t>DISCO ROQUITE 80</t>
-  </si>
-  <si>
-    <t>ESTOPA (LANÇAR POR UND)</t>
-  </si>
-  <si>
-    <t>ESCOVA  AÇO CABO PLAST</t>
-  </si>
-  <si>
-    <t>FAIXA REFLET LE 3M HB004037097</t>
-  </si>
-  <si>
-    <t>FAIXA REFLET LD 3M HB004037105</t>
-  </si>
-  <si>
-    <t>FAIXA REFLETIVA PARACHOQUE</t>
-  </si>
-  <si>
-    <t>LIXA OURO 120</t>
-  </si>
-  <si>
-    <t>LIXA OURO 220</t>
-  </si>
-  <si>
-    <t>LIXA FERRO N120 225X275MM</t>
-  </si>
-  <si>
-    <t>PINCEL</t>
-  </si>
-  <si>
-    <t>THINNER</t>
-  </si>
-  <si>
-    <t>TINTA BRANCO PU</t>
-  </si>
-  <si>
-    <t>TINTA PU PRETO CADILAC</t>
-  </si>
-  <si>
-    <t>TINTA SPRAY BRANCO 250ML</t>
-  </si>
-  <si>
-    <t>TINTA SPRAY PRETO BRILHANTE</t>
-  </si>
-  <si>
-    <t>TINTA SPRAY AZU 250GR</t>
-  </si>
-  <si>
-    <t>REBITE DE FERRRO</t>
-  </si>
-  <si>
-    <t>PORCA 16MM TRAVANTE ROSCA FINA</t>
-  </si>
-  <si>
-    <t>PORCA SEXT AUTO TRAV 16MM ROSCA GROSSA</t>
   </si>
 </sst>
 </file>
@@ -1864,7 +1867,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1952,20 +1955,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2246,7 +2248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1221"/>
+  <dimension ref="A1:I1222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2267,10 +2269,10 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
-        <v>1010008578</v>
+        <v>1010008637</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>404</v>
+        <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
@@ -2281,9 +2283,9 @@
         <v>1040019909</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2292,7 +2294,7 @@
         <v>1040023837</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>4</v>
@@ -2304,7 +2306,7 @@
         <v>1040023836</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>4</v>
@@ -2316,7 +2318,7 @@
         <v>1010000216</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>4</v>
@@ -2327,10 +2329,10 @@
         <v>1010022119</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>472</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
       <c r="F7" s="25"/>
     </row>
@@ -2339,7 +2341,7 @@
         <v>1010058682</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>4</v>
@@ -2350,7 +2352,7 @@
         <v>1010077386</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>4</v>
@@ -2362,7 +2364,7 @@
         <v>1010059706</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>4</v>
@@ -2373,7 +2375,7 @@
         <v>423651</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>4</v>
@@ -2384,7 +2386,7 @@
         <v>1040083308</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>4</v>
@@ -2395,7 +2397,7 @@
         <v>417715</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>4</v>
@@ -2406,7 +2408,7 @@
         <v>1010062075</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>4</v>
@@ -2417,7 +2419,7 @@
         <v>1010058325</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>4</v>
@@ -2428,7 +2430,7 @@
         <v>1010061986</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>4</v>
@@ -2439,7 +2441,7 @@
         <v>1040017265</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>4</v>
@@ -2450,7 +2452,7 @@
         <v>1040077346</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>4</v>
@@ -2461,7 +2463,7 @@
         <v>1010049326</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>4</v>
@@ -2472,7 +2474,7 @@
         <v>1040019851</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>4</v>
@@ -2483,7 +2485,7 @@
         <v>1010060188</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>4</v>
@@ -2494,7 +2496,7 @@
         <v>1040077348</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>4</v>
@@ -2505,7 +2507,7 @@
         <v>1040077347</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>4</v>
@@ -2516,7 +2518,7 @@
         <v>1010012011</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>4</v>
@@ -2527,7 +2529,7 @@
         <v>13781</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>4</v>
@@ -2538,7 +2540,7 @@
         <v>102286</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>4</v>
@@ -2549,7 +2551,7 @@
         <v>1010003615</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>4</v>
@@ -2560,7 +2562,7 @@
         <v>1010084124</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>4</v>
@@ -2571,7 +2573,7 @@
         <v>1010003651</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>4</v>
@@ -2582,7 +2584,7 @@
         <v>1040083258</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>4</v>
@@ -2593,7 +2595,7 @@
         <v>154897</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>4</v>
@@ -2604,7 +2606,7 @@
         <v>1040077349</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>4</v>
@@ -2615,7 +2617,7 @@
         <v>1010077433</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>4</v>
@@ -2626,7 +2628,7 @@
         <v>1040077350</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>4</v>
@@ -2637,7 +2639,7 @@
         <v>1010021550</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>4</v>
@@ -2648,7 +2650,7 @@
         <v>1010062027</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>4</v>
@@ -2659,7 +2661,7 @@
         <v>1040077352</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>4</v>
@@ -2670,7 +2672,7 @@
         <v>1010042610</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>4</v>
@@ -2681,7 +2683,7 @@
         <v>1040077354</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>4</v>
@@ -2692,7 +2694,7 @@
         <v>1040098335</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>4</v>
@@ -2703,7 +2705,7 @@
         <v>1010041375</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>4</v>
@@ -2714,7 +2716,7 @@
         <v>1010052336</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>4</v>
@@ -2725,7 +2727,7 @@
         <v>1010023362</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>4</v>
@@ -2736,7 +2738,7 @@
         <v>1040077355</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>4</v>
@@ -2747,7 +2749,7 @@
         <v>1010061810</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>4</v>
@@ -2758,7 +2760,7 @@
         <v>1010050496</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>4</v>
@@ -2769,7 +2771,7 @@
         <v>1010050536</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>4</v>
@@ -2780,7 +2782,7 @@
         <v>1040092580</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>4</v>
@@ -2791,10 +2793,10 @@
         <v>1010027772</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>411</v>
+        <v>52</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2802,10 +2804,10 @@
         <v>1010054278</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>409</v>
+        <v>54</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2813,10 +2815,10 @@
         <v>1010083462</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>410</v>
+        <v>55</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2824,10 +2826,10 @@
         <v>1010084591</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>474</v>
+        <v>56</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2835,10 +2837,10 @@
         <v>1010058709</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>475</v>
+        <v>57</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2846,7 +2848,7 @@
         <v>230110</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>4</v>
@@ -2857,7 +2859,7 @@
         <v>1010062152</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>4</v>
@@ -2868,7 +2870,7 @@
         <v>1010059706</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>4</v>
@@ -2879,10 +2881,10 @@
         <v>1010051997</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>407</v>
+        <v>61</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2890,10 +2892,10 @@
         <v>1010031694</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>406</v>
+        <v>62</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2901,10 +2903,10 @@
         <v>1010022601</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>408</v>
+        <v>63</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -2912,7 +2914,7 @@
         <v>1010004289</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>4</v>
@@ -2923,7 +2925,7 @@
         <v>1010004292</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>4</v>
@@ -2934,7 +2936,7 @@
         <v>1010012756</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>4</v>
@@ -2945,7 +2947,7 @@
         <v>1010004299</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>4</v>
@@ -2956,7 +2958,7 @@
         <v>1010004301</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>4</v>
@@ -2967,7 +2969,7 @@
         <v>1040077357</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>4</v>
@@ -2978,7 +2980,7 @@
         <v>1010023336</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>4</v>
@@ -2989,7 +2991,7 @@
         <v>1040077356</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>4</v>
@@ -3000,7 +3002,7 @@
         <v>1040090022</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>4</v>
@@ -3011,7 +3013,7 @@
         <v>1040075251</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>4</v>
@@ -3022,7 +3024,7 @@
         <v>1010045227</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>4</v>
@@ -3033,7 +3035,7 @@
         <v>1040077358</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>4</v>
@@ -3044,7 +3046,7 @@
         <v>1010021328</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>4</v>
@@ -3055,7 +3057,7 @@
         <v>1010085124</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>4</v>
@@ -3066,7 +3068,7 @@
         <v>1010046495</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>4</v>
@@ -3077,7 +3079,7 @@
         <v>1040101764</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>4</v>
@@ -3088,10 +3090,10 @@
         <v>1010084144</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3099,10 +3101,10 @@
         <v>1010084958</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3110,10 +3112,10 @@
         <v>1010084720</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3121,7 +3123,7 @@
         <v>1010000312</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>4</v>
@@ -3132,10 +3134,10 @@
         <v>1010021956</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>415</v>
+        <v>84</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3143,10 +3145,10 @@
         <v>1010021957</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>417</v>
+        <v>85</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3154,10 +3156,10 @@
         <v>1010025711</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>476</v>
+        <v>86</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3165,7 +3167,7 @@
         <v>428995</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>4</v>
@@ -3176,7 +3178,7 @@
         <v>428998</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>4</v>
@@ -3187,7 +3189,7 @@
         <v>1010050243</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>4</v>
@@ -3198,7 +3200,7 @@
         <v>1010050244</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>4</v>
@@ -3209,7 +3211,7 @@
         <v>1010031630</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>4</v>
@@ -3220,7 +3222,7 @@
         <v>1010031607</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>4</v>
@@ -3231,7 +3233,7 @@
         <v>1010045647</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>4</v>
@@ -3242,7 +3244,7 @@
         <v>1010031567</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>4</v>
@@ -3253,7 +3255,7 @@
         <v>1040077361</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>4</v>
@@ -3264,7 +3266,7 @@
         <v>1010050445</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>4</v>
@@ -3275,7 +3277,7 @@
         <v>1010050461</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>4</v>
@@ -3286,10 +3288,10 @@
         <v>1010077431</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>424</v>
+        <v>98</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3297,10 +3299,10 @@
         <v>1010077503</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>425</v>
+        <v>99</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3308,10 +3310,10 @@
         <v>1010026551</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>419</v>
+        <v>100</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3319,10 +3321,10 @@
         <v>1010039904</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>421</v>
+        <v>101</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3330,10 +3332,10 @@
         <v>1010042554</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>420</v>
+        <v>102</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3341,10 +3343,10 @@
         <v>1010060205</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>422</v>
+        <v>103</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3352,10 +3354,10 @@
         <v>1010060206</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>423</v>
+        <v>104</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3363,10 +3365,10 @@
         <v>1010062826</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>395</v>
+        <v>105</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>396</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3374,7 +3376,7 @@
         <v>1010087609</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>4</v>
@@ -3385,7 +3387,7 @@
         <v>1040097102</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>4</v>
@@ -3396,7 +3398,7 @@
         <v>1010053885</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>4</v>
@@ -3407,7 +3409,7 @@
         <v>1010087738</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>4</v>
@@ -3418,7 +3420,7 @@
         <v>1010020838</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>4</v>
@@ -3429,7 +3431,7 @@
         <v>1010087773</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>4</v>
@@ -3440,7 +3442,7 @@
         <v>1010087644</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>4</v>
@@ -3451,7 +3453,7 @@
         <v>1010087544</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>4</v>
@@ -3462,7 +3464,7 @@
         <v>1010042643</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>4</v>
@@ -3473,7 +3475,7 @@
         <v>341430</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>4</v>
@@ -3484,7 +3486,7 @@
         <v>425554</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>4</v>
@@ -3495,7 +3497,7 @@
         <v>1040076302</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>4</v>
@@ -3506,7 +3508,7 @@
         <v>1010084157</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>4</v>
@@ -3517,7 +3519,7 @@
         <v>1010084158</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>4</v>
@@ -3528,7 +3530,7 @@
         <v>1010084159</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>4</v>
@@ -3539,7 +3541,7 @@
         <v>1010084160</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>4</v>
@@ -3550,7 +3552,7 @@
         <v>1010084161</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>4</v>
@@ -3561,7 +3563,7 @@
         <v>1010084162</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>4</v>
@@ -3572,10 +3574,10 @@
         <v>1010002592</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>397</v>
+        <v>125</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>396</v>
+        <v>106</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3583,7 +3585,7 @@
         <v>224382</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>4</v>
@@ -3594,7 +3596,7 @@
         <v>1010021079</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>4</v>
@@ -3605,7 +3607,7 @@
         <v>94314</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>4</v>
@@ -3616,7 +3618,7 @@
         <v>1010003982</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>4</v>
@@ -3627,7 +3629,7 @@
         <v>1010000182</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>4</v>
@@ -3638,7 +3640,7 @@
         <v>1040077362</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>4</v>
@@ -3649,7 +3651,7 @@
         <v>1040077363</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>4</v>
@@ -3660,7 +3662,7 @@
         <v>1010062982</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>4</v>
@@ -3671,7 +3673,7 @@
         <v>1040074483</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>4</v>
@@ -3682,7 +3684,7 @@
         <v>1010063209</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>4</v>
@@ -3693,7 +3695,7 @@
         <v>1010002463</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>4</v>
@@ -3704,7 +3706,7 @@
         <v>1040096343</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>4</v>
@@ -3715,7 +3717,7 @@
         <v>1040048463</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>4</v>
@@ -3726,7 +3728,7 @@
         <v>1040077364</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>4</v>
@@ -3737,7 +3739,7 @@
         <v>409640</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>4</v>
@@ -3748,7 +3750,7 @@
         <v>1010032753</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>4</v>
@@ -3759,10 +3761,10 @@
         <v>1010001155</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>398</v>
+        <v>142</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>396</v>
+        <v>106</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3770,7 +3772,7 @@
         <v>1040098597</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>4</v>
@@ -3781,7 +3783,7 @@
         <v>1010007405</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>4</v>
@@ -3792,7 +3794,7 @@
         <v>1040077365</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>4</v>
@@ -3803,10 +3805,10 @@
         <v>1010028655</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>504</v>
+        <v>146</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3814,10 +3816,10 @@
         <v>1010028657</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>502</v>
+        <v>148</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3825,7 +3827,7 @@
         <v>1010027794</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>4</v>
@@ -3836,10 +3838,10 @@
         <v>1010080930</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>507</v>
+        <v>150</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3847,10 +3849,10 @@
         <v>51666</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>506</v>
+        <v>151</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3858,10 +3860,10 @@
         <v>145165</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>505</v>
+        <v>152</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3869,7 +3871,7 @@
         <v>1040077366</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>4</v>
@@ -3880,7 +3882,7 @@
         <v>1040077367</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>4</v>
@@ -3891,10 +3893,10 @@
         <v>161055</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>508</v>
+        <v>155</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3902,7 +3904,7 @@
         <v>1040017773</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>4</v>
@@ -3913,7 +3915,7 @@
         <v>1040084464</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>4</v>
@@ -3924,7 +3926,7 @@
         <v>1010021561</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>4</v>
@@ -3935,7 +3937,7 @@
         <v>1010021562</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>4</v>
@@ -3946,10 +3948,10 @@
         <v>1010084187</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>426</v>
+        <v>160</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3957,10 +3959,10 @@
         <v>1010080958</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>427</v>
+        <v>161</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -3968,7 +3970,7 @@
         <v>1010027792</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>4</v>
@@ -3979,7 +3981,7 @@
         <v>1010083731</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>4</v>
@@ -3990,7 +3992,7 @@
         <v>341430</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>4</v>
@@ -4001,7 +4003,7 @@
         <v>1010029366</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>4</v>
@@ -4012,7 +4014,7 @@
         <v>1010049216</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>4</v>
@@ -4023,7 +4025,7 @@
         <v>1010031723</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>4</v>
@@ -4034,7 +4036,7 @@
         <v>1010021582</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>4</v>
@@ -4045,7 +4047,7 @@
         <v>1010021544</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>4</v>
@@ -4056,7 +4058,7 @@
         <v>405558</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>4</v>
@@ -4067,7 +4069,7 @@
         <v>1010023038</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>4</v>
@@ -4078,7 +4080,7 @@
         <v>1010084109</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>4</v>
@@ -4089,10 +4091,10 @@
         <v>1010084190</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>510</v>
+        <v>173</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4100,10 +4102,10 @@
         <v>427341</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>478</v>
+        <v>174</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4111,10 +4113,10 @@
         <v>1010001062</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>399</v>
+        <v>175</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>396</v>
+        <v>106</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4122,10 +4124,10 @@
         <v>1010050517</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>509</v>
+        <v>176</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4133,10 +4135,10 @@
         <v>1010001400</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>512</v>
+        <v>177</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4144,10 +4146,10 @@
         <v>1010084195</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>511</v>
+        <v>178</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4155,10 +4157,10 @@
         <v>1010008416</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>513</v>
+        <v>179</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4166,7 +4168,7 @@
         <v>1010021564</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>4</v>
@@ -4177,7 +4179,7 @@
         <v>1010059334</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>4</v>
@@ -4188,7 +4190,7 @@
         <v>1010023019</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>4</v>
@@ -4199,7 +4201,7 @@
         <v>1010048541</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>4</v>
@@ -4210,7 +4212,7 @@
         <v>1010000277</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>4</v>
@@ -4221,7 +4223,7 @@
         <v>1010085344</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>4</v>
@@ -4232,7 +4234,7 @@
         <v>1010001389</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>4</v>
@@ -4243,10 +4245,10 @@
         <v>1010026032</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>428</v>
+        <v>187</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4254,7 +4256,7 @@
         <v>1010017703</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>4</v>
@@ -4265,7 +4267,7 @@
         <v>1010052036</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>144</v>
+        <v>189</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>4</v>
@@ -4276,10 +4278,10 @@
         <v>1010085384</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>429</v>
+        <v>190</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4287,7 +4289,7 @@
         <v>1010085383</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>4</v>
@@ -4298,7 +4300,7 @@
         <v>1040019325</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>4</v>
@@ -4309,7 +4311,7 @@
         <v>1040097133</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>4</v>
@@ -4320,7 +4322,7 @@
         <v>1010047089</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>4</v>
@@ -4328,10 +4330,10 @@
     </row>
     <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="14">
-        <v>64262</v>
+        <v>1010051726</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>4</v>
@@ -4342,10 +4344,10 @@
         <v>1010006347</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>430</v>
+        <v>196</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4353,10 +4355,10 @@
         <v>1010085179</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>431</v>
+        <v>197</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4364,183 +4366,184 @@
         <v>1010024131</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>433</v>
+        <v>198</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="14">
         <v>1010024158</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>432</v>
+        <v>199</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="H193" s="25"/>
+    </row>
+    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="14">
         <v>1010084328</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="14">
         <v>1040050168</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>149</v>
+        <v>201</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="14">
         <v>1040077370</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>150</v>
+        <v>202</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="14">
         <v>1040100560</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="14">
         <v>1040077374</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="14">
         <v>1040099247</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="14">
         <v>1010050632</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="14">
         <v>1010020504</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="14">
         <v>1010021733</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="14">
         <v>1010059684</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>477</v>
+        <v>209</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" s="14">
         <v>65219</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>380</v>
+        <v>210</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="14">
         <v>1010003966</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>378</v>
+        <v>211</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="13">
         <v>1010003967</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>379</v>
+        <v>212</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="20">
         <v>1040077380</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="17">
         <v>409250</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>4</v>
@@ -4551,7 +4554,7 @@
         <v>1010020541</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>4</v>
@@ -4562,7 +4565,7 @@
         <v>1010020879</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>4</v>
@@ -4573,7 +4576,7 @@
         <v>1010021520</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>4</v>
@@ -4584,7 +4587,7 @@
         <v>1010077261</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>4</v>
@@ -4595,7 +4598,7 @@
         <v>1040098861</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>163</v>
+        <v>219</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>4</v>
@@ -4606,7 +4609,7 @@
         <v>1010027664</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>4</v>
@@ -4617,7 +4620,7 @@
         <v>1010024047</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>4</v>
@@ -4628,7 +4631,7 @@
         <v>1040077377</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>4</v>
@@ -4639,7 +4642,7 @@
         <v>1040097068</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>4</v>
@@ -4650,7 +4653,7 @@
         <v>1040097070</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>4</v>
@@ -4661,7 +4664,7 @@
         <v>1010061942</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>172</v>
+        <v>225</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>4</v>
@@ -4672,10 +4675,10 @@
         <v>1010007160</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>434</v>
+        <v>226</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4683,10 +4686,10 @@
         <v>1010023642</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>435</v>
+        <v>227</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4694,10 +4697,10 @@
         <v>1010007193</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>436</v>
+        <v>228</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4705,10 +4708,10 @@
         <v>1040075324</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>439</v>
+        <v>229</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4716,10 +4719,10 @@
         <v>1040075323</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>438</v>
+        <v>230</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4727,10 +4730,10 @@
         <v>1040077661</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>443</v>
+        <v>231</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4738,10 +4741,10 @@
         <v>1040083312</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>442</v>
+        <v>232</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4749,10 +4752,10 @@
         <v>1040017489</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>445</v>
+        <v>233</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4760,10 +4763,10 @@
         <v>1010085180</v>
       </c>
       <c r="B228" s="11" t="s">
-        <v>444</v>
+        <v>234</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4771,10 +4774,10 @@
         <v>1010042637</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>437</v>
+        <v>235</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4782,10 +4785,10 @@
         <v>1040017204</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>471</v>
+        <v>236</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4793,10 +4796,10 @@
         <v>1040017505</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>448</v>
+        <v>237</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4804,10 +4807,10 @@
         <v>1010085181</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>446</v>
+        <v>238</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4815,10 +4818,10 @@
         <v>1040017503</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>449</v>
+        <v>239</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4826,10 +4829,10 @@
         <v>400175</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>447</v>
+        <v>240</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4837,10 +4840,10 @@
         <v>1010046445</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>450</v>
+        <v>241</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
       <c r="F235" s="25"/>
     </row>
@@ -4849,10 +4852,10 @@
         <v>1040074827</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>440</v>
+        <v>242</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4860,10 +4863,10 @@
         <v>1040099488</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>441</v>
+        <v>243</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4871,10 +4874,10 @@
         <v>1010021033</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>451</v>
+        <v>244</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="239" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4882,10 +4885,10 @@
         <v>1010057142</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>452</v>
+        <v>245</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4893,10 +4896,10 @@
         <v>1010055398</v>
       </c>
       <c r="B240" s="34" t="s">
-        <v>516</v>
+        <v>246</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4904,10 +4907,10 @@
         <v>1010018372</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>514</v>
+        <v>247</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4915,10 +4918,10 @@
         <v>1010018361</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>515</v>
+        <v>248</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4926,7 +4929,7 @@
         <v>1010001010</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>175</v>
+        <v>249</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>4</v>
@@ -4937,10 +4940,10 @@
         <v>1010044502</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>401</v>
+        <v>250</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>396</v>
+        <v>106</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4948,10 +4951,10 @@
         <v>1010053692</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>402</v>
+        <v>251</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>396</v>
+        <v>106</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -4959,7 +4962,7 @@
         <v>1010025482</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>179</v>
+        <v>252</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>4</v>
@@ -4970,7 +4973,7 @@
         <v>1010027308</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>177</v>
+        <v>253</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>4</v>
@@ -4981,7 +4984,7 @@
         <v>1010025509</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>180</v>
+        <v>254</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>4</v>
@@ -4992,7 +4995,7 @@
         <v>1040077383</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>4</v>
@@ -5003,7 +5006,7 @@
         <v>1010083908</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>4</v>
@@ -5014,7 +5017,7 @@
         <v>1010031616</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>4</v>
@@ -5025,7 +5028,7 @@
         <v>1010018301</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>183</v>
+        <v>258</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>4</v>
@@ -5036,7 +5039,7 @@
         <v>1010027789</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>4</v>
@@ -5047,7 +5050,7 @@
         <v>1010027790</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>182</v>
+        <v>260</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>4</v>
@@ -5058,7 +5061,7 @@
         <v>1010053728</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>185</v>
+        <v>261</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>4</v>
@@ -5069,7 +5072,7 @@
         <v>1010058554</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>4</v>
@@ -5080,7 +5083,7 @@
         <v>1010020758</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>186</v>
+        <v>263</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>4</v>
@@ -5091,7 +5094,7 @@
         <v>1010020781</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>4</v>
@@ -5102,7 +5105,7 @@
         <v>1010059332</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>4</v>
@@ -5113,7 +5116,7 @@
         <v>1010058426</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>188</v>
+        <v>266</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>4</v>
@@ -5124,10 +5127,10 @@
         <v>1010016356</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>453</v>
+        <v>267</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="262" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5135,10 +5138,10 @@
         <v>1010052021</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>455</v>
+        <v>268</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="263" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5146,10 +5149,10 @@
         <v>1010084363</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>454</v>
+        <v>269</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="264" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5157,10 +5160,10 @@
         <v>1010062022</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>457</v>
+        <v>270</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="265" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5168,10 +5171,10 @@
         <v>1040091721</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>456</v>
+        <v>271</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="266" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5179,7 +5182,7 @@
         <v>1040077389</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>190</v>
+        <v>272</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>4</v>
@@ -5190,7 +5193,7 @@
         <v>1010021364</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>4</v>
@@ -5201,7 +5204,7 @@
         <v>1010021541</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>192</v>
+        <v>274</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>4</v>
@@ -5212,7 +5215,7 @@
         <v>1010021955</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>193</v>
+        <v>275</v>
       </c>
       <c r="C269" s="4" t="s">
         <v>4</v>
@@ -5223,7 +5226,7 @@
         <v>1040077388</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>4</v>
@@ -5234,7 +5237,7 @@
         <v>1010058100</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>195</v>
+        <v>277</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>4</v>
@@ -5245,7 +5248,7 @@
         <v>1010020524</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>196</v>
+        <v>278</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>4</v>
@@ -5257,7 +5260,7 @@
         <v>1010021958</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>197</v>
+        <v>279</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>4</v>
@@ -5268,7 +5271,7 @@
         <v>1010019756</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>198</v>
+        <v>280</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>4</v>
@@ -5279,7 +5282,7 @@
         <v>1010019752</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>199</v>
+        <v>281</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>4</v>
@@ -5290,7 +5293,7 @@
         <v>1010047089</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>201</v>
+        <v>282</v>
       </c>
       <c r="C276" s="4" t="s">
         <v>4</v>
@@ -5301,7 +5304,7 @@
         <v>409639</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>200</v>
+        <v>283</v>
       </c>
       <c r="C277" s="4" t="s">
         <v>4</v>
@@ -5312,7 +5315,7 @@
         <v>1040084107</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>202</v>
+        <v>284</v>
       </c>
       <c r="C278" s="4" t="s">
         <v>4</v>
@@ -5323,10 +5326,10 @@
         <v>18336</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>458</v>
+        <v>285</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5334,7 +5337,7 @@
         <v>1010085203</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>203</v>
+        <v>286</v>
       </c>
       <c r="C280" s="4" t="s">
         <v>4</v>
@@ -5345,10 +5348,10 @@
         <v>1010085279</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>480</v>
+        <v>287</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5356,7 +5359,7 @@
         <v>424298</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>204</v>
+        <v>288</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>4</v>
@@ -5367,7 +5370,7 @@
         <v>421847</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>205</v>
+        <v>289</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>4</v>
@@ -5378,7 +5381,7 @@
         <v>431573</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>206</v>
+        <v>290</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>4</v>
@@ -5389,7 +5392,7 @@
         <v>1010021581</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>207</v>
+        <v>291</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>4</v>
@@ -5400,10 +5403,10 @@
         <v>229205</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>459</v>
+        <v>292</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5411,10 +5414,10 @@
         <v>60671</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>460</v>
+        <v>293</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5422,7 +5425,7 @@
         <v>1010021542</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>218</v>
+        <v>294</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>4</v>
@@ -5433,7 +5436,7 @@
         <v>301626</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>229</v>
+        <v>295</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>4</v>
@@ -5444,7 +5447,7 @@
         <v>429495</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>230</v>
+        <v>296</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>4</v>
@@ -5452,43 +5455,43 @@
     </row>
     <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="14">
+        <v>1040046638</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A292" s="14">
         <v>17738</v>
       </c>
-      <c r="B291" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C291" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A292" s="16">
+      <c r="B292" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A293" s="16">
         <v>1010003541</v>
       </c>
-      <c r="B292" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C292" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A293" s="14">
+      <c r="B293" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A294" s="14">
         <v>1010022606</v>
       </c>
-      <c r="B293" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C293" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A294" s="16">
-        <v>1010003527</v>
-      </c>
       <c r="B294" s="5" t="s">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>4</v>
@@ -5496,10 +5499,10 @@
     </row>
     <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="16">
-        <v>1010055707</v>
+        <v>1010003527</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>211</v>
+        <v>301</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>4</v>
@@ -5507,21 +5510,21 @@
     </row>
     <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="16">
+        <v>1010055707</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A297" s="16">
         <v>422027</v>
       </c>
-      <c r="B296" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C296" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A297" s="14">
-        <v>1010011313</v>
-      </c>
       <c r="B297" s="5" t="s">
-        <v>213</v>
+        <v>303</v>
       </c>
       <c r="C297" s="4" t="s">
         <v>4</v>
@@ -5529,10 +5532,10 @@
     </row>
     <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="14">
-        <v>1010003322</v>
+        <v>1010011313</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>236</v>
+        <v>304</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>4</v>
@@ -5540,10 +5543,10 @@
     </row>
     <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="14">
-        <v>27051</v>
+        <v>1010003322</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>214</v>
+        <v>305</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>4</v>
@@ -5551,10 +5554,10 @@
     </row>
     <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="14">
-        <v>1010011304</v>
+        <v>27051</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>215</v>
+        <v>306</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>4</v>
@@ -5562,10 +5565,10 @@
     </row>
     <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="14">
-        <v>1010003404</v>
+        <v>1010011304</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>235</v>
+        <v>307</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>4</v>
@@ -5573,10 +5576,10 @@
     </row>
     <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="14">
-        <v>35659</v>
+        <v>1010003404</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>4</v>
@@ -5584,10 +5587,10 @@
     </row>
     <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="14">
-        <v>1040077390</v>
+        <v>35659</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>217</v>
+        <v>309</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>4</v>
@@ -5595,10 +5598,10 @@
     </row>
     <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="14">
-        <v>1010011379</v>
+        <v>1040077390</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>220</v>
+        <v>310</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>4</v>
@@ -5606,10 +5609,10 @@
     </row>
     <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="14">
-        <v>1010003279</v>
+        <v>1010011379</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>221</v>
+        <v>311</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>4</v>
@@ -5617,10 +5620,10 @@
     </row>
     <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" s="14">
-        <v>1010011380</v>
+        <v>1010003279</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>222</v>
+        <v>312</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>4</v>
@@ -5628,10 +5631,10 @@
     </row>
     <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" s="14">
-        <v>351197</v>
+        <v>1010011380</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>4</v>
@@ -5639,10 +5642,10 @@
     </row>
     <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="14">
-        <v>1010011286</v>
+        <v>351197</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>224</v>
+        <v>314</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>4</v>
@@ -5650,10 +5653,10 @@
     </row>
     <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" s="14">
-        <v>2479</v>
+        <v>1010011286</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>4</v>
@@ -5661,10 +5664,10 @@
     </row>
     <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="14">
-        <v>1010011382</v>
+        <v>2479</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>226</v>
+        <v>316</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>4</v>
@@ -5672,10 +5675,10 @@
     </row>
     <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" s="14">
-        <v>1010055703</v>
+        <v>1010011382</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>227</v>
+        <v>317</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>4</v>
@@ -5683,10 +5686,10 @@
     </row>
     <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" s="14">
-        <v>4165</v>
+        <v>1010055703</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>228</v>
+        <v>318</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>4</v>
@@ -5694,10 +5697,10 @@
     </row>
     <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" s="14">
-        <v>1010021929</v>
+        <v>4165</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>4</v>
@@ -5705,10 +5708,10 @@
     </row>
     <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" s="14">
-        <v>162998</v>
+        <v>1010021929</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>231</v>
+        <v>320</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>4</v>
@@ -5716,98 +5719,98 @@
     </row>
     <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" s="14">
-        <v>1040090138</v>
+        <v>162998</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>487</v>
+        <v>321</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>473</v>
+        <v>4</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" s="14">
-        <v>428065</v>
+        <v>1040090138</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>234</v>
+        <v>322</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" s="14">
-        <v>1010026864</v>
+        <v>428065</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>483</v>
+        <v>323</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>473</v>
+        <v>4</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" s="14">
-        <v>1010022588</v>
+        <v>1010026864</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>482</v>
+        <v>324</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" s="14">
-        <v>1010030946</v>
+        <v>1010022588</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>484</v>
+        <v>325</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" s="14">
-        <v>1040090143</v>
+        <v>1010030946</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>486</v>
+        <v>326</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="14">
-        <v>1010022589</v>
+        <v>1040090143</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>485</v>
+        <v>327</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="14">
-        <v>1010085360</v>
+        <v>1010022589</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" s="14">
-        <v>1010064470</v>
+        <v>1010085360</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>4</v>
@@ -5815,43 +5818,43 @@
     </row>
     <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" s="14">
+        <v>1010064470</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A325" s="14">
         <v>432657</v>
       </c>
-      <c r="B324" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C324" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A325" s="17">
+      <c r="B325" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A326" s="17">
         <v>1010051765</v>
       </c>
-      <c r="B325" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C325" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A326" s="14">
+      <c r="B326" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A327" s="14">
         <v>1040017264</v>
       </c>
-      <c r="B326" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C326" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A327" s="13">
-        <v>1040077391</v>
-      </c>
-      <c r="B327" s="5" t="s">
-        <v>239</v>
+      <c r="B327" s="7" t="s">
+        <v>333</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>4</v>
@@ -5859,10 +5862,10 @@
     </row>
     <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" s="13">
-        <v>1010024661</v>
+        <v>1040077391</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>241</v>
+        <v>334</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>4</v>
@@ -5870,21 +5873,21 @@
     </row>
     <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="13">
+        <v>1010024661</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A330" s="13">
         <v>1010058624</v>
       </c>
-      <c r="B329" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C329" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A330" s="14">
-        <v>1010021089</v>
-      </c>
       <c r="B330" s="5" t="s">
-        <v>243</v>
+        <v>336</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>4</v>
@@ -5892,10 +5895,10 @@
     </row>
     <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="14">
-        <v>1040019315</v>
+        <v>1010021089</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>242</v>
+        <v>337</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>4</v>
@@ -5903,10 +5906,10 @@
     </row>
     <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="14">
-        <v>1010035272</v>
+        <v>1040019315</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>4</v>
@@ -5914,10 +5917,10 @@
     </row>
     <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="14">
-        <v>1040077392</v>
+        <v>1010035272</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>247</v>
+        <v>339</v>
       </c>
       <c r="C333" s="4" t="s">
         <v>4</v>
@@ -5925,10 +5928,10 @@
     </row>
     <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" s="14">
-        <v>1040077393</v>
+        <v>1040077392</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>248</v>
+        <v>340</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>4</v>
@@ -5936,32 +5939,32 @@
     </row>
     <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" s="14">
-        <v>422131</v>
+        <v>1040077393</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>517</v>
+        <v>341</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>503</v>
+        <v>4</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" s="14">
-        <v>1040077395</v>
+        <v>422131</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>249</v>
+        <v>342</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>4</v>
+        <v>147</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" s="14">
-        <v>27572</v>
+        <v>1040077395</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>251</v>
+        <v>343</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>4</v>
@@ -5969,10 +5972,10 @@
     </row>
     <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" s="14">
-        <v>1010025148</v>
+        <v>27572</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>256</v>
+        <v>344</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>4</v>
@@ -5980,32 +5983,32 @@
     </row>
     <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="14">
+        <v>1010025148</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A340" s="14">
         <v>1040077396</v>
       </c>
-      <c r="B339" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C339" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A340" s="21">
+      <c r="B340" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A341" s="21">
         <v>1040097154</v>
       </c>
-      <c r="B340" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="C340" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A341" s="14">
-        <v>1040077394</v>
-      </c>
-      <c r="B341" s="5" t="s">
-        <v>257</v>
+      <c r="B341" s="6" t="s">
+        <v>347</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>4</v>
@@ -6013,10 +6016,10 @@
     </row>
     <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" s="14">
-        <v>1010014049</v>
+        <v>1040077394</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>255</v>
+        <v>348</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>4</v>
@@ -6024,142 +6027,142 @@
     </row>
     <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" s="14">
-        <v>1030000370</v>
+        <v>1010014049</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>491</v>
+        <v>349</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>473</v>
+        <v>4</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="14">
-        <v>1030000368</v>
+        <v>1030000370</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>493</v>
+        <v>350</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="14">
-        <v>1010052320</v>
+        <v>1030000368</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>490</v>
+        <v>351</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="14">
-        <v>1030000511</v>
+        <v>1010052320</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>498</v>
+        <v>352</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="14">
-        <v>1030000821</v>
+        <v>1030000511</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>497</v>
+        <v>353</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" s="14">
-        <v>1030000366</v>
+        <v>1030000821</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>492</v>
+        <v>354</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" s="14">
+        <v>1030000366</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A350" s="14">
         <v>1030000369</v>
       </c>
-      <c r="B349" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="C349" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A350" s="17">
+      <c r="B350" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A351" s="17">
         <v>1010052319</v>
       </c>
-      <c r="B350" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C350" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A351" s="14">
-        <v>1030000490</v>
-      </c>
-      <c r="B351" s="7" t="s">
-        <v>496</v>
+      <c r="B351" s="5" t="s">
+        <v>357</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="14">
+        <v>1030000490</v>
+      </c>
+      <c r="B352" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A353" s="14">
         <v>1030000489</v>
       </c>
-      <c r="B352" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="C352" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A353" s="28">
+      <c r="B353" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A354" s="28">
         <v>1030001314</v>
       </c>
-      <c r="B353" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C353" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A354" s="14">
-        <v>1040040957</v>
-      </c>
       <c r="B354" s="5" t="s">
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="14">
-        <v>1040079329</v>
+        <v>1040040957</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>259</v>
+        <v>361</v>
       </c>
       <c r="C355" s="4" t="s">
         <v>4</v>
@@ -6167,10 +6170,10 @@
     </row>
     <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" s="14">
-        <v>1010010599</v>
+        <v>1040079329</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>263</v>
+        <v>362</v>
       </c>
       <c r="C356" s="4" t="s">
         <v>4</v>
@@ -6178,10 +6181,10 @@
     </row>
     <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="14">
-        <v>1040077398</v>
+        <v>1010010599</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>261</v>
+        <v>363</v>
       </c>
       <c r="C357" s="4" t="s">
         <v>4</v>
@@ -6189,32 +6192,32 @@
     </row>
     <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="14">
+        <v>1040077398</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A359" s="14">
         <v>1010053128</v>
       </c>
-      <c r="B358" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C358" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A359" s="16">
+      <c r="B359" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A360" s="16">
         <v>1010055962</v>
       </c>
-      <c r="B359" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C359" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A360" s="14">
-        <v>1010003578</v>
-      </c>
       <c r="B360" s="5" t="s">
-        <v>270</v>
+        <v>366</v>
       </c>
       <c r="C360" s="4" t="s">
         <v>4</v>
@@ -6222,10 +6225,10 @@
     </row>
     <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="14">
-        <v>332891</v>
+        <v>1010003578</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>271</v>
+        <v>367</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>4</v>
@@ -6233,10 +6236,10 @@
     </row>
     <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="14">
-        <v>281703</v>
+        <v>332891</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>525</v>
+        <v>368</v>
       </c>
       <c r="C362" s="4" t="s">
         <v>4</v>
@@ -6244,10 +6247,10 @@
     </row>
     <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" s="14">
-        <v>17727</v>
+        <v>281703</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>4</v>
@@ -6255,10 +6258,10 @@
     </row>
     <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="14">
-        <v>1010056064</v>
+        <v>17727</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>264</v>
+        <v>370</v>
       </c>
       <c r="C364" s="4" t="s">
         <v>4</v>
@@ -6266,10 +6269,10 @@
     </row>
     <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" s="14">
-        <v>5389</v>
+        <v>1010056064</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>265</v>
+        <v>371</v>
       </c>
       <c r="C365" s="4" t="s">
         <v>4</v>
@@ -6277,10 +6280,10 @@
     </row>
     <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="14">
-        <v>1010055969</v>
+        <v>5389</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>266</v>
+        <v>372</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>4</v>
@@ -6288,10 +6291,10 @@
     </row>
     <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="14">
-        <v>181395</v>
+        <v>1010055969</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>268</v>
+        <v>373</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>4</v>
@@ -6299,10 +6302,10 @@
     </row>
     <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="14">
-        <v>1010055970</v>
+        <v>181395</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>267</v>
+        <v>374</v>
       </c>
       <c r="C368" s="4" t="s">
         <v>4</v>
@@ -6310,10 +6313,10 @@
     </row>
     <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="14">
-        <v>1040085949</v>
+        <v>1010055970</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>274</v>
+        <v>375</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>4</v>
@@ -6321,10 +6324,10 @@
     </row>
     <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="14">
-        <v>1010020554</v>
+        <v>1040085949</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>273</v>
+        <v>376</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>4</v>
@@ -6332,10 +6335,10 @@
     </row>
     <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="14">
-        <v>1040077399</v>
+        <v>1010020554</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>153</v>
+        <v>377</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>4</v>
@@ -6346,7 +6349,7 @@
         <v>1040077399</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>155</v>
+        <v>378</v>
       </c>
       <c r="C372" s="4" t="s">
         <v>4</v>
@@ -6354,32 +6357,32 @@
     </row>
     <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="14">
-        <v>1010058415</v>
+        <v>1040077399</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>481</v>
+        <v>379</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>473</v>
+        <v>4</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" s="14">
-        <v>1040077401</v>
+        <v>1010058415</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" s="14">
-        <v>18745</v>
+        <v>1040077401</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>252</v>
+        <v>381</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>4</v>
@@ -6387,10 +6390,10 @@
     </row>
     <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" s="14">
-        <v>1040077400</v>
+        <v>18745</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>258</v>
+        <v>382</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>4</v>
@@ -6398,10 +6401,10 @@
     </row>
     <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" s="14">
-        <v>17918</v>
+        <v>1040077400</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>526</v>
+        <v>383</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>4</v>
@@ -6409,10 +6412,10 @@
     </row>
     <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" s="14">
-        <v>1010062086</v>
+        <v>17918</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>277</v>
+        <v>384</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>4</v>
@@ -6420,10 +6423,10 @@
     </row>
     <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" s="14">
-        <v>1010062087</v>
+        <v>1010062086</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>278</v>
+        <v>385</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>4</v>
@@ -6431,10 +6434,10 @@
     </row>
     <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="14">
-        <v>1010062938</v>
+        <v>1010062087</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>276</v>
+        <v>386</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>4</v>
@@ -6442,10 +6445,10 @@
     </row>
     <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" s="14">
-        <v>1010091004</v>
+        <v>1010062938</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>275</v>
+        <v>387</v>
       </c>
       <c r="C381" s="4" t="s">
         <v>4</v>
@@ -6453,32 +6456,32 @@
     </row>
     <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" s="14">
+        <v>1010091004</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A383" s="14">
         <v>1040077373</v>
       </c>
-      <c r="B382" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C382" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A383" s="21">
+      <c r="B383" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A384" s="21">
         <v>1040077372</v>
       </c>
-      <c r="B383" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="C383" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A384" s="14">
-        <v>1010036546</v>
-      </c>
-      <c r="B384" s="5" t="s">
-        <v>254</v>
+      <c r="B384" s="6" t="s">
+        <v>390</v>
       </c>
       <c r="C384" s="4" t="s">
         <v>4</v>
@@ -6486,54 +6489,54 @@
     </row>
     <row r="385" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="14">
+        <v>1010036546</v>
+      </c>
+      <c r="B385" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A386" s="14">
         <v>1010081353</v>
       </c>
-      <c r="B385" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C385" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="386" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A386" s="30">
+      <c r="B386" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C386" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A387" s="30">
         <v>1010029427</v>
       </c>
-      <c r="B386" s="10" t="s">
-        <v>524</v>
-      </c>
-      <c r="C386" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="387" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A387" s="14">
+      <c r="B387" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A388" s="14">
         <v>1010083992</v>
       </c>
-      <c r="B387" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="C387" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="388" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A388" s="21">
+      <c r="B388" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A389" s="21">
         <v>1010042579</v>
       </c>
-      <c r="B388" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="C388" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="389" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A389" s="14">
-        <v>133108</v>
-      </c>
-      <c r="B389" s="5" t="s">
-        <v>284</v>
+      <c r="B389" s="6" t="s">
+        <v>395</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>4</v>
@@ -6541,10 +6544,10 @@
     </row>
     <row r="390" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" s="14">
-        <v>269427</v>
+        <v>133108</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>285</v>
+        <v>396</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>4</v>
@@ -6552,10 +6555,10 @@
     </row>
     <row r="391" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" s="14">
-        <v>298227</v>
+        <v>269427</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>286</v>
+        <v>397</v>
       </c>
       <c r="C391" s="4" t="s">
         <v>4</v>
@@ -6563,10 +6566,10 @@
     </row>
     <row r="392" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" s="14">
-        <v>1010058052</v>
-      </c>
-      <c r="B392" s="35" t="s">
-        <v>288</v>
+        <v>298227</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>398</v>
       </c>
       <c r="C392" s="4" t="s">
         <v>4</v>
@@ -6574,10 +6577,10 @@
     </row>
     <row r="393" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" s="14">
-        <v>1010062285</v>
-      </c>
-      <c r="B393" s="5" t="s">
-        <v>287</v>
+        <v>1010058052</v>
+      </c>
+      <c r="B393" s="35" t="s">
+        <v>399</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>4</v>
@@ -6585,99 +6588,99 @@
     </row>
     <row r="394" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="14">
+        <v>1010062285</v>
+      </c>
+      <c r="B394" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C394" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A395" s="14">
         <v>1010050033</v>
       </c>
-      <c r="B394" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C394" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="395" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A395" s="33">
+      <c r="B395" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C395" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A396" s="33">
         <v>1010059726</v>
       </c>
-      <c r="B395" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="C395" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="F395" s="25"/>
-    </row>
-    <row r="396" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A396" s="18">
+      <c r="B396" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F396" s="25"/>
+    </row>
+    <row r="397" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A397" s="18">
         <v>1040098869</v>
       </c>
-      <c r="B396" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C396" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="397" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A397" s="16">
+      <c r="B397" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C397" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A398" s="16">
         <v>1010026464</v>
       </c>
-      <c r="B397" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="C397" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="398" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A398" s="14">
-        <v>1010026462</v>
-      </c>
       <c r="B398" s="5" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="399" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" s="14">
+        <v>1010026462</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C399" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A400" s="14">
         <v>1010084279</v>
       </c>
-      <c r="B399" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="C399" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="400" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A400" s="18">
-        <v>1010062045</v>
-      </c>
       <c r="B400" s="5" t="s">
-        <v>292</v>
+        <v>406</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" s="18">
+        <v>1010062045</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A402" s="18">
         <v>1010056523</v>
       </c>
-      <c r="B401" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C401" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A402" s="14">
-        <v>1010040346</v>
-      </c>
       <c r="B402" s="5" t="s">
-        <v>295</v>
+        <v>408</v>
       </c>
       <c r="C402" s="4" t="s">
         <v>4</v>
@@ -6685,10 +6688,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" s="14">
-        <v>1010014834</v>
+        <v>1010040346</v>
       </c>
       <c r="B403" s="5" t="s">
-        <v>168</v>
+        <v>409</v>
       </c>
       <c r="C403" s="4" t="s">
         <v>4</v>
@@ -6696,32 +6699,32 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="14">
+        <v>1010014834</v>
+      </c>
+      <c r="B404" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A405" s="14">
         <v>1040097575</v>
       </c>
-      <c r="B404" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C404" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A405" s="5">
+      <c r="B405" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A406" s="5">
         <v>1040100107</v>
       </c>
-      <c r="B405" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C405" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A406" s="14">
-        <v>1010021543</v>
-      </c>
       <c r="B406" s="5" t="s">
-        <v>296</v>
+        <v>412</v>
       </c>
       <c r="C406" s="4" t="s">
         <v>4</v>
@@ -6729,10 +6732,10 @@
     </row>
     <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="14">
-        <v>1040077397</v>
+        <v>1010021543</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>297</v>
+        <v>413</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>4</v>
@@ -6740,66 +6743,66 @@
     </row>
     <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="14">
-        <v>1010004281</v>
+        <v>1040077397</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>473</v>
+        <v>4</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="14">
-        <v>1040094213</v>
+        <v>1010004281</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>298</v>
+        <v>415</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="14">
+        <v>1040094213</v>
+      </c>
+      <c r="B410" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C410" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A411" s="14">
         <v>1010008144</v>
       </c>
-      <c r="B410" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="C410" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A411" s="17">
-        <v>1010085326</v>
-      </c>
-      <c r="B411" s="7" t="s">
-        <v>299</v>
+      <c r="B411" s="5" t="s">
+        <v>417</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D411" s="25"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="17">
+        <v>1010085326</v>
+      </c>
+      <c r="B412" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C412" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D412" s="25"/>
+    </row>
+    <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A413" s="17">
         <v>1010006162</v>
       </c>
-      <c r="B412" s="37" t="s">
-        <v>392</v>
-      </c>
-      <c r="C412" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A413" s="14">
-        <v>1010042688</v>
-      </c>
-      <c r="B413" s="7" t="s">
-        <v>301</v>
+      <c r="B413" s="37" t="s">
+        <v>419</v>
       </c>
       <c r="C413" s="4" t="s">
         <v>4</v>
@@ -6807,43 +6810,43 @@
     </row>
     <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="14">
+        <v>1010042688</v>
+      </c>
+      <c r="B414" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C414" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A415" s="14">
         <v>1010062007</v>
       </c>
-      <c r="B414" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="C414" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A415" s="13">
+      <c r="B415" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="C415" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A416" s="13">
         <v>1010050574</v>
       </c>
-      <c r="B415" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C415" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A416" s="18">
+      <c r="B416" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C416" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A417" s="18">
         <v>1010086126</v>
       </c>
-      <c r="B416" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C416" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A417" s="14">
-        <v>1010039879</v>
-      </c>
       <c r="B417" s="5" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="C417" s="4" t="s">
         <v>4</v>
@@ -6851,10 +6854,10 @@
     </row>
     <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="14">
-        <v>1010040133</v>
+        <v>1010039879</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>302</v>
+        <v>424</v>
       </c>
       <c r="C418" s="4" t="s">
         <v>4</v>
@@ -6862,10 +6865,10 @@
     </row>
     <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="14">
-        <v>1040043537</v>
+        <v>1010040133</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="C419" s="4" t="s">
         <v>4</v>
@@ -6873,10 +6876,10 @@
     </row>
     <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="14">
-        <v>62608</v>
+        <v>1040043537</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>304</v>
+        <v>426</v>
       </c>
       <c r="C420" s="4" t="s">
         <v>4</v>
@@ -6884,10 +6887,10 @@
     </row>
     <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" s="14">
-        <v>1010077469</v>
+        <v>62608</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>324</v>
+        <v>427</v>
       </c>
       <c r="C421" s="4" t="s">
         <v>4</v>
@@ -6895,10 +6898,10 @@
     </row>
     <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="14">
-        <v>1010077470</v>
+        <v>1010077469</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>325</v>
+        <v>428</v>
       </c>
       <c r="C422" s="4" t="s">
         <v>4</v>
@@ -6906,10 +6909,10 @@
     </row>
     <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="14">
-        <v>1010084519</v>
+        <v>1010077470</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>326</v>
+        <v>429</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>4</v>
@@ -6917,10 +6920,10 @@
     </row>
     <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="14">
-        <v>1010084108</v>
+        <v>1010084519</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>327</v>
+        <v>430</v>
       </c>
       <c r="C424" s="4" t="s">
         <v>4</v>
@@ -6928,10 +6931,10 @@
     </row>
     <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="14">
-        <v>1010087245</v>
+        <v>1010084108</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>321</v>
+        <v>431</v>
       </c>
       <c r="C425" s="4" t="s">
         <v>4</v>
@@ -6939,10 +6942,10 @@
     </row>
     <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="14">
-        <v>1010059685</v>
+        <v>1010087245</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>322</v>
+        <v>432</v>
       </c>
       <c r="C426" s="4" t="s">
         <v>4</v>
@@ -6950,10 +6953,10 @@
     </row>
     <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="14">
-        <v>1010059687</v>
+        <v>1010059685</v>
       </c>
       <c r="B427" s="5" t="s">
-        <v>323</v>
+        <v>433</v>
       </c>
       <c r="C427" s="4" t="s">
         <v>4</v>
@@ -6961,10 +6964,10 @@
     </row>
     <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="14">
-        <v>1040024322</v>
+        <v>1010059687</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="C428" s="4" t="s">
         <v>4</v>
@@ -6972,10 +6975,10 @@
     </row>
     <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="14">
-        <v>1010086877</v>
+        <v>1040024322</v>
       </c>
       <c r="B429" s="5" t="s">
-        <v>329</v>
+        <v>435</v>
       </c>
       <c r="C429" s="4" t="s">
         <v>4</v>
@@ -6983,10 +6986,10 @@
     </row>
     <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="14">
-        <v>1010042884</v>
-      </c>
-      <c r="B430" s="8" t="s">
-        <v>328</v>
+        <v>1010086877</v>
+      </c>
+      <c r="B430" s="5" t="s">
+        <v>436</v>
       </c>
       <c r="C430" s="4" t="s">
         <v>4</v>
@@ -6994,10 +6997,10 @@
     </row>
     <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" s="14">
-        <v>1010042564</v>
+        <v>1010042884</v>
       </c>
       <c r="B431" s="8" t="s">
-        <v>300</v>
+        <v>437</v>
       </c>
       <c r="C431" s="4" t="s">
         <v>4</v>
@@ -7005,10 +7008,10 @@
     </row>
     <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="14">
-        <v>1010059549</v>
-      </c>
-      <c r="B432" s="5" t="s">
-        <v>315</v>
+        <v>1010042564</v>
+      </c>
+      <c r="B432" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="C432" s="4" t="s">
         <v>4</v>
@@ -7016,10 +7019,10 @@
     </row>
     <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="14">
-        <v>1010046401</v>
+        <v>1010059549</v>
       </c>
       <c r="B433" s="5" t="s">
-        <v>331</v>
+        <v>439</v>
       </c>
       <c r="C433" s="4" t="s">
         <v>4</v>
@@ -7027,10 +7030,10 @@
     </row>
     <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="14">
-        <v>1010063326</v>
+        <v>1010046401</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>307</v>
+        <v>440</v>
       </c>
       <c r="C434" s="4" t="s">
         <v>4</v>
@@ -7038,10 +7041,10 @@
     </row>
     <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="14">
-        <v>1040017266</v>
+        <v>1010063326</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>306</v>
+        <v>441</v>
       </c>
       <c r="C435" s="4" t="s">
         <v>4</v>
@@ -7049,10 +7052,10 @@
     </row>
     <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="14">
-        <v>1040098603</v>
+        <v>1040017266</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>305</v>
+        <v>442</v>
       </c>
       <c r="C436" s="4" t="s">
         <v>4</v>
@@ -7060,21 +7063,21 @@
     </row>
     <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="14">
+        <v>1040098603</v>
+      </c>
+      <c r="B437" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C437" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A438" s="14">
         <v>1010026842</v>
       </c>
-      <c r="B437" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="C437" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A438" s="23">
-        <v>1010026841</v>
-      </c>
       <c r="B438" s="8" t="s">
-        <v>314</v>
+        <v>444</v>
       </c>
       <c r="C438" s="4" t="s">
         <v>4</v>
@@ -7082,10 +7085,10 @@
     </row>
     <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="23">
-        <v>1010042882</v>
+        <v>1010026841</v>
       </c>
       <c r="B439" s="8" t="s">
-        <v>311</v>
+        <v>445</v>
       </c>
       <c r="C439" s="4" t="s">
         <v>4</v>
@@ -7093,10 +7096,10 @@
     </row>
     <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="23">
-        <v>1010042873</v>
+        <v>1010042882</v>
       </c>
       <c r="B440" s="8" t="s">
-        <v>312</v>
+        <v>446</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>4</v>
@@ -7104,10 +7107,10 @@
     </row>
     <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="23">
-        <v>1010020552</v>
+        <v>1010042873</v>
       </c>
       <c r="B441" s="8" t="s">
-        <v>316</v>
+        <v>447</v>
       </c>
       <c r="C441" s="4" t="s">
         <v>4</v>
@@ -7115,21 +7118,21 @@
     </row>
     <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="23">
+        <v>1010020552</v>
+      </c>
+      <c r="B442" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C442" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A443" s="23">
         <v>1040078895</v>
       </c>
-      <c r="B442" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="C442" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A443" s="13">
-        <v>1040024309</v>
-      </c>
-      <c r="B443" s="9" t="s">
-        <v>318</v>
+      <c r="B443" s="5" t="s">
+        <v>449</v>
       </c>
       <c r="C443" s="4" t="s">
         <v>4</v>
@@ -7137,21 +7140,21 @@
     </row>
     <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="13">
+        <v>1040024309</v>
+      </c>
+      <c r="B444" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="C444" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A445" s="13">
         <v>1040024323</v>
       </c>
-      <c r="B444" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C444" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A445" s="14">
-        <v>1040019838</v>
-      </c>
       <c r="B445" s="5" t="s">
-        <v>310</v>
+        <v>451</v>
       </c>
       <c r="C445" s="4" t="s">
         <v>4</v>
@@ -7159,10 +7162,10 @@
     </row>
     <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="14">
-        <v>1010051284</v>
+        <v>1040019838</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>333</v>
+        <v>452</v>
       </c>
       <c r="C446" s="4" t="s">
         <v>4</v>
@@ -7170,10 +7173,10 @@
     </row>
     <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="14">
-        <v>1010032356</v>
+        <v>1010051284</v>
       </c>
       <c r="B447" s="5" t="s">
-        <v>68</v>
+        <v>453</v>
       </c>
       <c r="C447" s="4" t="s">
         <v>4</v>
@@ -7181,21 +7184,21 @@
     </row>
     <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" s="14">
+        <v>1010032356</v>
+      </c>
+      <c r="B448" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C448" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A449" s="14">
         <v>1010026889</v>
       </c>
-      <c r="B448" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="C448" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A449" s="21">
-        <v>1010042358</v>
-      </c>
       <c r="B449" s="5" t="s">
-        <v>337</v>
+        <v>455</v>
       </c>
       <c r="C449" s="4" t="s">
         <v>4</v>
@@ -7206,18 +7209,18 @@
         <v>1040017598</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>338</v>
+        <v>456</v>
       </c>
       <c r="C450" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A451" s="14">
-        <v>1040023848</v>
+      <c r="A451" s="21">
+        <v>1040018684</v>
       </c>
       <c r="B451" s="5" t="s">
-        <v>339</v>
+        <v>457</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>4</v>
@@ -7225,10 +7228,10 @@
     </row>
     <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" s="14">
-        <v>1040023858</v>
+        <v>1040023848</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>341</v>
+        <v>458</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>4</v>
@@ -7236,10 +7239,10 @@
     </row>
     <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="14">
-        <v>1010042341</v>
+        <v>1040023858</v>
       </c>
       <c r="B453" s="5" t="s">
-        <v>340</v>
+        <v>459</v>
       </c>
       <c r="C453" s="4" t="s">
         <v>4</v>
@@ -7247,10 +7250,10 @@
     </row>
     <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" s="14">
-        <v>1040098396</v>
+        <v>1010042341</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>342</v>
+        <v>460</v>
       </c>
       <c r="C454" s="4" t="s">
         <v>4</v>
@@ -7258,10 +7261,10 @@
     </row>
     <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="14">
-        <v>1010087281</v>
+        <v>1040098396</v>
       </c>
       <c r="B455" s="5" t="s">
-        <v>343</v>
+        <v>461</v>
       </c>
       <c r="C455" s="4" t="s">
         <v>4</v>
@@ -7269,10 +7272,10 @@
     </row>
     <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" s="14">
-        <v>1010027788</v>
+        <v>1010087281</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>334</v>
+        <v>462</v>
       </c>
       <c r="C456" s="4" t="s">
         <v>4</v>
@@ -7280,10 +7283,10 @@
     </row>
     <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" s="14">
-        <v>1010027786</v>
+        <v>1010027788</v>
       </c>
       <c r="B457" s="5" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
       <c r="C457" s="4" t="s">
         <v>4</v>
@@ -7291,10 +7294,10 @@
     </row>
     <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" s="14">
-        <v>1040101931</v>
+        <v>1010027786</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>345</v>
+        <v>464</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>4</v>
@@ -7302,10 +7305,10 @@
     </row>
     <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="14">
-        <v>1040041006</v>
+        <v>1040101931</v>
       </c>
       <c r="B459" s="5" t="s">
-        <v>344</v>
+        <v>465</v>
       </c>
       <c r="C459" s="4" t="s">
         <v>4</v>
@@ -7313,32 +7316,32 @@
     </row>
     <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" s="14">
-        <v>1010026973</v>
+        <v>1040041006</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>405</v>
+        <v>4</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" s="14">
-        <v>1040077410</v>
+        <v>1010026973</v>
       </c>
       <c r="B461" s="5" t="s">
-        <v>348</v>
+        <v>467</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" s="14">
-        <v>1040023843</v>
+        <v>1040077410</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>346</v>
+        <v>468</v>
       </c>
       <c r="C462" s="4" t="s">
         <v>4</v>
@@ -7346,10 +7349,10 @@
     </row>
     <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="14">
-        <v>1040077411</v>
+        <v>1040023843</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>347</v>
+        <v>469</v>
       </c>
       <c r="C463" s="4" t="s">
         <v>4</v>
@@ -7357,10 +7360,10 @@
     </row>
     <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="14">
-        <v>1040040960</v>
+        <v>1040077411</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>350</v>
+        <v>470</v>
       </c>
       <c r="C464" s="4" t="s">
         <v>4</v>
@@ -7368,10 +7371,10 @@
     </row>
     <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="14">
-        <v>1010062008</v>
+        <v>1040040960</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>349</v>
+        <v>471</v>
       </c>
       <c r="C465" s="4" t="s">
         <v>4</v>
@@ -7379,32 +7382,32 @@
     </row>
     <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="14">
+        <v>1010062008</v>
+      </c>
+      <c r="B466" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C466" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A467" s="14">
         <v>392696</v>
       </c>
-      <c r="B466" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="C466" s="4" t="s">
+      <c r="B467" s="5" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A467" s="5">
+      <c r="C467" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A468" s="5">
         <v>1010084767</v>
       </c>
-      <c r="B467" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="C467" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A468" s="14">
-        <v>1040077360</v>
-      </c>
       <c r="B468" s="5" t="s">
-        <v>354</v>
+        <v>474</v>
       </c>
       <c r="C468" s="4" t="s">
         <v>4</v>
@@ -7412,10 +7415,10 @@
     </row>
     <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="14">
-        <v>1010084930</v>
+        <v>1040077360</v>
       </c>
       <c r="B469" s="5" t="s">
-        <v>125</v>
+        <v>475</v>
       </c>
       <c r="C469" s="4" t="s">
         <v>4</v>
@@ -7423,54 +7426,54 @@
     </row>
     <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" s="14">
+        <v>1010084930</v>
+      </c>
+      <c r="B470" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C470" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A471" s="14">
         <v>1010007244</v>
       </c>
-      <c r="B470" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="C470" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A471" s="13">
+      <c r="B471" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="C471" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A472" s="13">
         <v>1010006827</v>
       </c>
-      <c r="B471" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="C471" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A472" s="14">
-        <v>1010044828</v>
-      </c>
       <c r="B472" s="5" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="14">
-        <v>1010021991</v>
+        <v>1010044828</v>
       </c>
       <c r="B473" s="5" t="s">
-        <v>356</v>
+        <v>479</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="14">
-        <v>1010021960</v>
+        <v>1010021991</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>357</v>
+        <v>480</v>
       </c>
       <c r="C474" s="4" t="s">
         <v>4</v>
@@ -7478,10 +7481,10 @@
     </row>
     <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="14">
-        <v>1010031536</v>
+        <v>1010021960</v>
       </c>
       <c r="B475" s="5" t="s">
-        <v>351</v>
+        <v>481</v>
       </c>
       <c r="C475" s="4" t="s">
         <v>4</v>
@@ -7489,10 +7492,10 @@
     </row>
     <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="14">
-        <v>1010031545</v>
+        <v>1010031536</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>352</v>
+        <v>482</v>
       </c>
       <c r="C476" s="4" t="s">
         <v>4</v>
@@ -7500,98 +7503,98 @@
     </row>
     <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="14">
+        <v>1010031545</v>
+      </c>
+      <c r="B477" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C477" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A478" s="14">
         <v>1010031690</v>
       </c>
-      <c r="B477" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C477" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="17">
-        <v>1010084370</v>
-      </c>
       <c r="B478" s="5" t="s">
-        <v>518</v>
+        <v>484</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>503</v>
+        <v>4</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" s="17">
+        <v>1010084370</v>
+      </c>
+      <c r="B479" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C479" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A480" s="17">
         <v>422759</v>
       </c>
-      <c r="B479" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="C479" s="4" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="14">
+      <c r="B480" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C480" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A481" s="14">
         <v>120955</v>
       </c>
-      <c r="B480" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="C480" s="4" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A481" s="13">
-        <v>1010084035</v>
-      </c>
       <c r="B481" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="C481" s="12" t="s">
-        <v>503</v>
+        <v>487</v>
+      </c>
+      <c r="C481" s="4" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" s="13">
+        <v>1010084035</v>
+      </c>
+      <c r="B482" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="C482" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A483" s="13">
         <v>1010000896</v>
       </c>
-      <c r="B482" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="C482" s="12" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="14">
-        <v>1010084308</v>
-      </c>
       <c r="B483" s="5" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="C483" s="12" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" s="14">
-        <v>1040098643</v>
+        <v>1010084308</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="C484" s="4" t="s">
-        <v>4</v>
+        <v>490</v>
+      </c>
+      <c r="C484" s="12" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="14">
-        <v>1010046550</v>
+        <v>1040098643</v>
       </c>
       <c r="B485" s="5" t="s">
-        <v>362</v>
+        <v>491</v>
       </c>
       <c r="C485" s="4" t="s">
         <v>4</v>
@@ -7599,10 +7602,10 @@
     </row>
     <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" s="14">
-        <v>1010086020</v>
+        <v>1010046550</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>361</v>
+        <v>492</v>
       </c>
       <c r="C486" s="4" t="s">
         <v>4</v>
@@ -7610,10 +7613,10 @@
     </row>
     <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="14">
-        <v>1010046402</v>
+        <v>1010086020</v>
       </c>
       <c r="B487" s="5" t="s">
-        <v>363</v>
+        <v>493</v>
       </c>
       <c r="C487" s="4" t="s">
         <v>4</v>
@@ -7621,10 +7624,10 @@
     </row>
     <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" s="14">
-        <v>1010022590</v>
+        <v>1010046402</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>359</v>
+        <v>494</v>
       </c>
       <c r="C488" s="4" t="s">
         <v>4</v>
@@ -7632,65 +7635,65 @@
     </row>
     <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" s="14">
-        <v>403459</v>
+        <v>1010022590</v>
       </c>
       <c r="B489" s="5" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>405</v>
+        <v>4</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" s="14">
-        <v>1010084313</v>
+        <v>403459</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>467</v>
+        <v>496</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" s="14">
-        <v>1040075426</v>
+        <v>1010084313</v>
       </c>
       <c r="B491" s="5" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" s="14">
-        <v>1040075427</v>
+        <v>1040075426</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" s="14">
-        <v>1010042609</v>
+        <v>1040075427</v>
       </c>
       <c r="B493" s="5" t="s">
-        <v>367</v>
+        <v>499</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" s="14">
-        <v>1040077412</v>
+        <v>1010042609</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>366</v>
+        <v>500</v>
       </c>
       <c r="C494" s="4" t="s">
         <v>4</v>
@@ -7698,21 +7701,21 @@
     </row>
     <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" s="14">
+        <v>1040077412</v>
+      </c>
+      <c r="B495" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="C495" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A496" s="14">
         <v>417701</v>
       </c>
-      <c r="B495" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="C495" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A496" s="15">
-        <v>399384</v>
-      </c>
       <c r="B496" s="8" t="s">
-        <v>369</v>
+        <v>502</v>
       </c>
       <c r="C496" s="4" t="s">
         <v>4</v>
@@ -7720,21 +7723,21 @@
     </row>
     <row r="497" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" s="15">
+        <v>399384</v>
+      </c>
+      <c r="B497" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="C497" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A498" s="15">
         <v>1010024086</v>
       </c>
-      <c r="B497" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="C497" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A498" s="14">
-        <v>1040077345</v>
-      </c>
-      <c r="B498" s="9" t="s">
-        <v>371</v>
+      <c r="B498" s="5" t="s">
+        <v>504</v>
       </c>
       <c r="C498" s="4" t="s">
         <v>4</v>
@@ -7742,10 +7745,10 @@
     </row>
     <row r="499" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" s="14">
-        <v>1040077368</v>
-      </c>
-      <c r="B499" s="5" t="s">
-        <v>372</v>
+        <v>1040077345</v>
+      </c>
+      <c r="B499" s="9" t="s">
+        <v>505</v>
       </c>
       <c r="C499" s="4" t="s">
         <v>4</v>
@@ -7753,10 +7756,10 @@
     </row>
     <row r="500" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" s="14">
-        <v>399253</v>
+        <v>1040077368</v>
       </c>
       <c r="B500" s="5" t="s">
-        <v>373</v>
+        <v>506</v>
       </c>
       <c r="C500" s="4" t="s">
         <v>4</v>
@@ -7764,10 +7767,10 @@
     </row>
     <row r="501" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" s="14">
-        <v>1010060291</v>
+        <v>399253</v>
       </c>
       <c r="B501" s="5" t="s">
-        <v>364</v>
+        <v>507</v>
       </c>
       <c r="C501" s="4" t="s">
         <v>4</v>
@@ -7775,10 +7778,10 @@
     </row>
     <row r="502" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" s="14">
-        <v>1010050920</v>
+        <v>1010060291</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>365</v>
+        <v>508</v>
       </c>
       <c r="C502" s="4" t="s">
         <v>4</v>
@@ -7786,10 +7789,10 @@
     </row>
     <row r="503" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" s="14">
-        <v>10168</v>
+        <v>1010050920</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>381</v>
+        <v>509</v>
       </c>
       <c r="C503" s="4" t="s">
         <v>4</v>
@@ -7797,32 +7800,32 @@
     </row>
     <row r="504" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" s="14">
+        <v>10168</v>
+      </c>
+      <c r="B504" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="C504" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A505" s="14">
         <v>1010084317</v>
       </c>
-      <c r="B504" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="C504" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A505" s="22">
+      <c r="B505" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C505" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A506" s="22">
         <v>1010085369</v>
       </c>
-      <c r="B505" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="C505" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A506" s="14">
-        <v>1010085370</v>
-      </c>
       <c r="B506" s="5" t="s">
-        <v>376</v>
+        <v>512</v>
       </c>
       <c r="C506" s="4" t="s">
         <v>4</v>
@@ -7830,10 +7833,10 @@
     </row>
     <row r="507" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" s="14">
-        <v>1010085204</v>
+        <v>1010085370</v>
       </c>
       <c r="B507" s="5" t="s">
-        <v>377</v>
+        <v>513</v>
       </c>
       <c r="C507" s="4" t="s">
         <v>4</v>
@@ -7841,32 +7844,32 @@
     </row>
     <row r="508" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" s="14">
+        <v>1010085204</v>
+      </c>
+      <c r="B508" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="C508" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A509" s="14">
         <v>1010083792</v>
       </c>
-      <c r="B508" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C508" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A509" s="33">
+      <c r="B509" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C509" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A510" s="33">
         <v>1040077414</v>
       </c>
-      <c r="B509" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C509" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A510" s="14">
-        <v>1010018482</v>
-      </c>
       <c r="B510" s="5" t="s">
-        <v>384</v>
+        <v>516</v>
       </c>
       <c r="C510" s="4" t="s">
         <v>4</v>
@@ -7874,32 +7877,32 @@
     </row>
     <row r="511" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" s="14">
+        <v>1010018482</v>
+      </c>
+      <c r="B511" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="C511" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A512" s="14">
         <v>1010084320</v>
       </c>
-      <c r="B511" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="C511" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A512" s="15">
+      <c r="B512" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="C512" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A513" s="15">
         <v>1010084532</v>
       </c>
-      <c r="B512" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="C512" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A513" s="14">
-        <v>1010052853</v>
-      </c>
       <c r="B513" s="5" t="s">
-        <v>391</v>
+        <v>519</v>
       </c>
       <c r="C513" s="4" t="s">
         <v>4</v>
@@ -7907,10 +7910,10 @@
     </row>
     <row r="514" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" s="14">
-        <v>1010027285</v>
+        <v>1010052853</v>
       </c>
       <c r="B514" s="5" t="s">
-        <v>387</v>
+        <v>520</v>
       </c>
       <c r="C514" s="4" t="s">
         <v>4</v>
@@ -7918,10 +7921,10 @@
     </row>
     <row r="515" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" s="14">
-        <v>1040077413</v>
+        <v>1010027285</v>
       </c>
       <c r="B515" s="5" t="s">
-        <v>388</v>
+        <v>521</v>
       </c>
       <c r="C515" s="4" t="s">
         <v>4</v>
@@ -7929,10 +7932,10 @@
     </row>
     <row r="516" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" s="14">
-        <v>1010085376</v>
+        <v>1040077413</v>
       </c>
       <c r="B516" s="5" t="s">
-        <v>389</v>
+        <v>522</v>
       </c>
       <c r="C516" s="4" t="s">
         <v>4</v>
@@ -7940,10 +7943,10 @@
     </row>
     <row r="517" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" s="14">
-        <v>1010022819</v>
+        <v>1010085376</v>
       </c>
       <c r="B517" s="5" t="s">
-        <v>390</v>
+        <v>523</v>
       </c>
       <c r="C517" s="4" t="s">
         <v>4</v>
@@ -7951,40 +7954,47 @@
     </row>
     <row r="518" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" s="14">
+        <v>1010022819</v>
+      </c>
+      <c r="B518" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="C518" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A519" s="14">
         <v>1010083885</v>
       </c>
-      <c r="B518" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C518" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A519" s="17">
+      <c r="B519" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="C519" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A520" s="17">
         <v>1010084377</v>
       </c>
-      <c r="B519" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="C519" s="36" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A520" s="31">
+      <c r="B520" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="C520" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A521" s="31">
         <v>1010022118</v>
       </c>
-      <c r="B520" s="32" t="s">
-        <v>501</v>
-      </c>
-      <c r="C520" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A521" s="2"/>
-      <c r="B521" s="2"/>
+      <c r="B521" s="32" t="s">
+        <v>527</v>
+      </c>
+      <c r="C521" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="522" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" s="2"/>
@@ -8028,11 +8038,11 @@
     </row>
     <row r="532" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" s="2"/>
-      <c r="B532" s="26"/>
+      <c r="B532" s="2"/>
     </row>
     <row r="533" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" s="2"/>
-      <c r="B533" s="2"/>
+      <c r="B533" s="26"/>
     </row>
     <row r="534" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" s="2"/>
@@ -9736,7 +9746,7 @@
     </row>
     <row r="959" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A959" s="2"/>
-      <c r="B959" s="1"/>
+      <c r="B959" s="2"/>
     </row>
     <row r="960" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A960" s="2"/>
@@ -10007,7 +10017,7 @@
       <c r="B1026" s="1"/>
     </row>
     <row r="1027" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1027" s="1"/>
+      <c r="A1027" s="2"/>
       <c r="B1027" s="1"/>
     </row>
     <row r="1028" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -10785,6 +10795,10 @@
     <row r="1221" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1221" s="1"/>
       <c r="B1221" s="1"/>
+    </row>
+    <row r="1222" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1222" s="1"/>
+      <c r="B1222" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10813,22 +10827,22 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>405</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>473</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>503</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>396</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
